--- a/fitness/docs/outils/cours-harmony.xlsx
+++ b/fitness/docs/outils/cours-harmony.xlsx
@@ -14,7 +14,7 @@
     <sheet name="Clubs" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cours'!$A$1:$X$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cours'!$A$1:$Z$81</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -576,7 +576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B34"/>
+  <dimension ref="B2:B37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -610,7 +610,7 @@
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Onglet « Cours » : un cours par ligne, et pour chaque club, dire si le cours y est donné et sous quelle forme. C'est la seule chose urgente. Les onglets « Textes » et « Clubs » peuvent attendre.</t>
+          <t>Onglet « Cours » : une ligne par cours, et une croix dans la colonne de chaque club où il est donné. C'est la seule chose urgente. Les onglets « Textes » et « Clubs » peuvent attendre.</t>
         </is>
       </c>
     </row>
@@ -620,142 +620,146 @@
     <row r="8" ht="20" customHeight="1">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Les deux colonnes grises, à ne pas négliger</t>
+          <t>La règle à retenir : une ligne = une forme de vente</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Identifiant · notre clé technique. Elle ne change jamais, même si le cours est renommé. Ne rien y écrire, ne pas la supprimer : c'est elle qui permet de recharger ce fichier sans tout recasser.</t>
+          <t>Un cours collectif est compris dans l'abonnement. Un Small Group Training se paie en plus, en Extra. Ce sont deux choses différentes, avec deux prix, deux durées parfois, et deux articles dans Echino. Donc deux lignes.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Code Echino · à vous. C'est le pont entre le site et Echino. Sans lui, les deux bases se rapprochent par le nom du cours, et ça casse au premier accent ou au premier renommage.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="B11" s="3" t="inlineStr"/>
+          <t>Quand la même pratique existe sous les deux formes selon le club, faites deux lignes et reliez-les par la colonne « Même cours que ». Exemple, déjà dans le fichier : Cross Training est un cours collectif à Versoix, et un Small Group Training à Genève · La Praille et Genève · Pâquis. Deux lignes, et le site n'en fera qu'une seule page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Un club ne peut pas être coché sur les deux lignes d'un même cours : il propose une forme ou l'autre, jamais les deux.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Les autres colonnes</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Cours · le nom exact, tel qu'il doit apparaître sur le site.</t>
+      <c r="B12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Les deux colonnes grises, à ne pas négliger</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Statut · Actif, Nouveau, ou À retirer. Ne supprimez pas une ligne : marquez-la À retirer, on saura quoi faire de l'existant.</t>
+          <t>Identifiant · notre clé technique. Elle ne change jamais, même si le cours est renommé. Ne rien y écrire, ne pas la supprimer : c'est elle qui permet de recharger ce fichier sans tout recasser.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Type · Cours co, SGT, ou « Les deux selon le club » quand la même pratique est incluse ici et payante ailleurs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Objectif principal · obligatoire. C'est lui qui range le cours dans le catalogue du site, classé par objectif. Un cours n'apparaît que dans un seul groupe, sinon le visiteur croit à deux cours.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Objectif secondaire · facultatif. Il s'affiche en second sur la fiche et il est pris en compte par la recherche.</t>
+          <t>Code Echino · à vous. C'est le pont entre le site et Echino. Sans lui, les deux bases se rapprochent par le nom du cours, et ça casse au premier accent ou au premier renommage. Un code par ligne, donc un code par forme de vente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="B16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Les autres colonnes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Intensité, Format, Durée · un choix chacun. La durée est celle du créneau type ; si elle varie d'un club à l'autre, dites-le en Remarques.</t>
+          <t>Cours · le nom exact, tel qu'il doit apparaître sur le site. Les deux lignes d'un même cours portent le même nom, c'est normal.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Licence · Les Mills, Hyrox, les deux, ou aucune. Une licence n'est pas un produit : elle ne s'affiche jamais seule comme nom de cours.</t>
+          <t>Statut · Actif, Nouveau, ou À retirer. Ne supprimez pas une ligne : marquez-la À retirer, on saura quoi faire de l'existant.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Places · seulement pour les petits groupes, le nombre de personnes maximum. C'est ce qui rend la réservation Echino nécessaire.</t>
+          <t>Type · Cours co ou SGT. C'est lui qui donne sa couleur aux croix de la ligne : vert pour ce qui est inclus, orange pour ce qui se paie.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Une colonne par club · vide si le cours n'y est pas donné, sinon Cours co (compris dans l'abonnement) ou SGT (payant, en Extra).</t>
+          <t>Même cours que · l'identifiant de l'autre ligne, quand la même pratique existe sous les deux formes. À remplir sur la ligne SGT, en pointant la ligne du cours collectif.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Contrôle · calculé, ne rien y écrire. La case devient rouge quand il manque quelque chose ou quand le Type et les clubs se contredisent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="B23" s="3" t="inlineStr"/>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Exemple de ligne</t>
+          <t>Famille (page hub) · la page qui réunit les variantes d'une même discipline, quand il y en a une : Pilates, Yoga, Les Mills, Aqua. Un cours qui appartient à une famille est listé sur sa page en plus du catalogue. « Aucune » si le cours ne se décline pas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Objectif principal · obligatoire. C'est lui qui range le cours dans le catalogue du site, classé par objectif. Un cours n'apparaît que dans un seul groupe, sinon le visiteur croit à deux cours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Objectif secondaire · facultatif. Il s'affiche en second sur la fiche et il est pris en compte par la recherche.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>HIIT · Type « Les deux selon le club » · Objectif principal « Se dépenser » · Intensité « Intense » · Format « Salle » · Durée 45 · Licence « Aucune » · Meyrin, Blandonnet, Genève · Eaux-Vives et Signy en « Cours co » · Genève · La Praille en « SGT » · les autres clubs laissés vides.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="B26" s="3" t="inlineStr"/>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Deux points d'attention</t>
+          <t>Intensité, Format, Durée · un choix chacun. La durée est celle du créneau type ; si elle varie d'un club à l'autre, dites-le en Remarques.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Licence · Les Mills, Hyrox, les deux, ou aucune. Une licence n'est pas un produit : elle ne s'affiche jamais seule comme nom de cours.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Places · seulement pour les petits groupes, le nombre de personnes maximum. C'est ce qui rend la réservation Echino nécessaire.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>1. Un Small Group Training n'est pas un cours collectif au sens du prix : il n'est compris dans aucune formule et s'ajoute à l'abonnement. C'est la distinction la plus importante de ce document, et la plus facile à rater : un planning ne dit pas si une séance est incluse ou payante.</t>
+          <t>Une colonne par club · une croix si le cours y est donné, rien sinon.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2. Un même nom peut porter les deux formes selon le club. C'est prévu : une seule ligne, et ce sont les colonnes des clubs qui le disent.</t>
+          <t>Contrôle · calculé, ne rien y écrire. La case devient rouge quand il manque quelque chose.</t>
         </is>
       </c>
     </row>
@@ -765,24 +769,41 @@
     <row r="31" ht="20" customHeight="1">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Les couleurs</t>
+          <t>Le point le plus facile à rater</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Jaune pâle · à remplir. Vert · cours compris dans l'abonnement. Orange · Small Group Training. Rouge · une incohérence à regarder.</t>
+          <t>Un planning ne dit pas si une séance est incluse ou payante. C'est exactement là que des Small Group Training nous ont été transmis comme des cours collectifs. Pour chaque ligne, la question à se poser est : est-ce que ça se paie en plus de l'abonnement ?</t>
         </is>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1">
       <c r="B33" s="3" t="inlineStr"/>
     </row>
-    <row r="34">
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Les lignes déjà remplies viennent des plannings qui nous ont été transmis. Elles sont à vérifier, pas à prendre pour argent comptant : c'est justement là que des cours collectifs et des Small Group Training ont été confondus.</t>
+    <row r="34" ht="20" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Les couleurs</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="3" t="inlineStr">
+        <is>
+          <t>Jaune pâle · à remplir. Vert · une croix sur une ligne Cours co. Orange · une croix sur une ligne SGT. Rouge · une incohérence à regarder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="B36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Les lignes déjà remplies viennent des plannings qui nous ont été transmis. Elles sont à vérifier, pas à prendre pour argent comptant.</t>
         </is>
       </c>
     </row>
@@ -797,33 +818,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X79"/>
+  <dimension ref="A1:Z81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="17" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
-    <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="15" customWidth="1" min="14" max="14"/>
-    <col width="15" customWidth="1" min="15" max="15"/>
-    <col width="15" customWidth="1" min="16" max="16"/>
-    <col width="15" customWidth="1" min="17" max="17"/>
-    <col width="15" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="15" customWidth="1" min="20" max="20"/>
-    <col width="15" customWidth="1" min="21" max="21"/>
-    <col width="15" customWidth="1" min="22" max="22"/>
-    <col width="30" customWidth="1" min="23" max="23"/>
-    <col width="40" customWidth="1" min="24" max="24"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="13" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="24" max="24"/>
+    <col width="34" customWidth="1" min="25" max="25"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1">
@@ -854,105 +877,115 @@
       </c>
       <c r="F1" s="6" t="inlineStr">
         <is>
+          <t>Même cours que</t>
+        </is>
+      </c>
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Famille (page hub)</t>
+        </is>
+      </c>
+      <c r="H1" s="6" t="inlineStr">
+        <is>
           <t>Objectif principal</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>Objectif secondaire</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>Intensité</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>Format</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="L1" s="6" t="inlineStr">
         <is>
           <t>Durée (min)</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="M1" s="6" t="inlineStr">
         <is>
           <t>Licence</t>
         </is>
       </c>
-      <c r="L1" s="6" t="inlineStr">
+      <c r="N1" s="6" t="inlineStr">
         <is>
           <t>Places (petit groupe)</t>
         </is>
       </c>
-      <c r="M1" s="7" t="inlineStr">
+      <c r="O1" s="7" t="inlineStr">
         <is>
           <t>Blandonnet
 (Essential)</t>
         </is>
       </c>
-      <c r="N1" s="7" t="inlineStr">
+      <c r="P1" s="7" t="inlineStr">
         <is>
           <t>Genève · Eaux-Vives
 (Essential)</t>
         </is>
       </c>
-      <c r="O1" s="7" t="inlineStr">
+      <c r="Q1" s="7" t="inlineStr">
         <is>
           <t>Genève · La Praille
 (Premium)</t>
         </is>
       </c>
-      <c r="P1" s="7" t="inlineStr">
+      <c r="R1" s="7" t="inlineStr">
         <is>
           <t>Genève · Pâquis
 (Gym)</t>
         </is>
       </c>
-      <c r="Q1" s="7" t="inlineStr">
+      <c r="S1" s="7" t="inlineStr">
         <is>
           <t>Meyrin
 (Essential)</t>
         </is>
       </c>
-      <c r="R1" s="7" t="inlineStr">
+      <c r="T1" s="7" t="inlineStr">
         <is>
           <t>Versoix
 (Essential)</t>
         </is>
       </c>
-      <c r="S1" s="7" t="inlineStr">
+      <c r="U1" s="7" t="inlineStr">
         <is>
           <t>Veyrier
 (Premium)</t>
         </is>
       </c>
-      <c r="T1" s="7" t="inlineStr">
+      <c r="V1" s="7" t="inlineStr">
         <is>
           <t>Denges
 (Premium)</t>
         </is>
       </c>
-      <c r="U1" s="7" t="inlineStr">
+      <c r="W1" s="7" t="inlineStr">
         <is>
           <t>Gland
 (Essential)</t>
         </is>
       </c>
-      <c r="V1" s="7" t="inlineStr">
+      <c r="X1" s="7" t="inlineStr">
         <is>
           <t>Signy
 (Essential)</t>
         </is>
       </c>
-      <c r="W1" s="6" t="inlineStr">
+      <c r="Y1" s="6" t="inlineStr">
         <is>
           <t>Contrôle</t>
         </is>
       </c>
-      <c r="X1" s="6" t="inlineStr">
+      <c r="Z1" s="6" t="inlineStr">
         <is>
           <t>Remarques</t>
         </is>
@@ -980,66 +1013,72 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="9" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>Pilates</t>
+        </is>
+      </c>
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I2" s="9" t="inlineStr">
+      <c r="K2" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J2" s="10" t="n">
+      <c r="L2" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="M2" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N2" s="10" t="inlineStr"/>
+      <c r="N2" s="10" t="n"/>
       <c r="O2" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P2" s="10" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P2" s="10" t="n"/>
       <c r="Q2" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R2" s="10" t="inlineStr"/>
-      <c r="S2" s="10" t="inlineStr"/>
-      <c r="T2" s="10" t="inlineStr"/>
-      <c r="U2" s="10" t="inlineStr"/>
-      <c r="V2" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W2" s="11">
-        <f>IF(C2="","",IF(E2="","Type à choisir",IF(F2="","Objectif principal à choisir",IF(H2="","Intensité à choisir",IF(I2="","Format à choisir",IF(COUNTIF(M2:V2,"Cours co")+COUNTIF(M2:V2,"SGT")=0,"Aucun club coché",IF(E2=IF(COUNTIF(M2:V2,"Cours co")&gt;0,IF(COUNTIF(M2:V2,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X2" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y2" s="11">
+        <f>IF(C2="","",IF(E2="","Type à choisir",IF(H2="","Objectif principal à choisir",IF(J2="","Intensité à choisir",IF(K2="","Format à choisir",IF(COUNTA(O2:X2)=0,"Aucun club coché",IF(AND(F2&lt;&gt;"",COUNTIF($A$2:$A$81,F2)=0),"Même cours que : identifiant inconnu",IF(AND(F2&lt;&gt;"",F2=A2),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z2" s="9" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
@@ -1063,50 +1102,56 @@
           <t>SGT</t>
         </is>
       </c>
-      <c r="F3" s="9" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr"/>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>Pilates</t>
+        </is>
+      </c>
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G3" s="9" t="inlineStr"/>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I3" s="9" t="inlineStr">
+      <c r="K3" s="9" t="inlineStr">
         <is>
           <t>Petit groupe</t>
         </is>
       </c>
-      <c r="J3" s="10" t="n">
+      <c r="L3" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="M3" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="inlineStr"/>
-      <c r="N3" s="10" t="inlineStr"/>
-      <c r="O3" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="P3" s="10" t="inlineStr"/>
-      <c r="Q3" s="10" t="inlineStr"/>
-      <c r="R3" s="10" t="inlineStr"/>
-      <c r="S3" s="10" t="inlineStr"/>
-      <c r="T3" s="10" t="inlineStr"/>
-      <c r="U3" s="10" t="inlineStr"/>
-      <c r="V3" s="10" t="inlineStr"/>
-      <c r="W3" s="11">
-        <f>IF(C3="","",IF(E3="","Type à choisir",IF(F3="","Objectif principal à choisir",IF(H3="","Intensité à choisir",IF(I3="","Format à choisir",IF(COUNTIF(M3:V3,"Cours co")+COUNTIF(M3:V3,"SGT")=0,"Aucun club coché",IF(E3=IF(COUNTIF(M3:V3,"Cours co")&gt;0,IF(COUNTIF(M3:V3,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X3" s="9" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="11">
+        <f>IF(C3="","",IF(E3="","Type à choisir",IF(H3="","Objectif principal à choisir",IF(J3="","Intensité à choisir",IF(K3="","Format à choisir",IF(COUNTA(O3:X3)=0,"Aucun club coché",IF(AND(F3&lt;&gt;"",COUNTIF($A$2:$A$81,F3)=0),"Même cours que : identifiant inconnu",IF(AND(F3&lt;&gt;"",F3=A3),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
@@ -1130,50 +1175,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F4" s="9" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr"/>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>Pilates</t>
+        </is>
+      </c>
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="G4" s="9" t="inlineStr"/>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="I4" s="9" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="K4" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n">
+      <c r="L4" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="M4" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="inlineStr"/>
-      <c r="N4" s="10" t="inlineStr"/>
-      <c r="O4" s="10" t="inlineStr"/>
-      <c r="P4" s="10" t="inlineStr"/>
-      <c r="Q4" s="10" t="inlineStr"/>
-      <c r="R4" s="10" t="inlineStr"/>
-      <c r="S4" s="10" t="inlineStr"/>
-      <c r="T4" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U4" s="10" t="inlineStr"/>
-      <c r="V4" s="10" t="inlineStr"/>
-      <c r="W4" s="11">
-        <f>IF(C4="","",IF(E4="","Type à choisir",IF(F4="","Objectif principal à choisir",IF(H4="","Intensité à choisir",IF(I4="","Format à choisir",IF(COUNTIF(M4:V4,"Cours co")+COUNTIF(M4:V4,"SGT")=0,"Aucun club coché",IF(E4=IF(COUNTIF(M4:V4,"Cours co")&gt;0,IF(COUNTIF(M4:V4,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X4" s="9" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="11">
+        <f>IF(C4="","",IF(E4="","Type à choisir",IF(H4="","Objectif principal à choisir",IF(J4="","Intensité à choisir",IF(K4="","Format à choisir",IF(COUNTA(O4:X4)=0,"Aucun club coché",IF(AND(F4&lt;&gt;"",COUNTIF($A$2:$A$81,F4)=0),"Même cours que : identifiant inconnu",IF(AND(F4&lt;&gt;"",F4=A4),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
@@ -1197,50 +1248,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F5" s="9" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>Pilates</t>
+        </is>
+      </c>
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G5" s="9" t="inlineStr"/>
-      <c r="H5" s="9" t="inlineStr">
+      <c r="I5" s="9" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I5" s="9" t="inlineStr">
+      <c r="K5" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="L5" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K5" s="9" t="inlineStr">
+      <c r="M5" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L5" s="10" t="n"/>
-      <c r="M5" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N5" s="10" t="inlineStr"/>
-      <c r="O5" s="10" t="inlineStr"/>
-      <c r="P5" s="10" t="inlineStr"/>
-      <c r="Q5" s="10" t="inlineStr"/>
-      <c r="R5" s="10" t="inlineStr"/>
-      <c r="S5" s="10" t="inlineStr"/>
-      <c r="T5" s="10" t="inlineStr"/>
-      <c r="U5" s="10" t="inlineStr"/>
-      <c r="V5" s="10" t="inlineStr"/>
-      <c r="W5" s="11">
-        <f>IF(C5="","",IF(E5="","Type à choisir",IF(F5="","Objectif principal à choisir",IF(H5="","Intensité à choisir",IF(I5="","Format à choisir",IF(COUNTIF(M5:V5,"Cours co")+COUNTIF(M5:V5,"SGT")=0,"Aucun club coché",IF(E5=IF(COUNTIF(M5:V5,"Cours co")&gt;0,IF(COUNTIF(M5:V5,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X5" s="9" t="n"/>
+      <c r="N5" s="10" t="n"/>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n"/>
+      <c r="S5" s="10" t="n"/>
+      <c r="T5" s="10" t="n"/>
+      <c r="U5" s="10" t="n"/>
+      <c r="V5" s="10" t="n"/>
+      <c r="W5" s="10" t="n"/>
+      <c r="X5" s="10" t="n"/>
+      <c r="Y5" s="11">
+        <f>IF(C5="","",IF(E5="","Type à choisir",IF(H5="","Objectif principal à choisir",IF(J5="","Intensité à choisir",IF(K5="","Format à choisir",IF(COUNTA(O5:X5)=0,"Aucun club coché",IF(AND(F5&lt;&gt;"",COUNTIF($A$2:$A$81,F5)=0),"Même cours que : identifiant inconnu",IF(AND(F5&lt;&gt;"",F5=A5),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -1264,50 +1321,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr"/>
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>Pilates</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr"/>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J6" s="10" t="n">
+      <c r="L6" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K6" s="9" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L6" s="10" t="n"/>
-      <c r="M6" s="10" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr"/>
-      <c r="O6" s="10" t="inlineStr"/>
-      <c r="P6" s="10" t="inlineStr"/>
-      <c r="Q6" s="10" t="inlineStr"/>
-      <c r="R6" s="10" t="inlineStr"/>
-      <c r="S6" s="10" t="inlineStr"/>
-      <c r="T6" s="10" t="inlineStr"/>
-      <c r="U6" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="V6" s="10" t="inlineStr"/>
-      <c r="W6" s="11">
-        <f>IF(C6="","",IF(E6="","Type à choisir",IF(F6="","Objectif principal à choisir",IF(H6="","Intensité à choisir",IF(I6="","Format à choisir",IF(COUNTIF(M6:V6,"Cours co")+COUNTIF(M6:V6,"SGT")=0,"Aucun club coché",IF(E6=IF(COUNTIF(M6:V6,"Cours co")&gt;0,IF(COUNTIF(M6:V6,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X6" s="9" t="n"/>
+      <c r="N6" s="10" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="10" t="n"/>
+      <c r="S6" s="10" t="n"/>
+      <c r="T6" s="10" t="n"/>
+      <c r="U6" s="10" t="n"/>
+      <c r="V6" s="10" t="n"/>
+      <c r="W6" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X6" s="10" t="n"/>
+      <c r="Y6" s="11">
+        <f>IF(C6="","",IF(E6="","Type à choisir",IF(H6="","Objectif principal à choisir",IF(J6="","Intensité à choisir",IF(K6="","Format à choisir",IF(COUNTA(O6:X6)=0,"Aucun club coché",IF(AND(F6&lt;&gt;"",COUNTIF($A$2:$A$81,F6)=0),"Même cours que : identifiant inconnu",IF(AND(F6&lt;&gt;"",F6=A6),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z6" s="9" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
@@ -1331,50 +1394,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F7" s="9" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>Pilates</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr"/>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr"/>
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="K7" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J7" s="10" t="n">
+      <c r="L7" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="K7" s="9" t="inlineStr">
+      <c r="M7" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L7" s="10" t="n"/>
-      <c r="M7" s="10" t="inlineStr"/>
-      <c r="N7" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="O7" s="10" t="inlineStr"/>
-      <c r="P7" s="10" t="inlineStr"/>
-      <c r="Q7" s="10" t="inlineStr"/>
-      <c r="R7" s="10" t="inlineStr"/>
-      <c r="S7" s="10" t="inlineStr"/>
-      <c r="T7" s="10" t="inlineStr"/>
-      <c r="U7" s="10" t="inlineStr"/>
-      <c r="V7" s="10" t="inlineStr"/>
-      <c r="W7" s="11">
-        <f>IF(C7="","",IF(E7="","Type à choisir",IF(F7="","Objectif principal à choisir",IF(H7="","Intensité à choisir",IF(I7="","Format à choisir",IF(COUNTIF(M7:V7,"Cours co")+COUNTIF(M7:V7,"SGT")=0,"Aucun club coché",IF(E7=IF(COUNTIF(M7:V7,"Cours co")&gt;0,IF(COUNTIF(M7:V7,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X7" s="9" t="n"/>
+      <c r="N7" s="10" t="n"/>
+      <c r="O7" s="10" t="n"/>
+      <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n"/>
+      <c r="S7" s="10" t="n"/>
+      <c r="T7" s="10" t="n"/>
+      <c r="U7" s="10" t="n"/>
+      <c r="V7" s="10" t="n"/>
+      <c r="W7" s="10" t="n"/>
+      <c r="X7" s="10" t="n"/>
+      <c r="Y7" s="11">
+        <f>IF(C7="","",IF(E7="","Type à choisir",IF(H7="","Objectif principal à choisir",IF(J7="","Intensité à choisir",IF(K7="","Format à choisir",IF(COUNTA(O7:X7)=0,"Aucun club coché",IF(AND(F7&lt;&gt;"",COUNTIF($A$2:$A$81,F7)=0),"Même cours que : identifiant inconnu",IF(AND(F7&lt;&gt;"",F7=A7),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z7" s="9" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -1398,50 +1467,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F8" s="9" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr"/>
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>Pilates</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G8" s="9" t="inlineStr"/>
-      <c r="H8" s="9" t="inlineStr">
+      <c r="I8" s="9" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I8" s="9" t="inlineStr">
+      <c r="K8" s="9" t="inlineStr">
         <is>
           <t>Petit groupe</t>
         </is>
       </c>
-      <c r="J8" s="10" t="n">
+      <c r="L8" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K8" s="9" t="inlineStr">
+      <c r="M8" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L8" s="10" t="n"/>
-      <c r="M8" s="10" t="inlineStr"/>
-      <c r="N8" s="10" t="inlineStr"/>
-      <c r="O8" s="10" t="inlineStr"/>
-      <c r="P8" s="10" t="inlineStr"/>
-      <c r="Q8" s="10" t="inlineStr"/>
-      <c r="R8" s="10" t="inlineStr"/>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="T8" s="10" t="inlineStr"/>
-      <c r="U8" s="10" t="inlineStr"/>
-      <c r="V8" s="10" t="inlineStr"/>
-      <c r="W8" s="11">
-        <f>IF(C8="","",IF(E8="","Type à choisir",IF(F8="","Objectif principal à choisir",IF(H8="","Intensité à choisir",IF(I8="","Format à choisir",IF(COUNTIF(M8:V8,"Cours co")+COUNTIF(M8:V8,"SGT")=0,"Aucun club coché",IF(E8=IF(COUNTIF(M8:V8,"Cours co")&gt;0,IF(COUNTIF(M8:V8,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X8" s="9" t="n"/>
+      <c r="N8" s="10" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n"/>
+      <c r="S8" s="10" t="n"/>
+      <c r="T8" s="10" t="n"/>
+      <c r="U8" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V8" s="10" t="n"/>
+      <c r="W8" s="10" t="n"/>
+      <c r="X8" s="10" t="n"/>
+      <c r="Y8" s="11">
+        <f>IF(C8="","",IF(E8="","Type à choisir",IF(H8="","Objectif principal à choisir",IF(J8="","Intensité à choisir",IF(K8="","Format à choisir",IF(COUNTA(O8:X8)=0,"Aucun club coché",IF(AND(F8&lt;&gt;"",COUNTIF($A$2:$A$81,F8)=0),"Même cours que : identifiant inconnu",IF(AND(F8&lt;&gt;"",F8=A8),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z8" s="9" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
@@ -1465,54 +1540,60 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F9" s="9" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>Yoga</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>Se détendre</t>
         </is>
       </c>
-      <c r="G9" s="9" t="inlineStr"/>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I9" s="9" t="inlineStr">
+      <c r="K9" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J9" s="10" t="n">
+      <c r="L9" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K9" s="9" t="inlineStr">
+      <c r="M9" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L9" s="10" t="n"/>
-      <c r="M9" s="10" t="inlineStr"/>
-      <c r="N9" s="10" t="inlineStr"/>
-      <c r="O9" s="10" t="inlineStr"/>
-      <c r="P9" s="10" t="inlineStr"/>
-      <c r="Q9" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R9" s="10" t="inlineStr"/>
+      <c r="N9" s="10" t="n"/>
+      <c r="O9" s="10" t="n"/>
+      <c r="P9" s="10" t="n"/>
+      <c r="Q9" s="10" t="n"/>
+      <c r="R9" s="10" t="n"/>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="T9" s="10" t="inlineStr"/>
-      <c r="U9" s="10" t="inlineStr"/>
-      <c r="V9" s="10" t="inlineStr"/>
-      <c r="W9" s="11">
-        <f>IF(C9="","",IF(E9="","Type à choisir",IF(F9="","Objectif principal à choisir",IF(H9="","Intensité à choisir",IF(I9="","Format à choisir",IF(COUNTIF(M9:V9,"Cours co")+COUNTIF(M9:V9,"SGT")=0,"Aucun club coché",IF(E9=IF(COUNTIF(M9:V9,"Cours co")&gt;0,IF(COUNTIF(M9:V9,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X9" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T9" s="10" t="n"/>
+      <c r="U9" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V9" s="10" t="n"/>
+      <c r="W9" s="10" t="n"/>
+      <c r="X9" s="10" t="n"/>
+      <c r="Y9" s="11">
+        <f>IF(C9="","",IF(E9="","Type à choisir",IF(H9="","Objectif principal à choisir",IF(J9="","Intensité à choisir",IF(K9="","Format à choisir",IF(COUNTA(O9:X9)=0,"Aucun club coché",IF(AND(F9&lt;&gt;"",COUNTIF($A$2:$A$81,F9)=0),"Même cours que : identifiant inconnu",IF(AND(F9&lt;&gt;"",F9=A9),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
@@ -1536,50 +1617,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F10" s="9" t="inlineStr">
+      <c r="F10" s="9" t="inlineStr"/>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>Yoga</t>
+        </is>
+      </c>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>Se détendre</t>
         </is>
       </c>
-      <c r="G10" s="9" t="inlineStr"/>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I10" s="9" t="inlineStr">
+      <c r="K10" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="L10" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K10" s="9" t="inlineStr">
+      <c r="M10" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L10" s="10" t="n"/>
-      <c r="M10" s="10" t="inlineStr"/>
-      <c r="N10" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="O10" s="10" t="inlineStr"/>
-      <c r="P10" s="10" t="inlineStr"/>
-      <c r="Q10" s="10" t="inlineStr"/>
-      <c r="R10" s="10" t="inlineStr"/>
-      <c r="S10" s="10" t="inlineStr"/>
-      <c r="T10" s="10" t="inlineStr"/>
-      <c r="U10" s="10" t="inlineStr"/>
-      <c r="V10" s="10" t="inlineStr"/>
-      <c r="W10" s="11">
-        <f>IF(C10="","",IF(E10="","Type à choisir",IF(F10="","Objectif principal à choisir",IF(H10="","Intensité à choisir",IF(I10="","Format à choisir",IF(COUNTIF(M10:V10,"Cours co")+COUNTIF(M10:V10,"SGT")=0,"Aucun club coché",IF(E10=IF(COUNTIF(M10:V10,"Cours co")&gt;0,IF(COUNTIF(M10:V10,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X10" s="9" t="n"/>
+      <c r="N10" s="10" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q10" s="10" t="n"/>
+      <c r="R10" s="10" t="n"/>
+      <c r="S10" s="10" t="n"/>
+      <c r="T10" s="10" t="n"/>
+      <c r="U10" s="10" t="n"/>
+      <c r="V10" s="10" t="n"/>
+      <c r="W10" s="10" t="n"/>
+      <c r="X10" s="10" t="n"/>
+      <c r="Y10" s="11">
+        <f>IF(C10="","",IF(E10="","Type à choisir",IF(H10="","Objectif principal à choisir",IF(J10="","Intensité à choisir",IF(K10="","Format à choisir",IF(COUNTA(O10:X10)=0,"Aucun club coché",IF(AND(F10&lt;&gt;"",COUNTIF($A$2:$A$81,F10)=0),"Même cours que : identifiant inconnu",IF(AND(F10&lt;&gt;"",F10=A10),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
@@ -1603,50 +1690,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F11" s="9" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Yoga</t>
+        </is>
+      </c>
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>Se détendre</t>
         </is>
       </c>
-      <c r="G11" s="9" t="inlineStr"/>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr"/>
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I11" s="9" t="inlineStr">
+      <c r="K11" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J11" s="10" t="n">
+      <c r="L11" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K11" s="9" t="inlineStr">
+      <c r="M11" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L11" s="10" t="n"/>
-      <c r="M11" s="10" t="inlineStr"/>
-      <c r="N11" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="O11" s="10" t="inlineStr"/>
-      <c r="P11" s="10" t="inlineStr"/>
-      <c r="Q11" s="10" t="inlineStr"/>
-      <c r="R11" s="10" t="inlineStr"/>
-      <c r="S11" s="10" t="inlineStr"/>
-      <c r="T11" s="10" t="inlineStr"/>
-      <c r="U11" s="10" t="inlineStr"/>
-      <c r="V11" s="10" t="inlineStr"/>
-      <c r="W11" s="11">
-        <f>IF(C11="","",IF(E11="","Type à choisir",IF(F11="","Objectif principal à choisir",IF(H11="","Intensité à choisir",IF(I11="","Format à choisir",IF(COUNTIF(M11:V11,"Cours co")+COUNTIF(M11:V11,"SGT")=0,"Aucun club coché",IF(E11=IF(COUNTIF(M11:V11,"Cours co")&gt;0,IF(COUNTIF(M11:V11,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X11" s="9" t="n"/>
+      <c r="N11" s="10" t="n"/>
+      <c r="O11" s="10" t="n"/>
+      <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="n"/>
+      <c r="R11" s="10" t="n"/>
+      <c r="S11" s="10" t="n"/>
+      <c r="T11" s="10" t="n"/>
+      <c r="U11" s="10" t="n"/>
+      <c r="V11" s="10" t="n"/>
+      <c r="W11" s="10" t="n"/>
+      <c r="X11" s="10" t="n"/>
+      <c r="Y11" s="11">
+        <f>IF(C11="","",IF(E11="","Type à choisir",IF(H11="","Objectif principal à choisir",IF(J11="","Intensité à choisir",IF(K11="","Format à choisir",IF(COUNTA(O11:X11)=0,"Aucun club coché",IF(AND(F11&lt;&gt;"",COUNTIF($A$2:$A$81,F11)=0),"Même cours que : identifiant inconnu",IF(AND(F11&lt;&gt;"",F11=A11),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
@@ -1670,50 +1763,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F12" s="9" t="inlineStr">
+      <c r="F12" s="9" t="inlineStr"/>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Yoga</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>Se détendre</t>
         </is>
       </c>
-      <c r="G12" s="9" t="inlineStr"/>
-      <c r="H12" s="9" t="inlineStr">
+      <c r="I12" s="9" t="inlineStr"/>
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I12" s="9" t="inlineStr">
+      <c r="K12" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="L12" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K12" s="9" t="inlineStr">
+      <c r="M12" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L12" s="10" t="n"/>
-      <c r="M12" s="10" t="inlineStr"/>
-      <c r="N12" s="10" t="inlineStr"/>
-      <c r="O12" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P12" s="10" t="inlineStr"/>
-      <c r="Q12" s="10" t="inlineStr"/>
-      <c r="R12" s="10" t="inlineStr"/>
-      <c r="S12" s="10" t="inlineStr"/>
-      <c r="T12" s="10" t="inlineStr"/>
-      <c r="U12" s="10" t="inlineStr"/>
-      <c r="V12" s="10" t="inlineStr"/>
-      <c r="W12" s="11">
-        <f>IF(C12="","",IF(E12="","Type à choisir",IF(F12="","Objectif principal à choisir",IF(H12="","Intensité à choisir",IF(I12="","Format à choisir",IF(COUNTIF(M12:V12,"Cours co")+COUNTIF(M12:V12,"SGT")=0,"Aucun club coché",IF(E12=IF(COUNTIF(M12:V12,"Cours co")&gt;0,IF(COUNTIF(M12:V12,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X12" s="9" t="n"/>
+      <c r="N12" s="10" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R12" s="10" t="n"/>
+      <c r="S12" s="10" t="n"/>
+      <c r="T12" s="10" t="n"/>
+      <c r="U12" s="10" t="n"/>
+      <c r="V12" s="10" t="n"/>
+      <c r="W12" s="10" t="n"/>
+      <c r="X12" s="10" t="n"/>
+      <c r="Y12" s="11">
+        <f>IF(C12="","",IF(E12="","Type à choisir",IF(H12="","Objectif principal à choisir",IF(J12="","Intensité à choisir",IF(K12="","Format à choisir",IF(COUNTA(O12:X12)=0,"Aucun club coché",IF(AND(F12&lt;&gt;"",COUNTIF($A$2:$A$81,F12)=0),"Même cours que : identifiant inconnu",IF(AND(F12&lt;&gt;"",F12=A12),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z12" s="9" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
@@ -1737,50 +1836,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F13" s="9" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Yoga</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t>Se détendre</t>
         </is>
       </c>
-      <c r="G13" s="9" t="inlineStr"/>
-      <c r="H13" s="9" t="inlineStr">
+      <c r="I13" s="9" t="inlineStr"/>
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I13" s="9" t="inlineStr">
+      <c r="K13" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J13" s="10" t="n">
+      <c r="L13" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K13" s="9" t="inlineStr">
+      <c r="M13" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L13" s="10" t="n"/>
-      <c r="M13" s="10" t="inlineStr"/>
-      <c r="N13" s="10" t="inlineStr"/>
-      <c r="O13" s="10" t="inlineStr"/>
-      <c r="P13" s="10" t="inlineStr"/>
-      <c r="Q13" s="10" t="inlineStr"/>
-      <c r="R13" s="10" t="inlineStr"/>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="T13" s="10" t="inlineStr"/>
-      <c r="U13" s="10" t="inlineStr"/>
-      <c r="V13" s="10" t="inlineStr"/>
-      <c r="W13" s="11">
-        <f>IF(C13="","",IF(E13="","Type à choisir",IF(F13="","Objectif principal à choisir",IF(H13="","Intensité à choisir",IF(I13="","Format à choisir",IF(COUNTIF(M13:V13,"Cours co")+COUNTIF(M13:V13,"SGT")=0,"Aucun club coché",IF(E13=IF(COUNTIF(M13:V13,"Cours co")&gt;0,IF(COUNTIF(M13:V13,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X13" s="9" t="n"/>
+      <c r="N13" s="10" t="n"/>
+      <c r="O13" s="10" t="n"/>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n"/>
+      <c r="S13" s="10" t="n"/>
+      <c r="T13" s="10" t="n"/>
+      <c r="U13" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V13" s="10" t="n"/>
+      <c r="W13" s="10" t="n"/>
+      <c r="X13" s="10" t="n"/>
+      <c r="Y13" s="11">
+        <f>IF(C13="","",IF(E13="","Type à choisir",IF(H13="","Objectif principal à choisir",IF(J13="","Intensité à choisir",IF(K13="","Format à choisir",IF(COUNTA(O13:X13)=0,"Aucun club coché",IF(AND(F13&lt;&gt;"",COUNTIF($A$2:$A$81,F13)=0),"Même cours que : identifiant inconnu",IF(AND(F13&lt;&gt;"",F13=A13),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
@@ -1804,50 +1909,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr"/>
+      <c r="G14" s="9" t="inlineStr">
+        <is>
+          <t>Yoga</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr"/>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr"/>
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J14" s="10" t="n">
+      <c r="L14" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L14" s="10" t="n"/>
-      <c r="M14" s="10" t="inlineStr"/>
-      <c r="N14" s="10" t="inlineStr"/>
-      <c r="O14" s="10" t="inlineStr"/>
-      <c r="P14" s="10" t="inlineStr"/>
-      <c r="Q14" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R14" s="10" t="inlineStr"/>
-      <c r="S14" s="10" t="inlineStr"/>
-      <c r="T14" s="10" t="inlineStr"/>
-      <c r="U14" s="10" t="inlineStr"/>
-      <c r="V14" s="10" t="inlineStr"/>
-      <c r="W14" s="11">
-        <f>IF(C14="","",IF(E14="","Type à choisir",IF(F14="","Objectif principal à choisir",IF(H14="","Intensité à choisir",IF(I14="","Format à choisir",IF(COUNTIF(M14:V14,"Cours co")+COUNTIF(M14:V14,"SGT")=0,"Aucun club coché",IF(E14=IF(COUNTIF(M14:V14,"Cours co")&gt;0,IF(COUNTIF(M14:V14,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X14" s="9" t="n"/>
+      <c r="N14" s="10" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n"/>
+      <c r="R14" s="10" t="n"/>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T14" s="10" t="n"/>
+      <c r="U14" s="10" t="n"/>
+      <c r="V14" s="10" t="n"/>
+      <c r="W14" s="10" t="n"/>
+      <c r="X14" s="10" t="n"/>
+      <c r="Y14" s="11">
+        <f>IF(C14="","",IF(E14="","Type à choisir",IF(H14="","Objectif principal à choisir",IF(J14="","Intensité à choisir",IF(K14="","Format à choisir",IF(COUNTA(O14:X14)=0,"Aucun club coché",IF(AND(F14&lt;&gt;"",COUNTIF($A$2:$A$81,F14)=0),"Même cours que : identifiant inconnu",IF(AND(F14&lt;&gt;"",F14=A14),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z14" s="9" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
@@ -1871,70 +1982,76 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F15" s="9" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr">
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I15" s="9" t="inlineStr">
+      <c r="K15" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J15" s="10" t="n">
+      <c r="L15" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K15" s="9" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Les Mills</t>
         </is>
       </c>
-      <c r="L15" s="10" t="n"/>
-      <c r="M15" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N15" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
+      <c r="N15" s="10" t="n"/>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
       <c r="Q15" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R15" s="10" t="inlineStr"/>
-      <c r="S15" s="10" t="inlineStr"/>
-      <c r="T15" s="10" t="inlineStr"/>
-      <c r="U15" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="V15" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W15" s="11">
-        <f>IF(C15="","",IF(E15="","Type à choisir",IF(F15="","Objectif principal à choisir",IF(H15="","Intensité à choisir",IF(I15="","Format à choisir",IF(COUNTIF(M15:V15,"Cours co")+COUNTIF(M15:V15,"SGT")=0,"Aucun club coché",IF(E15=IF(COUNTIF(M15:V15,"Cours co")&gt;0,IF(COUNTIF(M15:V15,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X15" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R15" s="10" t="n"/>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T15" s="10" t="n"/>
+      <c r="U15" s="10" t="n"/>
+      <c r="V15" s="10" t="n"/>
+      <c r="W15" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X15" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y15" s="11">
+        <f>IF(C15="","",IF(E15="","Type à choisir",IF(H15="","Objectif principal à choisir",IF(J15="","Intensité à choisir",IF(K15="","Format à choisir",IF(COUNTA(O15:X15)=0,"Aucun club coché",IF(AND(F15&lt;&gt;"",COUNTIF($A$2:$A$81,F15)=0),"Même cours que : identifiant inconnu",IF(AND(F15&lt;&gt;"",F15=A15),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
@@ -1958,50 +2075,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F16" s="9" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr"/>
+      <c r="G16" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G16" s="9" t="inlineStr"/>
-      <c r="H16" s="9" t="inlineStr">
+      <c r="I16" s="9" t="inlineStr"/>
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I16" s="9" t="inlineStr">
+      <c r="K16" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J16" s="10" t="n">
+      <c r="L16" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="K16" s="9" t="inlineStr">
+      <c r="M16" s="9" t="inlineStr">
         <is>
           <t>Les Mills</t>
         </is>
       </c>
-      <c r="L16" s="10" t="n"/>
-      <c r="M16" s="10" t="inlineStr"/>
-      <c r="N16" s="10" t="inlineStr"/>
-      <c r="O16" s="10" t="inlineStr"/>
-      <c r="P16" s="10" t="inlineStr"/>
-      <c r="Q16" s="10" t="inlineStr"/>
-      <c r="R16" s="10" t="inlineStr"/>
-      <c r="S16" s="10" t="inlineStr"/>
-      <c r="T16" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U16" s="10" t="inlineStr"/>
-      <c r="V16" s="10" t="inlineStr"/>
-      <c r="W16" s="11">
-        <f>IF(C16="","",IF(E16="","Type à choisir",IF(F16="","Objectif principal à choisir",IF(H16="","Intensité à choisir",IF(I16="","Format à choisir",IF(COUNTIF(M16:V16,"Cours co")+COUNTIF(M16:V16,"SGT")=0,"Aucun club coché",IF(E16=IF(COUNTIF(M16:V16,"Cours co")&gt;0,IF(COUNTIF(M16:V16,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X16" s="9" t="n"/>
+      <c r="N16" s="10" t="n"/>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n"/>
+      <c r="S16" s="10" t="n"/>
+      <c r="T16" s="10" t="n"/>
+      <c r="U16" s="10" t="n"/>
+      <c r="V16" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W16" s="10" t="n"/>
+      <c r="X16" s="10" t="n"/>
+      <c r="Y16" s="11">
+        <f>IF(C16="","",IF(E16="","Type à choisir",IF(H16="","Objectif principal à choisir",IF(J16="","Intensité à choisir",IF(K16="","Format à choisir",IF(COUNTA(O16:X16)=0,"Aucun club coché",IF(AND(F16&lt;&gt;"",COUNTIF($A$2:$A$81,F16)=0),"Même cours que : identifiant inconnu",IF(AND(F16&lt;&gt;"",F16=A16),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
@@ -2025,54 +2148,60 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F17" s="9" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t>Se détendre</t>
         </is>
       </c>
-      <c r="G17" s="9" t="inlineStr">
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I17" s="9" t="inlineStr">
+      <c r="K17" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J17" s="10" t="n">
+      <c r="L17" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K17" s="9" t="inlineStr">
+      <c r="M17" s="9" t="inlineStr">
         <is>
           <t>Les Mills</t>
         </is>
       </c>
-      <c r="L17" s="10" t="n"/>
-      <c r="M17" s="10" t="inlineStr"/>
-      <c r="N17" s="10" t="inlineStr"/>
-      <c r="O17" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P17" s="10" t="inlineStr"/>
-      <c r="Q17" s="10" t="inlineStr"/>
-      <c r="R17" s="10" t="inlineStr"/>
-      <c r="S17" s="10" t="inlineStr"/>
-      <c r="T17" s="10" t="inlineStr"/>
-      <c r="U17" s="10" t="inlineStr"/>
-      <c r="V17" s="10" t="inlineStr"/>
-      <c r="W17" s="11">
-        <f>IF(C17="","",IF(E17="","Type à choisir",IF(F17="","Objectif principal à choisir",IF(H17="","Intensité à choisir",IF(I17="","Format à choisir",IF(COUNTIF(M17:V17,"Cours co")+COUNTIF(M17:V17,"SGT")=0,"Aucun club coché",IF(E17=IF(COUNTIF(M17:V17,"Cours co")&gt;0,IF(COUNTIF(M17:V17,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X17" s="9" t="n"/>
+      <c r="N17" s="10" t="n"/>
+      <c r="O17" s="10" t="n"/>
+      <c r="P17" s="10" t="n"/>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R17" s="10" t="n"/>
+      <c r="S17" s="10" t="n"/>
+      <c r="T17" s="10" t="n"/>
+      <c r="U17" s="10" t="n"/>
+      <c r="V17" s="10" t="n"/>
+      <c r="W17" s="10" t="n"/>
+      <c r="X17" s="10" t="n"/>
+      <c r="Y17" s="11">
+        <f>IF(C17="","",IF(E17="","Type à choisir",IF(H17="","Objectif principal à choisir",IF(J17="","Intensité à choisir",IF(K17="","Format à choisir",IF(COUNTA(O17:X17)=0,"Aucun club coché",IF(AND(F17&lt;&gt;"",COUNTIF($A$2:$A$81,F17)=0),"Même cours que : identifiant inconnu",IF(AND(F17&lt;&gt;"",F17=A17),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z17" s="9" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
@@ -2096,54 +2225,60 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F18" s="9" t="inlineStr">
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G18" s="9" t="inlineStr"/>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr"/>
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I18" s="9" t="inlineStr">
+      <c r="K18" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J18" s="10" t="n">
+      <c r="L18" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="K18" s="9" t="inlineStr">
+      <c r="M18" s="9" t="inlineStr">
         <is>
           <t>Les Mills</t>
         </is>
       </c>
-      <c r="L18" s="10" t="n"/>
-      <c r="M18" s="10" t="inlineStr"/>
-      <c r="N18" s="10" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P18" s="10" t="inlineStr"/>
-      <c r="Q18" s="10" t="inlineStr"/>
-      <c r="R18" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr"/>
-      <c r="T18" s="10" t="inlineStr"/>
-      <c r="U18" s="10" t="inlineStr"/>
-      <c r="V18" s="10" t="inlineStr"/>
-      <c r="W18" s="11">
-        <f>IF(C18="","",IF(E18="","Type à choisir",IF(F18="","Objectif principal à choisir",IF(H18="","Intensité à choisir",IF(I18="","Format à choisir",IF(COUNTIF(M18:V18,"Cours co")+COUNTIF(M18:V18,"SGT")=0,"Aucun club coché",IF(E18=IF(COUNTIF(M18:V18,"Cours co")&gt;0,IF(COUNTIF(M18:V18,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X18" s="9" t="n"/>
+      <c r="N18" s="10" t="n"/>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R18" s="10" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U18" s="10" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="10" t="n"/>
+      <c r="X18" s="10" t="n"/>
+      <c r="Y18" s="11">
+        <f>IF(C18="","",IF(E18="","Type à choisir",IF(H18="","Objectif principal à choisir",IF(J18="","Intensité à choisir",IF(K18="","Format à choisir",IF(COUNTA(O18:X18)=0,"Aucun club coché",IF(AND(F18&lt;&gt;"",COUNTIF($A$2:$A$81,F18)=0),"Même cours que : identifiant inconnu",IF(AND(F18&lt;&gt;"",F18=A18),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z18" s="9" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
@@ -2167,50 +2302,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F19" s="9" t="inlineStr">
+      <c r="F19" s="9" t="inlineStr"/>
+      <c r="G19" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H19" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G19" s="9" t="inlineStr"/>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr"/>
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="K19" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J19" s="10" t="n">
+      <c r="L19" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="K19" s="9" t="inlineStr">
+      <c r="M19" s="9" t="inlineStr">
         <is>
           <t>Les Mills</t>
         </is>
       </c>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="inlineStr"/>
-      <c r="N19" s="10" t="inlineStr"/>
-      <c r="O19" s="10" t="inlineStr"/>
-      <c r="P19" s="10" t="inlineStr"/>
-      <c r="Q19" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R19" s="10" t="inlineStr"/>
-      <c r="S19" s="10" t="inlineStr"/>
-      <c r="T19" s="10" t="inlineStr"/>
-      <c r="U19" s="10" t="inlineStr"/>
-      <c r="V19" s="10" t="inlineStr"/>
-      <c r="W19" s="11">
-        <f>IF(C19="","",IF(E19="","Type à choisir",IF(F19="","Objectif principal à choisir",IF(H19="","Intensité à choisir",IF(I19="","Format à choisir",IF(COUNTIF(M19:V19,"Cours co")+COUNTIF(M19:V19,"SGT")=0,"Aucun club coché",IF(E19=IF(COUNTIF(M19:V19,"Cours co")&gt;0,IF(COUNTIF(M19:V19,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X19" s="9" t="n"/>
+      <c r="N19" s="10" t="n"/>
+      <c r="O19" s="10" t="n"/>
+      <c r="P19" s="10" t="n"/>
+      <c r="Q19" s="10" t="n"/>
+      <c r="R19" s="10" t="n"/>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T19" s="10" t="n"/>
+      <c r="U19" s="10" t="n"/>
+      <c r="V19" s="10" t="n"/>
+      <c r="W19" s="10" t="n"/>
+      <c r="X19" s="10" t="n"/>
+      <c r="Y19" s="11">
+        <f>IF(C19="","",IF(E19="","Type à choisir",IF(H19="","Objectif principal à choisir",IF(J19="","Intensité à choisir",IF(K19="","Format à choisir",IF(COUNTA(O19:X19)=0,"Aucun club coché",IF(AND(F19&lt;&gt;"",COUNTIF($A$2:$A$81,F19)=0),"Même cours que : identifiant inconnu",IF(AND(F19&lt;&gt;"",F19=A19),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z19" s="9" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -2234,50 +2375,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F20" s="9" t="inlineStr">
+      <c r="F20" s="9" t="inlineStr"/>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H20" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G20" s="9" t="inlineStr"/>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="I20" s="9" t="inlineStr"/>
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="K20" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J20" s="10" t="n">
+      <c r="L20" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K20" s="9" t="inlineStr">
+      <c r="M20" s="9" t="inlineStr">
         <is>
           <t>Les Mills</t>
         </is>
       </c>
-      <c r="L20" s="10" t="n"/>
-      <c r="M20" s="10" t="inlineStr"/>
-      <c r="N20" s="10" t="inlineStr"/>
-      <c r="O20" s="10" t="inlineStr"/>
-      <c r="P20" s="10" t="inlineStr"/>
-      <c r="Q20" s="10" t="inlineStr"/>
-      <c r="R20" s="10" t="inlineStr"/>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="T20" s="10" t="inlineStr"/>
-      <c r="U20" s="10" t="inlineStr"/>
-      <c r="V20" s="10" t="inlineStr"/>
-      <c r="W20" s="11">
-        <f>IF(C20="","",IF(E20="","Type à choisir",IF(F20="","Objectif principal à choisir",IF(H20="","Intensité à choisir",IF(I20="","Format à choisir",IF(COUNTIF(M20:V20,"Cours co")+COUNTIF(M20:V20,"SGT")=0,"Aucun club coché",IF(E20=IF(COUNTIF(M20:V20,"Cours co")&gt;0,IF(COUNTIF(M20:V20,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X20" s="9" t="n"/>
+      <c r="N20" s="10" t="n"/>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="10" t="n"/>
+      <c r="R20" s="10" t="n"/>
+      <c r="S20" s="10" t="n"/>
+      <c r="T20" s="10" t="n"/>
+      <c r="U20" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V20" s="10" t="n"/>
+      <c r="W20" s="10" t="n"/>
+      <c r="X20" s="10" t="n"/>
+      <c r="Y20" s="11">
+        <f>IF(C20="","",IF(E20="","Type à choisir",IF(H20="","Objectif principal à choisir",IF(J20="","Intensité à choisir",IF(K20="","Format à choisir",IF(COUNTA(O20:X20)=0,"Aucun club coché",IF(AND(F20&lt;&gt;"",COUNTIF($A$2:$A$81,F20)=0),"Même cours que : identifiant inconnu",IF(AND(F20&lt;&gt;"",F20=A20),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z20" s="9" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
@@ -2301,62 +2448,68 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F21" s="9" t="inlineStr">
+      <c r="F21" s="9" t="inlineStr"/>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="I21" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="H21" s="9" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I21" s="9" t="inlineStr">
+      <c r="K21" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J21" s="10" t="n">
+      <c r="L21" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="M21" s="9" t="inlineStr">
         <is>
           <t>Les Mills</t>
         </is>
       </c>
-      <c r="L21" s="10" t="n"/>
-      <c r="M21" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N21" s="10" t="inlineStr"/>
-      <c r="O21" s="10" t="inlineStr"/>
-      <c r="P21" s="10" t="inlineStr"/>
-      <c r="Q21" s="10" t="inlineStr"/>
-      <c r="R21" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr"/>
-      <c r="T21" s="10" t="inlineStr"/>
-      <c r="U21" s="10" t="inlineStr"/>
-      <c r="V21" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W21" s="11">
-        <f>IF(C21="","",IF(E21="","Type à choisir",IF(F21="","Objectif principal à choisir",IF(H21="","Intensité à choisir",IF(I21="","Format à choisir",IF(COUNTIF(M21:V21,"Cours co")+COUNTIF(M21:V21,"SGT")=0,"Aucun club coché",IF(E21=IF(COUNTIF(M21:V21,"Cours co")&gt;0,IF(COUNTIF(M21:V21,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X21" s="9" t="n"/>
+      <c r="N21" s="10" t="n"/>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="n"/>
+      <c r="Q21" s="10" t="n"/>
+      <c r="R21" s="10" t="n"/>
+      <c r="S21" s="10" t="n"/>
+      <c r="T21" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U21" s="10" t="n"/>
+      <c r="V21" s="10" t="n"/>
+      <c r="W21" s="10" t="n"/>
+      <c r="X21" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y21" s="11">
+        <f>IF(C21="","",IF(E21="","Type à choisir",IF(H21="","Objectif principal à choisir",IF(J21="","Intensité à choisir",IF(K21="","Format à choisir",IF(COUNTA(O21:X21)=0,"Aucun club coché",IF(AND(F21&lt;&gt;"",COUNTIF($A$2:$A$81,F21)=0),"Même cours que : identifiant inconnu",IF(AND(F21&lt;&gt;"",F21=A21),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z21" s="9" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -2380,58 +2533,64 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F22" s="9" t="inlineStr">
+      <c r="F22" s="9" t="inlineStr"/>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>Se dépasser</t>
         </is>
       </c>
-      <c r="G22" s="9" t="inlineStr"/>
-      <c r="H22" s="9" t="inlineStr">
+      <c r="I22" s="9" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I22" s="9" t="inlineStr">
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J22" s="10" t="n">
+      <c r="L22" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K22" s="9" t="inlineStr">
+      <c r="M22" s="9" t="inlineStr">
         <is>
           <t>Les Mills + Hyrox</t>
         </is>
       </c>
-      <c r="L22" s="10" t="n"/>
-      <c r="M22" s="10" t="inlineStr"/>
-      <c r="N22" s="10" t="inlineStr"/>
-      <c r="O22" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P22" s="10" t="inlineStr"/>
+      <c r="N22" s="10" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="10" t="n"/>
       <c r="Q22" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R22" s="10" t="inlineStr"/>
-      <c r="S22" s="10" t="inlineStr"/>
-      <c r="T22" s="10" t="inlineStr"/>
-      <c r="U22" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="V22" s="10" t="inlineStr"/>
-      <c r="W22" s="11">
-        <f>IF(C22="","",IF(E22="","Type à choisir",IF(F22="","Objectif principal à choisir",IF(H22="","Intensité à choisir",IF(I22="","Format à choisir",IF(COUNTIF(M22:V22,"Cours co")+COUNTIF(M22:V22,"SGT")=0,"Aucun club coché",IF(E22=IF(COUNTIF(M22:V22,"Cours co")&gt;0,IF(COUNTIF(M22:V22,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X22" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R22" s="10" t="n"/>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T22" s="10" t="n"/>
+      <c r="U22" s="10" t="n"/>
+      <c r="V22" s="10" t="n"/>
+      <c r="W22" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X22" s="10" t="n"/>
+      <c r="Y22" s="11">
+        <f>IF(C22="","",IF(E22="","Type à choisir",IF(H22="","Objectif principal à choisir",IF(J22="","Intensité à choisir",IF(K22="","Format à choisir",IF(COUNTA(O22:X22)=0,"Aucun club coché",IF(AND(F22&lt;&gt;"",COUNTIF($A$2:$A$81,F22)=0),"Même cours que : identifiant inconnu",IF(AND(F22&lt;&gt;"",F22=A22),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z22" s="9" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
@@ -2455,50 +2614,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F23" s="9" t="inlineStr">
+      <c r="F23" s="9" t="inlineStr"/>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>Se dépasser</t>
         </is>
       </c>
-      <c r="G23" s="9" t="inlineStr"/>
-      <c r="H23" s="9" t="inlineStr">
+      <c r="I23" s="9" t="inlineStr"/>
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I23" s="9" t="inlineStr">
+      <c r="K23" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J23" s="10" t="n">
+      <c r="L23" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K23" s="9" t="inlineStr">
+      <c r="M23" s="9" t="inlineStr">
         <is>
           <t>Les Mills</t>
         </is>
       </c>
-      <c r="L23" s="10" t="n"/>
-      <c r="M23" s="10" t="inlineStr"/>
-      <c r="N23" s="10" t="inlineStr"/>
-      <c r="O23" s="10" t="inlineStr"/>
-      <c r="P23" s="10" t="inlineStr"/>
-      <c r="Q23" s="10" t="inlineStr"/>
-      <c r="R23" s="10" t="inlineStr"/>
-      <c r="S23" s="10" t="inlineStr"/>
-      <c r="T23" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U23" s="10" t="inlineStr"/>
-      <c r="V23" s="10" t="inlineStr"/>
-      <c r="W23" s="11">
-        <f>IF(C23="","",IF(E23="","Type à choisir",IF(F23="","Objectif principal à choisir",IF(H23="","Intensité à choisir",IF(I23="","Format à choisir",IF(COUNTIF(M23:V23,"Cours co")+COUNTIF(M23:V23,"SGT")=0,"Aucun club coché",IF(E23=IF(COUNTIF(M23:V23,"Cours co")&gt;0,IF(COUNTIF(M23:V23,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X23" s="9" t="n"/>
+      <c r="N23" s="10" t="n"/>
+      <c r="O23" s="10" t="n"/>
+      <c r="P23" s="10" t="n"/>
+      <c r="Q23" s="10" t="n"/>
+      <c r="R23" s="10" t="n"/>
+      <c r="S23" s="10" t="n"/>
+      <c r="T23" s="10" t="n"/>
+      <c r="U23" s="10" t="n"/>
+      <c r="V23" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W23" s="10" t="n"/>
+      <c r="X23" s="10" t="n"/>
+      <c r="Y23" s="11">
+        <f>IF(C23="","",IF(E23="","Type à choisir",IF(H23="","Objectif principal à choisir",IF(J23="","Intensité à choisir",IF(K23="","Format à choisir",IF(COUNTA(O23:X23)=0,"Aucun club coché",IF(AND(F23&lt;&gt;"",COUNTIF($A$2:$A$81,F23)=0),"Même cours que : identifiant inconnu",IF(AND(F23&lt;&gt;"",F23=A23),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z23" s="9" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
@@ -2522,58 +2687,64 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F24" s="9" t="inlineStr">
+      <c r="F24" s="9" t="inlineStr"/>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>Aqua</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G24" s="9" t="inlineStr"/>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I24" s="9" t="inlineStr">
+      <c r="K24" s="9" t="inlineStr">
         <is>
           <t>Aqua</t>
         </is>
       </c>
-      <c r="J24" s="10" t="n">
+      <c r="L24" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K24" s="9" t="inlineStr">
+      <c r="M24" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L24" s="10" t="n"/>
-      <c r="M24" s="10" t="inlineStr"/>
-      <c r="N24" s="10" t="inlineStr"/>
-      <c r="O24" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P24" s="10" t="inlineStr"/>
-      <c r="Q24" s="10" t="inlineStr"/>
-      <c r="R24" s="10" t="inlineStr"/>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="T24" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U24" s="10" t="inlineStr"/>
-      <c r="V24" s="10" t="inlineStr"/>
-      <c r="W24" s="11">
-        <f>IF(C24="","",IF(E24="","Type à choisir",IF(F24="","Objectif principal à choisir",IF(H24="","Intensité à choisir",IF(I24="","Format à choisir",IF(COUNTIF(M24:V24,"Cours co")+COUNTIF(M24:V24,"SGT")=0,"Aucun club coché",IF(E24=IF(COUNTIF(M24:V24,"Cours co")&gt;0,IF(COUNTIF(M24:V24,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X24" s="9" t="n"/>
+      <c r="N24" s="10" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="10" t="n"/>
+      <c r="Q24" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R24" s="10" t="n"/>
+      <c r="S24" s="10" t="n"/>
+      <c r="T24" s="10" t="n"/>
+      <c r="U24" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V24" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W24" s="10" t="n"/>
+      <c r="X24" s="10" t="n"/>
+      <c r="Y24" s="11">
+        <f>IF(C24="","",IF(E24="","Type à choisir",IF(H24="","Objectif principal à choisir",IF(J24="","Intensité à choisir",IF(K24="","Format à choisir",IF(COUNTA(O24:X24)=0,"Aucun club coché",IF(AND(F24&lt;&gt;"",COUNTIF($A$2:$A$81,F24)=0),"Même cours que : identifiant inconnu",IF(AND(F24&lt;&gt;"",F24=A24),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
@@ -2597,58 +2768,64 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F25" s="9" t="inlineStr">
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr">
+        <is>
+          <t>Aqua</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G25" s="9" t="inlineStr"/>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr"/>
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I25" s="9" t="inlineStr">
+      <c r="K25" s="9" t="inlineStr">
         <is>
           <t>Aqua</t>
         </is>
       </c>
-      <c r="J25" s="10" t="n">
+      <c r="L25" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K25" s="9" t="inlineStr">
+      <c r="M25" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L25" s="10" t="n"/>
-      <c r="M25" s="10" t="inlineStr"/>
-      <c r="N25" s="10" t="inlineStr"/>
-      <c r="O25" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P25" s="10" t="inlineStr"/>
-      <c r="Q25" s="10" t="inlineStr"/>
-      <c r="R25" s="10" t="inlineStr"/>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="T25" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U25" s="10" t="inlineStr"/>
-      <c r="V25" s="10" t="inlineStr"/>
-      <c r="W25" s="11">
-        <f>IF(C25="","",IF(E25="","Type à choisir",IF(F25="","Objectif principal à choisir",IF(H25="","Intensité à choisir",IF(I25="","Format à choisir",IF(COUNTIF(M25:V25,"Cours co")+COUNTIF(M25:V25,"SGT")=0,"Aucun club coché",IF(E25=IF(COUNTIF(M25:V25,"Cours co")&gt;0,IF(COUNTIF(M25:V25,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X25" s="9" t="n"/>
+      <c r="N25" s="10" t="n"/>
+      <c r="O25" s="10" t="n"/>
+      <c r="P25" s="10" t="n"/>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="n"/>
+      <c r="S25" s="10" t="n"/>
+      <c r="T25" s="10" t="n"/>
+      <c r="U25" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V25" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W25" s="10" t="n"/>
+      <c r="X25" s="10" t="n"/>
+      <c r="Y25" s="11">
+        <f>IF(C25="","",IF(E25="","Type à choisir",IF(H25="","Objectif principal à choisir",IF(J25="","Intensité à choisir",IF(K25="","Format à choisir",IF(COUNTA(O25:X25)=0,"Aucun club coché",IF(AND(F25&lt;&gt;"",COUNTIF($A$2:$A$81,F25)=0),"Même cours que : identifiant inconnu",IF(AND(F25&lt;&gt;"",F25=A25),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z25" s="9" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
@@ -2672,50 +2849,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F26" s="9" t="inlineStr">
+      <c r="F26" s="9" t="inlineStr"/>
+      <c r="G26" s="9" t="inlineStr">
+        <is>
+          <t>Aqua</t>
+        </is>
+      </c>
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>Danser</t>
         </is>
       </c>
-      <c r="G26" s="9" t="inlineStr"/>
-      <c r="H26" s="9" t="inlineStr">
+      <c r="I26" s="9" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I26" s="9" t="inlineStr">
+      <c r="K26" s="9" t="inlineStr">
         <is>
           <t>Aqua</t>
         </is>
       </c>
-      <c r="J26" s="10" t="n">
+      <c r="L26" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K26" s="9" t="inlineStr">
+      <c r="M26" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L26" s="10" t="n"/>
-      <c r="M26" s="10" t="inlineStr"/>
-      <c r="N26" s="10" t="inlineStr"/>
-      <c r="O26" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P26" s="10" t="inlineStr"/>
-      <c r="Q26" s="10" t="inlineStr"/>
-      <c r="R26" s="10" t="inlineStr"/>
-      <c r="S26" s="10" t="inlineStr"/>
-      <c r="T26" s="10" t="inlineStr"/>
-      <c r="U26" s="10" t="inlineStr"/>
-      <c r="V26" s="10" t="inlineStr"/>
-      <c r="W26" s="11">
-        <f>IF(C26="","",IF(E26="","Type à choisir",IF(F26="","Objectif principal à choisir",IF(H26="","Intensité à choisir",IF(I26="","Format à choisir",IF(COUNTIF(M26:V26,"Cours co")+COUNTIF(M26:V26,"SGT")=0,"Aucun club coché",IF(E26=IF(COUNTIF(M26:V26,"Cours co")&gt;0,IF(COUNTIF(M26:V26,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X26" s="9" t="n"/>
+      <c r="N26" s="10" t="n"/>
+      <c r="O26" s="10" t="n"/>
+      <c r="P26" s="10" t="n"/>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="n"/>
+      <c r="S26" s="10" t="n"/>
+      <c r="T26" s="10" t="n"/>
+      <c r="U26" s="10" t="n"/>
+      <c r="V26" s="10" t="n"/>
+      <c r="W26" s="10" t="n"/>
+      <c r="X26" s="10" t="n"/>
+      <c r="Y26" s="11">
+        <f>IF(C26="","",IF(E26="","Type à choisir",IF(H26="","Objectif principal à choisir",IF(J26="","Intensité à choisir",IF(K26="","Format à choisir",IF(COUNTA(O26:X26)=0,"Aucun club coché",IF(AND(F26&lt;&gt;"",COUNTIF($A$2:$A$81,F26)=0),"Même cours que : identifiant inconnu",IF(AND(F26&lt;&gt;"",F26=A26),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z26" s="9" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
@@ -2739,50 +2922,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F27" s="9" t="inlineStr">
+      <c r="F27" s="9" t="inlineStr"/>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>Aqua</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G27" s="9" t="inlineStr"/>
-      <c r="H27" s="9" t="inlineStr">
+      <c r="I27" s="9" t="inlineStr"/>
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I27" s="9" t="inlineStr">
+      <c r="K27" s="9" t="inlineStr">
         <is>
           <t>Aqua</t>
         </is>
       </c>
-      <c r="J27" s="10" t="n">
+      <c r="L27" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K27" s="9" t="inlineStr">
+      <c r="M27" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L27" s="10" t="n"/>
-      <c r="M27" s="10" t="inlineStr"/>
-      <c r="N27" s="10" t="inlineStr"/>
-      <c r="O27" s="10" t="inlineStr"/>
-      <c r="P27" s="10" t="inlineStr"/>
-      <c r="Q27" s="10" t="inlineStr"/>
-      <c r="R27" s="10" t="inlineStr"/>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="T27" s="10" t="inlineStr"/>
-      <c r="U27" s="10" t="inlineStr"/>
-      <c r="V27" s="10" t="inlineStr"/>
-      <c r="W27" s="11">
-        <f>IF(C27="","",IF(E27="","Type à choisir",IF(F27="","Objectif principal à choisir",IF(H27="","Intensité à choisir",IF(I27="","Format à choisir",IF(COUNTIF(M27:V27,"Cours co")+COUNTIF(M27:V27,"SGT")=0,"Aucun club coché",IF(E27=IF(COUNTIF(M27:V27,"Cours co")&gt;0,IF(COUNTIF(M27:V27,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X27" s="9" t="n"/>
+      <c r="N27" s="10" t="n"/>
+      <c r="O27" s="10" t="n"/>
+      <c r="P27" s="10" t="n"/>
+      <c r="Q27" s="10" t="n"/>
+      <c r="R27" s="10" t="n"/>
+      <c r="S27" s="10" t="n"/>
+      <c r="T27" s="10" t="n"/>
+      <c r="U27" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V27" s="10" t="n"/>
+      <c r="W27" s="10" t="n"/>
+      <c r="X27" s="10" t="n"/>
+      <c r="Y27" s="11">
+        <f>IF(C27="","",IF(E27="","Type à choisir",IF(H27="","Objectif principal à choisir",IF(J27="","Intensité à choisir",IF(K27="","Format à choisir",IF(COUNTA(O27:X27)=0,"Aucun club coché",IF(AND(F27&lt;&gt;"",COUNTIF($A$2:$A$81,F27)=0),"Même cours que : identifiant inconnu",IF(AND(F27&lt;&gt;"",F27=A27),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z27" s="9" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
@@ -2806,50 +2995,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F28" s="9" t="inlineStr">
+      <c r="F28" s="9" t="inlineStr"/>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H28" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G28" s="9" t="inlineStr"/>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr"/>
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I28" s="9" t="inlineStr">
+      <c r="K28" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J28" s="10" t="n">
+      <c r="L28" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K28" s="9" t="inlineStr">
+      <c r="M28" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L28" s="10" t="n"/>
-      <c r="M28" s="10" t="inlineStr"/>
-      <c r="N28" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="O28" s="10" t="inlineStr"/>
-      <c r="P28" s="10" t="inlineStr"/>
-      <c r="Q28" s="10" t="inlineStr"/>
-      <c r="R28" s="10" t="inlineStr"/>
-      <c r="S28" s="10" t="inlineStr"/>
-      <c r="T28" s="10" t="inlineStr"/>
-      <c r="U28" s="10" t="inlineStr"/>
-      <c r="V28" s="10" t="inlineStr"/>
-      <c r="W28" s="11">
-        <f>IF(C28="","",IF(E28="","Type à choisir",IF(F28="","Objectif principal à choisir",IF(H28="","Intensité à choisir",IF(I28="","Format à choisir",IF(COUNTIF(M28:V28,"Cours co")+COUNTIF(M28:V28,"SGT")=0,"Aucun club coché",IF(E28=IF(COUNTIF(M28:V28,"Cours co")&gt;0,IF(COUNTIF(M28:V28,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X28" s="9" t="n"/>
+      <c r="N28" s="10" t="n"/>
+      <c r="O28" s="10" t="n"/>
+      <c r="P28" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q28" s="10" t="n"/>
+      <c r="R28" s="10" t="n"/>
+      <c r="S28" s="10" t="n"/>
+      <c r="T28" s="10" t="n"/>
+      <c r="U28" s="10" t="n"/>
+      <c r="V28" s="10" t="n"/>
+      <c r="W28" s="10" t="n"/>
+      <c r="X28" s="10" t="n"/>
+      <c r="Y28" s="11">
+        <f>IF(C28="","",IF(E28="","Type à choisir",IF(H28="","Objectif principal à choisir",IF(J28="","Intensité à choisir",IF(K28="","Format à choisir",IF(COUNTA(O28:X28)=0,"Aucun club coché",IF(AND(F28&lt;&gt;"",COUNTIF($A$2:$A$81,F28)=0),"Même cours que : identifiant inconnu",IF(AND(F28&lt;&gt;"",F28=A28),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z28" s="9" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
@@ -2873,50 +3068,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F29" s="9" t="inlineStr">
+      <c r="F29" s="9" t="inlineStr"/>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G29" s="9" t="inlineStr"/>
-      <c r="H29" s="9" t="inlineStr">
+      <c r="I29" s="9" t="inlineStr"/>
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I29" s="9" t="inlineStr">
+      <c r="K29" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J29" s="10" t="n">
+      <c r="L29" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K29" s="9" t="inlineStr">
+      <c r="M29" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L29" s="10" t="n"/>
-      <c r="M29" s="10" t="inlineStr"/>
-      <c r="N29" s="10" t="inlineStr"/>
-      <c r="O29" s="10" t="inlineStr"/>
-      <c r="P29" s="10" t="inlineStr"/>
-      <c r="Q29" s="10" t="inlineStr"/>
-      <c r="R29" s="10" t="inlineStr"/>
-      <c r="S29" s="10" t="inlineStr"/>
-      <c r="T29" s="10" t="inlineStr"/>
-      <c r="U29" s="10" t="inlineStr"/>
-      <c r="V29" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W29" s="11">
-        <f>IF(C29="","",IF(E29="","Type à choisir",IF(F29="","Objectif principal à choisir",IF(H29="","Intensité à choisir",IF(I29="","Format à choisir",IF(COUNTIF(M29:V29,"Cours co")+COUNTIF(M29:V29,"SGT")=0,"Aucun club coché",IF(E29=IF(COUNTIF(M29:V29,"Cours co")&gt;0,IF(COUNTIF(M29:V29,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X29" s="9" t="n"/>
+      <c r="N29" s="10" t="n"/>
+      <c r="O29" s="10" t="n"/>
+      <c r="P29" s="10" t="n"/>
+      <c r="Q29" s="10" t="n"/>
+      <c r="R29" s="10" t="n"/>
+      <c r="S29" s="10" t="n"/>
+      <c r="T29" s="10" t="n"/>
+      <c r="U29" s="10" t="n"/>
+      <c r="V29" s="10" t="n"/>
+      <c r="W29" s="10" t="n"/>
+      <c r="X29" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y29" s="11">
+        <f>IF(C29="","",IF(E29="","Type à choisir",IF(H29="","Objectif principal à choisir",IF(J29="","Intensité à choisir",IF(K29="","Format à choisir",IF(COUNTA(O29:X29)=0,"Aucun club coché",IF(AND(F29&lt;&gt;"",COUNTIF($A$2:$A$81,F29)=0),"Même cours que : identifiant inconnu",IF(AND(F29&lt;&gt;"",F29=A29),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z29" s="9" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
@@ -2940,58 +3141,64 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F30" s="9" t="inlineStr">
+      <c r="F30" s="9" t="inlineStr"/>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G30" s="9" t="inlineStr"/>
-      <c r="H30" s="9" t="inlineStr">
+      <c r="I30" s="9" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I30" s="9" t="inlineStr">
+      <c r="K30" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J30" s="10" t="n">
+      <c r="L30" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="K30" s="9" t="inlineStr">
+      <c r="M30" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L30" s="10" t="n"/>
-      <c r="M30" s="10" t="inlineStr"/>
-      <c r="N30" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="O30" s="10" t="inlineStr"/>
-      <c r="P30" s="10" t="inlineStr"/>
-      <c r="Q30" s="10" t="inlineStr"/>
-      <c r="R30" s="10" t="inlineStr"/>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="T30" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U30" s="10" t="inlineStr"/>
-      <c r="V30" s="10" t="inlineStr"/>
-      <c r="W30" s="11">
-        <f>IF(C30="","",IF(E30="","Type à choisir",IF(F30="","Objectif principal à choisir",IF(H30="","Intensité à choisir",IF(I30="","Format à choisir",IF(COUNTIF(M30:V30,"Cours co")+COUNTIF(M30:V30,"SGT")=0,"Aucun club coché",IF(E30=IF(COUNTIF(M30:V30,"Cours co")&gt;0,IF(COUNTIF(M30:V30,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X30" s="9" t="n"/>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="10" t="n"/>
+      <c r="S30" s="10" t="n"/>
+      <c r="T30" s="10" t="n"/>
+      <c r="U30" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V30" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="10" t="n"/>
+      <c r="Y30" s="11">
+        <f>IF(C30="","",IF(E30="","Type à choisir",IF(H30="","Objectif principal à choisir",IF(J30="","Intensité à choisir",IF(K30="","Format à choisir",IF(COUNTA(O30:X30)=0,"Aucun club coché",IF(AND(F30&lt;&gt;"",COUNTIF($A$2:$A$81,F30)=0),"Même cours que : identifiant inconnu",IF(AND(F30&lt;&gt;"",F30=A30),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z30" s="9" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
@@ -3015,50 +3222,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F31" s="9" t="inlineStr">
+      <c r="F31" s="9" t="inlineStr"/>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G31" s="9" t="inlineStr"/>
-      <c r="H31" s="9" t="inlineStr">
+      <c r="I31" s="9" t="inlineStr"/>
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I31" s="9" t="inlineStr">
+      <c r="K31" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J31" s="10" t="n">
+      <c r="L31" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K31" s="9" t="inlineStr">
+      <c r="M31" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="10" t="inlineStr"/>
-      <c r="N31" s="10" t="inlineStr"/>
-      <c r="O31" s="10" t="inlineStr"/>
-      <c r="P31" s="10" t="inlineStr"/>
-      <c r="Q31" s="10" t="inlineStr"/>
-      <c r="R31" s="10" t="inlineStr"/>
-      <c r="S31" s="10" t="inlineStr"/>
-      <c r="T31" s="10" t="inlineStr"/>
-      <c r="U31" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="V31" s="10" t="inlineStr"/>
-      <c r="W31" s="11">
-        <f>IF(C31="","",IF(E31="","Type à choisir",IF(F31="","Objectif principal à choisir",IF(H31="","Intensité à choisir",IF(I31="","Format à choisir",IF(COUNTIF(M31:V31,"Cours co")+COUNTIF(M31:V31,"SGT")=0,"Aucun club coché",IF(E31=IF(COUNTIF(M31:V31,"Cours co")&gt;0,IF(COUNTIF(M31:V31,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X31" s="9" t="n"/>
+      <c r="N31" s="10" t="n"/>
+      <c r="O31" s="10" t="n"/>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n"/>
+      <c r="R31" s="10" t="n"/>
+      <c r="S31" s="10" t="n"/>
+      <c r="T31" s="10" t="n"/>
+      <c r="U31" s="10" t="n"/>
+      <c r="V31" s="10" t="n"/>
+      <c r="W31" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X31" s="10" t="n"/>
+      <c r="Y31" s="11">
+        <f>IF(C31="","",IF(E31="","Type à choisir",IF(H31="","Objectif principal à choisir",IF(J31="","Intensité à choisir",IF(K31="","Format à choisir",IF(COUNTA(O31:X31)=0,"Aucun club coché",IF(AND(F31&lt;&gt;"",COUNTIF($A$2:$A$81,F31)=0),"Même cours que : identifiant inconnu",IF(AND(F31&lt;&gt;"",F31=A31),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z31" s="9" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
@@ -3082,50 +3295,56 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F32" s="9" t="inlineStr">
+      <c r="F32" s="9" t="inlineStr"/>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr">
         <is>
           <t>Se renforcer et sculpter</t>
         </is>
       </c>
-      <c r="G32" s="9" t="inlineStr"/>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="I32" s="9" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="K32" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J32" s="10" t="n">
+      <c r="L32" s="10" t="n">
         <v>30</v>
       </c>
-      <c r="K32" s="9" t="inlineStr">
+      <c r="M32" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L32" s="10" t="n"/>
-      <c r="M32" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N32" s="10" t="inlineStr"/>
-      <c r="O32" s="10" t="inlineStr"/>
-      <c r="P32" s="10" t="inlineStr"/>
-      <c r="Q32" s="10" t="inlineStr"/>
-      <c r="R32" s="10" t="inlineStr"/>
-      <c r="S32" s="10" t="inlineStr"/>
-      <c r="T32" s="10" t="inlineStr"/>
-      <c r="U32" s="10" t="inlineStr"/>
-      <c r="V32" s="10" t="inlineStr"/>
-      <c r="W32" s="11">
-        <f>IF(C32="","",IF(E32="","Type à choisir",IF(F32="","Objectif principal à choisir",IF(H32="","Intensité à choisir",IF(I32="","Format à choisir",IF(COUNTIF(M32:V32,"Cours co")+COUNTIF(M32:V32,"SGT")=0,"Aucun club coché",IF(E32=IF(COUNTIF(M32:V32,"Cours co")&gt;0,IF(COUNTIF(M32:V32,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X32" s="9" t="n"/>
+      <c r="N32" s="10" t="n"/>
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n"/>
+      <c r="S32" s="10" t="n"/>
+      <c r="T32" s="10" t="n"/>
+      <c r="U32" s="10" t="n"/>
+      <c r="V32" s="10" t="n"/>
+      <c r="W32" s="10" t="n"/>
+      <c r="X32" s="10" t="n"/>
+      <c r="Y32" s="11">
+        <f>IF(C32="","",IF(E32="","Type à choisir",IF(H32="","Objectif principal à choisir",IF(J32="","Intensité à choisir",IF(K32="","Format à choisir",IF(COUNTA(O32:X32)=0,"Aucun club coché",IF(AND(F32&lt;&gt;"",COUNTIF($A$2:$A$81,F32)=0),"Même cours que : identifiant inconnu",IF(AND(F32&lt;&gt;"",F32=A32),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z32" s="9" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
@@ -3146,80 +3365,82 @@
       </c>
       <c r="E33" s="9" t="inlineStr">
         <is>
-          <t>Les deux selon le club</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
+          <t>Cours co</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr"/>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G33" s="9" t="inlineStr"/>
-      <c r="H33" s="9" t="inlineStr">
+      <c r="I33" s="9" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I33" s="9" t="inlineStr">
+      <c r="K33" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J33" s="10" t="n">
+      <c r="L33" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K33" s="9" t="inlineStr">
+      <c r="M33" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L33" s="10" t="n"/>
-      <c r="M33" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N33" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
+      <c r="N33" s="10" t="n"/>
       <c r="O33" s="10" t="inlineStr">
         <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="P33" s="10" t="inlineStr"/>
-      <c r="Q33" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R33" s="10" t="inlineStr"/>
-      <c r="S33" s="10" t="inlineStr"/>
-      <c r="T33" s="10" t="inlineStr"/>
-      <c r="U33" s="10" t="inlineStr"/>
-      <c r="V33" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W33" s="11">
-        <f>IF(C33="","",IF(E33="","Type à choisir",IF(F33="","Objectif principal à choisir",IF(H33="","Intensité à choisir",IF(I33="","Format à choisir",IF(COUNTIF(M33:V33,"Cours co")+COUNTIF(M33:V33,"SGT")=0,"Aucun club coché",IF(E33=IF(COUNTIF(M33:V33,"Cours co")&gt;0,IF(COUNTIF(M33:V33,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X33" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="10" t="n"/>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T33" s="10" t="n"/>
+      <c r="U33" s="10" t="n"/>
+      <c r="V33" s="10" t="n"/>
+      <c r="W33" s="10" t="n"/>
+      <c r="X33" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y33" s="11">
+        <f>IF(C33="","",IF(E33="","Type à choisir",IF(H33="","Objectif principal à choisir",IF(J33="","Intensité à choisir",IF(K33="","Format à choisir",IF(COUNTA(O33:X33)=0,"Aucun club coché",IF(AND(F33&lt;&gt;"",COUNTIF($A$2:$A$81,F33)=0),"Même cours que : identifiant inconnu",IF(AND(F33&lt;&gt;"",F33=A33),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z33" s="9" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>circuit-training</t>
+          <t>hiit-sgt</t>
         </is>
       </c>
       <c r="B34" s="9" t="n"/>
       <c r="C34" s="9" t="inlineStr">
         <is>
-          <t>Circuit Training</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
@@ -3229,64 +3450,74 @@
       </c>
       <c r="E34" s="9" t="inlineStr">
         <is>
-          <t>Cours co</t>
+          <t>SGT</t>
         </is>
       </c>
       <c r="F34" s="9" t="inlineStr">
         <is>
+          <t>hiit</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr">
+        <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G34" s="9" t="inlineStr"/>
-      <c r="H34" s="9" t="inlineStr">
+      <c r="I34" s="9" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>Salle</t>
-        </is>
-      </c>
-      <c r="J34" s="10" t="n">
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>Petit groupe</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K34" s="9" t="inlineStr">
+      <c r="M34" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L34" s="10" t="n"/>
-      <c r="M34" s="10" t="inlineStr"/>
-      <c r="N34" s="10" t="inlineStr"/>
-      <c r="O34" s="10" t="inlineStr"/>
-      <c r="P34" s="10" t="inlineStr"/>
-      <c r="Q34" s="10" t="inlineStr"/>
-      <c r="R34" s="10" t="inlineStr"/>
-      <c r="S34" s="10" t="inlineStr"/>
-      <c r="T34" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U34" s="10" t="inlineStr"/>
-      <c r="V34" s="10" t="inlineStr"/>
-      <c r="W34" s="11">
-        <f>IF(C34="","",IF(E34="","Type à choisir",IF(F34="","Objectif principal à choisir",IF(H34="","Intensité à choisir",IF(I34="","Format à choisir",IF(COUNTIF(M34:V34,"Cours co")+COUNTIF(M34:V34,"SGT")=0,"Aucun club coché",IF(E34=IF(COUNTIF(M34:V34,"Cours co")&gt;0,IF(COUNTIF(M34:V34,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X34" s="9" t="n"/>
+      <c r="N34" s="10" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="10" t="n"/>
+      <c r="Q34" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R34" s="10" t="n"/>
+      <c r="S34" s="10" t="n"/>
+      <c r="T34" s="10" t="n"/>
+      <c r="U34" s="10" t="n"/>
+      <c r="V34" s="10" t="n"/>
+      <c r="W34" s="10" t="n"/>
+      <c r="X34" s="10" t="n"/>
+      <c r="Y34" s="11">
+        <f>IF(C34="","",IF(E34="","Type à choisir",IF(H34="","Objectif principal à choisir",IF(J34="","Intensité à choisir",IF(K34="","Format à choisir",IF(COUNTA(O34:X34)=0,"Aucun club coché",IF(AND(F34&lt;&gt;"",COUNTIF($A$2:$A$81,F34)=0),"Même cours que : identifiant inconnu",IF(AND(F34&lt;&gt;"",F34=A34),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z34" s="9" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>cross-training</t>
+          <t>circuit-training</t>
         </is>
       </c>
       <c r="B35" s="9" t="n"/>
       <c r="C35" s="9" t="inlineStr">
         <is>
-          <t>Cross Training</t>
+          <t>Circuit Training</t>
         </is>
       </c>
       <c r="D35" s="9" t="inlineStr">
@@ -3296,72 +3527,70 @@
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>Les deux selon le club</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
+          <t>Cours co</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr"/>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G35" s="9" t="inlineStr"/>
-      <c r="H35" s="9" t="inlineStr">
+      <c r="I35" s="9" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I35" s="9" t="inlineStr">
+      <c r="K35" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J35" s="10" t="n">
+      <c r="L35" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K35" s="9" t="inlineStr">
+      <c r="M35" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L35" s="10" t="n"/>
-      <c r="M35" s="10" t="inlineStr"/>
-      <c r="N35" s="10" t="inlineStr"/>
-      <c r="O35" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="P35" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="Q35" s="10" t="inlineStr"/>
-      <c r="R35" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr"/>
-      <c r="T35" s="10" t="inlineStr"/>
-      <c r="U35" s="10" t="inlineStr"/>
-      <c r="V35" s="10" t="inlineStr"/>
-      <c r="W35" s="11">
-        <f>IF(C35="","",IF(E35="","Type à choisir",IF(F35="","Objectif principal à choisir",IF(H35="","Intensité à choisir",IF(I35="","Format à choisir",IF(COUNTIF(M35:V35,"Cours co")+COUNTIF(M35:V35,"SGT")=0,"Aucun club coché",IF(E35=IF(COUNTIF(M35:V35,"Cours co")&gt;0,IF(COUNTIF(M35:V35,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X35" s="9" t="n"/>
+      <c r="N35" s="10" t="n"/>
+      <c r="O35" s="10" t="n"/>
+      <c r="P35" s="10" t="n"/>
+      <c r="Q35" s="10" t="n"/>
+      <c r="R35" s="10" t="n"/>
+      <c r="S35" s="10" t="n"/>
+      <c r="T35" s="10" t="n"/>
+      <c r="U35" s="10" t="n"/>
+      <c r="V35" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W35" s="10" t="n"/>
+      <c r="X35" s="10" t="n"/>
+      <c r="Y35" s="11">
+        <f>IF(C35="","",IF(E35="","Type à choisir",IF(H35="","Objectif principal à choisir",IF(J35="","Intensité à choisir",IF(K35="","Format à choisir",IF(COUNTA(O35:X35)=0,"Aucun club coché",IF(AND(F35&lt;&gt;"",COUNTIF($A$2:$A$81,F35)=0),"Même cours que : identifiant inconnu",IF(AND(F35&lt;&gt;"",F35=A35),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z35" s="9" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>indoor-cycling</t>
+          <t>cross-training</t>
         </is>
       </c>
       <c r="B36" s="9" t="n"/>
       <c r="C36" s="9" t="inlineStr">
         <is>
-          <t>Indoor Cycling</t>
+          <t>Cross Training</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
@@ -3374,65 +3603,67 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F36" s="9" t="inlineStr">
+      <c r="F36" s="9" t="inlineStr"/>
+      <c r="G36" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G36" s="9" t="inlineStr"/>
-      <c r="H36" s="9" t="inlineStr">
+      <c r="I36" s="9" t="inlineStr"/>
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I36" s="9" t="inlineStr">
+      <c r="K36" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J36" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="K36" s="9" t="inlineStr">
+      <c r="L36" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="M36" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L36" s="10" t="n"/>
-      <c r="M36" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N36" s="10" t="inlineStr"/>
-      <c r="O36" s="10" t="inlineStr"/>
-      <c r="P36" s="10" t="inlineStr"/>
-      <c r="Q36" s="10" t="inlineStr"/>
-      <c r="R36" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr"/>
-      <c r="T36" s="10" t="inlineStr"/>
-      <c r="U36" s="10" t="inlineStr"/>
-      <c r="V36" s="10" t="inlineStr"/>
-      <c r="W36" s="11">
-        <f>IF(C36="","",IF(E36="","Type à choisir",IF(F36="","Objectif principal à choisir",IF(H36="","Intensité à choisir",IF(I36="","Format à choisir",IF(COUNTIF(M36:V36,"Cours co")+COUNTIF(M36:V36,"SGT")=0,"Aucun club coché",IF(E36=IF(COUNTIF(M36:V36,"Cours co")&gt;0,IF(COUNTIF(M36:V36,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X36" s="9" t="n"/>
+      <c r="N36" s="10" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="10" t="n"/>
+      <c r="R36" s="10" t="n"/>
+      <c r="S36" s="10" t="n"/>
+      <c r="T36" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U36" s="10" t="n"/>
+      <c r="V36" s="10" t="n"/>
+      <c r="W36" s="10" t="n"/>
+      <c r="X36" s="10" t="n"/>
+      <c r="Y36" s="11">
+        <f>IF(C36="","",IF(E36="","Type à choisir",IF(H36="","Objectif principal à choisir",IF(J36="","Intensité à choisir",IF(K36="","Format à choisir",IF(COUNTA(O36:X36)=0,"Aucun club coché",IF(AND(F36&lt;&gt;"",COUNTIF($A$2:$A$81,F36)=0),"Même cours que : identifiant inconnu",IF(AND(F36&lt;&gt;"",F36=A36),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z36" s="9" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>cross-training-sgt</t>
         </is>
       </c>
       <c r="B37" s="9" t="n"/>
       <c r="C37" s="9" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Cross Training</t>
         </is>
       </c>
       <c r="D37" s="9" t="inlineStr">
@@ -3442,64 +3673,78 @@
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>Cours co</t>
+          <t>SGT</t>
         </is>
       </c>
       <c r="F37" s="9" t="inlineStr">
         <is>
+          <t>cross-training</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr">
+        <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G37" s="9" t="inlineStr"/>
-      <c r="H37" s="9" t="inlineStr">
-        <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
-        <is>
-          <t>Salle</t>
-        </is>
-      </c>
-      <c r="J37" s="10" t="n">
+      <c r="I37" s="9" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>Intense</t>
+        </is>
+      </c>
+      <c r="K37" s="9" t="inlineStr">
+        <is>
+          <t>Petit groupe</t>
+        </is>
+      </c>
+      <c r="L37" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K37" s="9" t="inlineStr">
+      <c r="M37" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L37" s="10" t="n"/>
-      <c r="M37" s="10" t="inlineStr"/>
-      <c r="N37" s="10" t="inlineStr"/>
-      <c r="O37" s="10" t="inlineStr"/>
-      <c r="P37" s="10" t="inlineStr"/>
-      <c r="Q37" s="10" t="inlineStr"/>
-      <c r="R37" s="10" t="inlineStr"/>
-      <c r="S37" s="10" t="inlineStr"/>
-      <c r="T37" s="10" t="inlineStr"/>
-      <c r="U37" s="10" t="inlineStr"/>
-      <c r="V37" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W37" s="11">
-        <f>IF(C37="","",IF(E37="","Type à choisir",IF(F37="","Objectif principal à choisir",IF(H37="","Intensité à choisir",IF(I37="","Format à choisir",IF(COUNTIF(M37:V37,"Cours co")+COUNTIF(M37:V37,"SGT")=0,"Aucun club coché",IF(E37=IF(COUNTIF(M37:V37,"Cours co")&gt;0,IF(COUNTIF(M37:V37,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X37" s="9" t="n"/>
+      <c r="N37" s="10" t="n"/>
+      <c r="O37" s="10" t="n"/>
+      <c r="P37" s="10" t="n"/>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="n"/>
+      <c r="T37" s="10" t="n"/>
+      <c r="U37" s="10" t="n"/>
+      <c r="V37" s="10" t="n"/>
+      <c r="W37" s="10" t="n"/>
+      <c r="X37" s="10" t="n"/>
+      <c r="Y37" s="11">
+        <f>IF(C37="","",IF(E37="","Type à choisir",IF(H37="","Objectif principal à choisir",IF(J37="","Intensité à choisir",IF(K37="","Format à choisir",IF(COUNTA(O37:X37)=0,"Aucun club coché",IF(AND(F37&lt;&gt;"",COUNTIF($A$2:$A$81,F37)=0),"Même cours que : identifiant inconnu",IF(AND(F37&lt;&gt;"",F37=A37),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z37" s="9" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>core-bike</t>
+          <t>indoor-cycling</t>
         </is>
       </c>
       <c r="B38" s="9" t="n"/>
       <c r="C38" s="9" t="inlineStr">
         <is>
-          <t>Core Bike</t>
+          <t>Indoor Cycling</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
@@ -3512,61 +3757,71 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F38" s="9" t="inlineStr">
+      <c r="F38" s="9" t="inlineStr"/>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr">
         <is>
           <t>Se dépenser</t>
         </is>
       </c>
-      <c r="G38" s="9" t="inlineStr"/>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="I38" s="9" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="K38" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J38" s="10" t="n">
+      <c r="L38" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="K38" s="9" t="inlineStr">
+      <c r="M38" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L38" s="10" t="n"/>
-      <c r="M38" s="10" t="inlineStr"/>
-      <c r="N38" s="10" t="inlineStr"/>
-      <c r="O38" s="10" t="inlineStr"/>
-      <c r="P38" s="10" t="inlineStr"/>
-      <c r="Q38" s="10" t="inlineStr"/>
-      <c r="R38" s="10" t="inlineStr"/>
-      <c r="S38" s="10" t="inlineStr"/>
-      <c r="T38" s="10" t="inlineStr"/>
-      <c r="U38" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="V38" s="10" t="inlineStr"/>
-      <c r="W38" s="11">
-        <f>IF(C38="","",IF(E38="","Type à choisir",IF(F38="","Objectif principal à choisir",IF(H38="","Intensité à choisir",IF(I38="","Format à choisir",IF(COUNTIF(M38:V38,"Cours co")+COUNTIF(M38:V38,"SGT")=0,"Aucun club coché",IF(E38=IF(COUNTIF(M38:V38,"Cours co")&gt;0,IF(COUNTIF(M38:V38,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X38" s="9" t="n"/>
+      <c r="N38" s="10" t="n"/>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="10" t="n"/>
+      <c r="R38" s="10" t="n"/>
+      <c r="S38" s="10" t="n"/>
+      <c r="T38" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U38" s="10" t="n"/>
+      <c r="V38" s="10" t="n"/>
+      <c r="W38" s="10" t="n"/>
+      <c r="X38" s="10" t="n"/>
+      <c r="Y38" s="11">
+        <f>IF(C38="","",IF(E38="","Type à choisir",IF(H38="","Objectif principal à choisir",IF(J38="","Intensité à choisir",IF(K38="","Format à choisir",IF(COUNTA(O38:X38)=0,"Aucun club coché",IF(AND(F38&lt;&gt;"",COUNTIF($A$2:$A$81,F38)=0),"Même cours que : identifiant inconnu",IF(AND(F38&lt;&gt;"",F38=A38),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z38" s="9" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>hybrid-training</t>
+          <t>step</t>
         </is>
       </c>
       <c r="B39" s="9" t="n"/>
       <c r="C39" s="9" t="inlineStr">
         <is>
-          <t>Hybrid Training by Harmony</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="D39" s="9" t="inlineStr">
@@ -3579,69 +3834,67 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F39" s="9" t="inlineStr">
-        <is>
-          <t>Se dépasser</t>
-        </is>
-      </c>
-      <c r="G39" s="9" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H39" s="9" t="inlineStr">
         <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
+          <t>Se dépenser</t>
+        </is>
+      </c>
+      <c r="I39" s="9" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J39" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K39" s="9" t="inlineStr">
+      <c r="L39" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="M39" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L39" s="10" t="n"/>
-      <c r="M39" s="10" t="inlineStr"/>
-      <c r="N39" s="10" t="inlineStr"/>
-      <c r="O39" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P39" s="10" t="inlineStr"/>
-      <c r="Q39" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R39" s="10" t="inlineStr"/>
-      <c r="S39" s="10" t="inlineStr"/>
-      <c r="T39" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U39" s="10" t="inlineStr"/>
-      <c r="V39" s="10" t="inlineStr"/>
-      <c r="W39" s="11">
-        <f>IF(C39="","",IF(E39="","Type à choisir",IF(F39="","Objectif principal à choisir",IF(H39="","Intensité à choisir",IF(I39="","Format à choisir",IF(COUNTIF(M39:V39,"Cours co")+COUNTIF(M39:V39,"SGT")=0,"Aucun club coché",IF(E39=IF(COUNTIF(M39:V39,"Cours co")&gt;0,IF(COUNTIF(M39:V39,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X39" s="9" t="n"/>
+      <c r="N39" s="10" t="n"/>
+      <c r="O39" s="10" t="n"/>
+      <c r="P39" s="10" t="n"/>
+      <c r="Q39" s="10" t="n"/>
+      <c r="R39" s="10" t="n"/>
+      <c r="S39" s="10" t="n"/>
+      <c r="T39" s="10" t="n"/>
+      <c r="U39" s="10" t="n"/>
+      <c r="V39" s="10" t="n"/>
+      <c r="W39" s="10" t="n"/>
+      <c r="X39" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y39" s="11">
+        <f>IF(C39="","",IF(E39="","Type à choisir",IF(H39="","Objectif principal à choisir",IF(J39="","Intensité à choisir",IF(K39="","Format à choisir",IF(COUNTA(O39:X39)=0,"Aucun club coché",IF(AND(F39&lt;&gt;"",COUNTIF($A$2:$A$81,F39)=0),"Même cours que : identifiant inconnu",IF(AND(F39&lt;&gt;"",F39=A39),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z39" s="9" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>stretching</t>
+          <t>core-bike</t>
         </is>
       </c>
       <c r="B40" s="9" t="n"/>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Stretching</t>
+          <t>Core Bike</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
@@ -3654,61 +3907,67 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F40" s="9" t="inlineStr">
-        <is>
-          <t>Bouger mieux et soulager son dos</t>
-        </is>
-      </c>
-      <c r="G40" s="9" t="inlineStr"/>
+      <c r="F40" s="9" t="inlineStr"/>
+      <c r="G40" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H40" s="9" t="inlineStr">
         <is>
-          <t>Doux</t>
-        </is>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
+          <t>Se dépenser</t>
+        </is>
+      </c>
+      <c r="I40" s="9" t="inlineStr"/>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>Intense</t>
+        </is>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J40" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="K40" s="9" t="inlineStr">
+      <c r="L40" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="M40" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="inlineStr"/>
-      <c r="N40" s="10" t="inlineStr"/>
-      <c r="O40" s="10" t="inlineStr"/>
-      <c r="P40" s="10" t="inlineStr"/>
-      <c r="Q40" s="10" t="inlineStr"/>
-      <c r="R40" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr"/>
-      <c r="T40" s="10" t="inlineStr"/>
-      <c r="U40" s="10" t="inlineStr"/>
-      <c r="V40" s="10" t="inlineStr"/>
-      <c r="W40" s="11">
-        <f>IF(C40="","",IF(E40="","Type à choisir",IF(F40="","Objectif principal à choisir",IF(H40="","Intensité à choisir",IF(I40="","Format à choisir",IF(COUNTIF(M40:V40,"Cours co")+COUNTIF(M40:V40,"SGT")=0,"Aucun club coché",IF(E40=IF(COUNTIF(M40:V40,"Cours co")&gt;0,IF(COUNTIF(M40:V40,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X40" s="9" t="n"/>
+      <c r="N40" s="10" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="10" t="n"/>
+      <c r="R40" s="10" t="n"/>
+      <c r="S40" s="10" t="n"/>
+      <c r="T40" s="10" t="n"/>
+      <c r="U40" s="10" t="n"/>
+      <c r="V40" s="10" t="n"/>
+      <c r="W40" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X40" s="10" t="n"/>
+      <c r="Y40" s="11">
+        <f>IF(C40="","",IF(E40="","Type à choisir",IF(H40="","Objectif principal à choisir",IF(J40="","Intensité à choisir",IF(K40="","Format à choisir",IF(COUNTA(O40:X40)=0,"Aucun club coché",IF(AND(F40&lt;&gt;"",COUNTIF($A$2:$A$81,F40)=0),"Même cours que : identifiant inconnu",IF(AND(F40&lt;&gt;"",F40=A40),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>mobilite-stretching</t>
+          <t>hybrid-training</t>
         </is>
       </c>
       <c r="B41" s="9" t="n"/>
       <c r="C41" s="9" t="inlineStr">
         <is>
-          <t>Mobilité Stretching</t>
+          <t>Hybrid Training by Harmony</t>
         </is>
       </c>
       <c r="D41" s="9" t="inlineStr">
@@ -3721,69 +3980,75 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>Bouger mieux et soulager son dos</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr"/>
+      <c r="F41" s="9" t="inlineStr"/>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H41" s="9" t="inlineStr">
         <is>
-          <t>Doux</t>
-        </is>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
+          <t>Se dépasser</t>
+        </is>
+      </c>
+      <c r="I41" s="9" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>Intense</t>
+        </is>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J41" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="K41" s="9" t="inlineStr">
+      <c r="L41" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M41" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L41" s="10" t="n"/>
-      <c r="M41" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N41" s="10" t="inlineStr"/>
-      <c r="O41" s="10" t="inlineStr"/>
-      <c r="P41" s="10" t="inlineStr"/>
-      <c r="Q41" s="10" t="inlineStr"/>
-      <c r="R41" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr"/>
-      <c r="T41" s="10" t="inlineStr"/>
-      <c r="U41" s="10" t="inlineStr"/>
+      <c r="N41" s="10" t="n"/>
+      <c r="O41" s="10" t="n"/>
+      <c r="P41" s="10" t="n"/>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="n"/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T41" s="10" t="n"/>
+      <c r="U41" s="10" t="n"/>
       <c r="V41" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W41" s="11">
-        <f>IF(C41="","",IF(E41="","Type à choisir",IF(F41="","Objectif principal à choisir",IF(H41="","Intensité à choisir",IF(I41="","Format à choisir",IF(COUNTIF(M41:V41,"Cours co")+COUNTIF(M41:V41,"SGT")=0,"Aucun club coché",IF(E41=IF(COUNTIF(M41:V41,"Cours co")&gt;0,IF(COUNTIF(M41:V41,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X41" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W41" s="10" t="n"/>
+      <c r="X41" s="10" t="n"/>
+      <c r="Y41" s="11">
+        <f>IF(C41="","",IF(E41="","Type à choisir",IF(H41="","Objectif principal à choisir",IF(J41="","Intensité à choisir",IF(K41="","Format à choisir",IF(COUNTA(O41:X41)=0,"Aucun club coché",IF(AND(F41&lt;&gt;"",COUNTIF($A$2:$A$81,F41)=0),"Même cours que : identifiant inconnu",IF(AND(F41&lt;&gt;"",F41=A41),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z41" s="9" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>gym-douce</t>
+          <t>stretching</t>
         </is>
       </c>
       <c r="B42" s="9" t="n"/>
       <c r="C42" s="9" t="inlineStr">
         <is>
-          <t>Gym Douce</t>
+          <t>Stretching</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
@@ -3796,61 +4061,67 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F42" s="9" t="inlineStr">
+      <c r="F42" s="9" t="inlineStr"/>
+      <c r="G42" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="G42" s="9" t="inlineStr"/>
-      <c r="H42" s="9" t="inlineStr">
+      <c r="I42" s="9" t="inlineStr"/>
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I42" s="9" t="inlineStr">
+      <c r="K42" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J42" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K42" s="9" t="inlineStr">
+      <c r="L42" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="M42" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L42" s="10" t="n"/>
-      <c r="M42" s="10" t="inlineStr"/>
-      <c r="N42" s="10" t="inlineStr"/>
-      <c r="O42" s="10" t="inlineStr"/>
-      <c r="P42" s="10" t="inlineStr"/>
-      <c r="Q42" s="10" t="inlineStr"/>
-      <c r="R42" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr"/>
-      <c r="T42" s="10" t="inlineStr"/>
-      <c r="U42" s="10" t="inlineStr"/>
-      <c r="V42" s="10" t="inlineStr"/>
-      <c r="W42" s="11">
-        <f>IF(C42="","",IF(E42="","Type à choisir",IF(F42="","Objectif principal à choisir",IF(H42="","Intensité à choisir",IF(I42="","Format à choisir",IF(COUNTIF(M42:V42,"Cours co")+COUNTIF(M42:V42,"SGT")=0,"Aucun club coché",IF(E42=IF(COUNTIF(M42:V42,"Cours co")&gt;0,IF(COUNTIF(M42:V42,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X42" s="9" t="n"/>
+      <c r="N42" s="10" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="10" t="n"/>
+      <c r="R42" s="10" t="n"/>
+      <c r="S42" s="10" t="n"/>
+      <c r="T42" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U42" s="10" t="n"/>
+      <c r="V42" s="10" t="n"/>
+      <c r="W42" s="10" t="n"/>
+      <c r="X42" s="10" t="n"/>
+      <c r="Y42" s="11">
+        <f>IF(C42="","",IF(E42="","Type à choisir",IF(H42="","Objectif principal à choisir",IF(J42="","Intensité à choisir",IF(K42="","Format à choisir",IF(COUNTA(O42:X42)=0,"Aucun club coché",IF(AND(F42&lt;&gt;"",COUNTIF($A$2:$A$81,F42)=0),"Même cours que : identifiant inconnu",IF(AND(F42&lt;&gt;"",F42=A42),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z42" s="9" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="inlineStr">
         <is>
-          <t>gym-douce-dos</t>
+          <t>mobilite-stretching</t>
         </is>
       </c>
       <c r="B43" s="9" t="n"/>
       <c r="C43" s="9" t="inlineStr">
         <is>
-          <t>Gym Douce Dos</t>
+          <t>Mobilité Stretching</t>
         </is>
       </c>
       <c r="D43" s="9" t="inlineStr">
@@ -3863,69 +4134,75 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F43" s="9" t="inlineStr">
+      <c r="F43" s="9" t="inlineStr"/>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="G43" s="9" t="inlineStr"/>
-      <c r="H43" s="9" t="inlineStr">
+      <c r="I43" s="9" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I43" s="9" t="inlineStr">
+      <c r="K43" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J43" s="10" t="n">
+      <c r="L43" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="K43" s="9" t="inlineStr">
+      <c r="M43" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L43" s="10" t="n"/>
-      <c r="M43" s="10" t="inlineStr"/>
-      <c r="N43" s="10" t="inlineStr"/>
+      <c r="N43" s="10" t="n"/>
       <c r="O43" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P43" s="10" t="inlineStr"/>
-      <c r="Q43" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R43" s="10" t="inlineStr"/>
-      <c r="S43" s="10" t="inlineStr"/>
-      <c r="T43" s="10" t="inlineStr"/>
-      <c r="U43" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="V43" s="10" t="inlineStr"/>
-      <c r="W43" s="11">
-        <f>IF(C43="","",IF(E43="","Type à choisir",IF(F43="","Objectif principal à choisir",IF(H43="","Intensité à choisir",IF(I43="","Format à choisir",IF(COUNTIF(M43:V43,"Cours co")+COUNTIF(M43:V43,"SGT")=0,"Aucun club coché",IF(E43=IF(COUNTIF(M43:V43,"Cours co")&gt;0,IF(COUNTIF(M43:V43,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X43" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P43" s="10" t="n"/>
+      <c r="Q43" s="10" t="n"/>
+      <c r="R43" s="10" t="n"/>
+      <c r="S43" s="10" t="n"/>
+      <c r="T43" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U43" s="10" t="n"/>
+      <c r="V43" s="10" t="n"/>
+      <c r="W43" s="10" t="n"/>
+      <c r="X43" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y43" s="11">
+        <f>IF(C43="","",IF(E43="","Type à choisir",IF(H43="","Objectif principal à choisir",IF(J43="","Intensité à choisir",IF(K43="","Format à choisir",IF(COUNTA(O43:X43)=0,"Aucun club coché",IF(AND(F43&lt;&gt;"",COUNTIF($A$2:$A$81,F43)=0),"Même cours que : identifiant inconnu",IF(AND(F43&lt;&gt;"",F43=A43),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z43" s="9" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="inlineStr">
         <is>
-          <t>move-and-mind</t>
+          <t>gym-douce</t>
         </is>
       </c>
       <c r="B44" s="9" t="n"/>
       <c r="C44" s="9" t="inlineStr">
         <is>
-          <t>Move &amp; Mind</t>
+          <t>Gym Douce</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
@@ -3938,69 +4215,67 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F44" s="9" t="inlineStr">
+      <c r="F44" s="9" t="inlineStr"/>
+      <c r="G44" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr">
         <is>
           <t>Bouger mieux et soulager son dos</t>
         </is>
       </c>
-      <c r="G44" s="9" t="inlineStr"/>
-      <c r="H44" s="9" t="inlineStr">
+      <c r="I44" s="9" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I44" s="9" t="inlineStr">
+      <c r="K44" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J44" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="K44" s="9" t="inlineStr">
+      <c r="L44" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M44" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L44" s="10" t="n"/>
-      <c r="M44" s="10" t="inlineStr"/>
-      <c r="N44" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="O44" s="10" t="inlineStr"/>
-      <c r="P44" s="10" t="inlineStr"/>
-      <c r="Q44" s="10" t="inlineStr"/>
-      <c r="R44" s="10" t="inlineStr"/>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
+      <c r="N44" s="10" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="10" t="n"/>
+      <c r="R44" s="10" t="n"/>
+      <c r="S44" s="10" t="n"/>
       <c r="T44" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U44" s="10" t="inlineStr"/>
-      <c r="V44" s="10" t="inlineStr"/>
-      <c r="W44" s="11">
-        <f>IF(C44="","",IF(E44="","Type à choisir",IF(F44="","Objectif principal à choisir",IF(H44="","Intensité à choisir",IF(I44="","Format à choisir",IF(COUNTIF(M44:V44,"Cours co")+COUNTIF(M44:V44,"SGT")=0,"Aucun club coché",IF(E44=IF(COUNTIF(M44:V44,"Cours co")&gt;0,IF(COUNTIF(M44:V44,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X44" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U44" s="10" t="n"/>
+      <c r="V44" s="10" t="n"/>
+      <c r="W44" s="10" t="n"/>
+      <c r="X44" s="10" t="n"/>
+      <c r="Y44" s="11">
+        <f>IF(C44="","",IF(E44="","Type à choisir",IF(H44="","Objectif principal à choisir",IF(J44="","Intensité à choisir",IF(K44="","Format à choisir",IF(COUNTA(O44:X44)=0,"Aucun club coché",IF(AND(F44&lt;&gt;"",COUNTIF($A$2:$A$81,F44)=0),"Même cours que : identifiant inconnu",IF(AND(F44&lt;&gt;"",F44=A44),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z44" s="9" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>cours-zen</t>
+          <t>gym-douce-dos</t>
         </is>
       </c>
       <c r="B45" s="9" t="n"/>
       <c r="C45" s="9" t="inlineStr">
         <is>
-          <t>Cours Zen</t>
+          <t>Gym Douce Dos</t>
         </is>
       </c>
       <c r="D45" s="9" t="inlineStr">
@@ -4013,69 +4288,75 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F45" s="9" t="inlineStr">
-        <is>
-          <t>Se détendre</t>
-        </is>
-      </c>
-      <c r="G45" s="9" t="inlineStr"/>
+      <c r="F45" s="9" t="inlineStr"/>
+      <c r="G45" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H45" s="9" t="inlineStr">
         <is>
+          <t>Bouger mieux et soulager son dos</t>
+        </is>
+      </c>
+      <c r="I45" s="9" t="inlineStr"/>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I45" s="9" t="inlineStr">
+      <c r="K45" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J45" s="10" t="n">
+      <c r="L45" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="K45" s="9" t="inlineStr">
+      <c r="M45" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L45" s="10" t="n"/>
-      <c r="M45" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N45" s="10" t="inlineStr"/>
-      <c r="O45" s="10" t="inlineStr"/>
-      <c r="P45" s="10" t="inlineStr"/>
-      <c r="Q45" s="10" t="inlineStr"/>
-      <c r="R45" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr"/>
-      <c r="T45" s="10" t="inlineStr"/>
-      <c r="U45" s="10" t="inlineStr"/>
-      <c r="V45" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W45" s="11">
-        <f>IF(C45="","",IF(E45="","Type à choisir",IF(F45="","Objectif principal à choisir",IF(H45="","Intensité à choisir",IF(I45="","Format à choisir",IF(COUNTIF(M45:V45,"Cours co")+COUNTIF(M45:V45,"SGT")=0,"Aucun club coché",IF(E45=IF(COUNTIF(M45:V45,"Cours co")&gt;0,IF(COUNTIF(M45:V45,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X45" s="9" t="n"/>
+      <c r="N45" s="10" t="n"/>
+      <c r="O45" s="10" t="n"/>
+      <c r="P45" s="10" t="n"/>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R45" s="10" t="n"/>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T45" s="10" t="n"/>
+      <c r="U45" s="10" t="n"/>
+      <c r="V45" s="10" t="n"/>
+      <c r="W45" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X45" s="10" t="n"/>
+      <c r="Y45" s="11">
+        <f>IF(C45="","",IF(E45="","Type à choisir",IF(H45="","Objectif principal à choisir",IF(J45="","Intensité à choisir",IF(K45="","Format à choisir",IF(COUNTA(O45:X45)=0,"Aucun club coché",IF(AND(F45&lt;&gt;"",COUNTIF($A$2:$A$81,F45)=0),"Même cours que : identifiant inconnu",IF(AND(F45&lt;&gt;"",F45=A45),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z45" s="9" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>sophrologie-stretching</t>
+          <t>move-and-mind</t>
         </is>
       </c>
       <c r="B46" s="9" t="n"/>
       <c r="C46" s="9" t="inlineStr">
         <is>
-          <t>Sophrologie Stretching</t>
+          <t>Move &amp; Mind</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
@@ -4088,69 +4369,75 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F46" s="9" t="inlineStr">
-        <is>
-          <t>Se détendre</t>
-        </is>
-      </c>
-      <c r="G46" s="9" t="inlineStr"/>
+      <c r="F46" s="9" t="inlineStr"/>
+      <c r="G46" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H46" s="9" t="inlineStr">
         <is>
+          <t>Bouger mieux et soulager son dos</t>
+        </is>
+      </c>
+      <c r="I46" s="9" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
           <t>Doux</t>
         </is>
       </c>
-      <c r="I46" s="9" t="inlineStr">
+      <c r="K46" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J46" s="10" t="n">
+      <c r="L46" s="10" t="n">
         <v>55</v>
       </c>
-      <c r="K46" s="9" t="inlineStr">
+      <c r="M46" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="inlineStr"/>
-      <c r="N46" s="10" t="inlineStr"/>
-      <c r="O46" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="P46" s="10" t="inlineStr"/>
-      <c r="Q46" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R46" s="10" t="inlineStr"/>
-      <c r="S46" s="10" t="inlineStr"/>
-      <c r="T46" s="10" t="inlineStr"/>
+      <c r="N46" s="10" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q46" s="10" t="n"/>
+      <c r="R46" s="10" t="n"/>
+      <c r="S46" s="10" t="n"/>
+      <c r="T46" s="10" t="n"/>
       <c r="U46" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="V46" s="10" t="inlineStr"/>
-      <c r="W46" s="11">
-        <f>IF(C46="","",IF(E46="","Type à choisir",IF(F46="","Objectif principal à choisir",IF(H46="","Intensité à choisir",IF(I46="","Format à choisir",IF(COUNTIF(M46:V46,"Cours co")+COUNTIF(M46:V46,"SGT")=0,"Aucun club coché",IF(E46=IF(COUNTIF(M46:V46,"Cours co")&gt;0,IF(COUNTIF(M46:V46,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X46" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V46" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W46" s="10" t="n"/>
+      <c r="X46" s="10" t="n"/>
+      <c r="Y46" s="11">
+        <f>IF(C46="","",IF(E46="","Type à choisir",IF(H46="","Objectif principal à choisir",IF(J46="","Intensité à choisir",IF(K46="","Format à choisir",IF(COUNTA(O46:X46)=0,"Aucun club coché",IF(AND(F46&lt;&gt;"",COUNTIF($A$2:$A$81,F46)=0),"Même cours que : identifiant inconnu",IF(AND(F46&lt;&gt;"",F46=A46),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z46" s="9" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>zumba</t>
+          <t>cours-zen</t>
         </is>
       </c>
       <c r="B47" s="9" t="n"/>
       <c r="C47" s="9" t="inlineStr">
         <is>
-          <t>Zumba</t>
+          <t>Cours Zen</t>
         </is>
       </c>
       <c r="D47" s="9" t="inlineStr">
@@ -4163,73 +4450,75 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F47" s="9" t="inlineStr">
-        <is>
-          <t>Danser</t>
-        </is>
-      </c>
-      <c r="G47" s="9" t="inlineStr"/>
+      <c r="F47" s="9" t="inlineStr"/>
+      <c r="G47" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H47" s="9" t="inlineStr">
         <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-      <c r="I47" s="9" t="inlineStr">
+          <t>Se détendre</t>
+        </is>
+      </c>
+      <c r="I47" s="9" t="inlineStr"/>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>Doux</t>
+        </is>
+      </c>
+      <c r="K47" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J47" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K47" s="9" t="inlineStr">
+      <c r="L47" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="M47" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L47" s="10" t="n"/>
-      <c r="M47" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N47" s="10" t="inlineStr"/>
-      <c r="O47" s="10" t="inlineStr"/>
-      <c r="P47" s="10" t="inlineStr"/>
-      <c r="Q47" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="R47" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr"/>
-      <c r="T47" s="10" t="inlineStr"/>
-      <c r="U47" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="V47" s="10" t="inlineStr"/>
-      <c r="W47" s="11">
-        <f>IF(C47="","",IF(E47="","Type à choisir",IF(F47="","Objectif principal à choisir",IF(H47="","Intensité à choisir",IF(I47="","Format à choisir",IF(COUNTIF(M47:V47,"Cours co")+COUNTIF(M47:V47,"SGT")=0,"Aucun club coché",IF(E47=IF(COUNTIF(M47:V47,"Cours co")&gt;0,IF(COUNTIF(M47:V47,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X47" s="9" t="n"/>
+      <c r="N47" s="10" t="n"/>
+      <c r="O47" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P47" s="10" t="n"/>
+      <c r="Q47" s="10" t="n"/>
+      <c r="R47" s="10" t="n"/>
+      <c r="S47" s="10" t="n"/>
+      <c r="T47" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U47" s="10" t="n"/>
+      <c r="V47" s="10" t="n"/>
+      <c r="W47" s="10" t="n"/>
+      <c r="X47" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y47" s="11">
+        <f>IF(C47="","",IF(E47="","Type à choisir",IF(H47="","Objectif principal à choisir",IF(J47="","Intensité à choisir",IF(K47="","Format à choisir",IF(COUNTA(O47:X47)=0,"Aucun club coché",IF(AND(F47&lt;&gt;"",COUNTIF($A$2:$A$81,F47)=0),"Même cours que : identifiant inconnu",IF(AND(F47&lt;&gt;"",F47=A47),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z47" s="9" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>salsa</t>
+          <t>sophrologie-stretching</t>
         </is>
       </c>
       <c r="B48" s="9" t="n"/>
       <c r="C48" s="9" t="inlineStr">
         <is>
-          <t>Salsa</t>
+          <t>Sophrologie Stretching</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
@@ -4242,61 +4531,75 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F48" s="9" t="inlineStr">
-        <is>
-          <t>Danser</t>
-        </is>
-      </c>
-      <c r="G48" s="9" t="inlineStr"/>
+      <c r="F48" s="9" t="inlineStr"/>
+      <c r="G48" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H48" s="9" t="inlineStr">
         <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
+          <t>Se détendre</t>
+        </is>
+      </c>
+      <c r="I48" s="9" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr">
+        <is>
+          <t>Doux</t>
+        </is>
+      </c>
+      <c r="K48" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J48" s="10" t="n">
-        <v>60</v>
-      </c>
-      <c r="K48" s="9" t="inlineStr">
+      <c r="L48" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="M48" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L48" s="10" t="n"/>
-      <c r="M48" s="10" t="inlineStr"/>
-      <c r="N48" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="O48" s="10" t="inlineStr"/>
-      <c r="P48" s="10" t="inlineStr"/>
-      <c r="Q48" s="10" t="inlineStr"/>
-      <c r="R48" s="10" t="inlineStr"/>
-      <c r="S48" s="10" t="inlineStr"/>
-      <c r="T48" s="10" t="inlineStr"/>
-      <c r="U48" s="10" t="inlineStr"/>
-      <c r="V48" s="10" t="inlineStr"/>
-      <c r="W48" s="11">
-        <f>IF(C48="","",IF(E48="","Type à choisir",IF(F48="","Objectif principal à choisir",IF(H48="","Intensité à choisir",IF(I48="","Format à choisir",IF(COUNTIF(M48:V48,"Cours co")+COUNTIF(M48:V48,"SGT")=0,"Aucun club coché",IF(E48=IF(COUNTIF(M48:V48,"Cours co")&gt;0,IF(COUNTIF(M48:V48,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X48" s="9" t="n"/>
+      <c r="N48" s="10" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R48" s="10" t="n"/>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T48" s="10" t="n"/>
+      <c r="U48" s="10" t="n"/>
+      <c r="V48" s="10" t="n"/>
+      <c r="W48" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X48" s="10" t="n"/>
+      <c r="Y48" s="11">
+        <f>IF(C48="","",IF(E48="","Type à choisir",IF(H48="","Objectif principal à choisir",IF(J48="","Intensité à choisir",IF(K48="","Format à choisir",IF(COUNTA(O48:X48)=0,"Aucun club coché",IF(AND(F48&lt;&gt;"",COUNTIF($A$2:$A$81,F48)=0),"Même cours que : identifiant inconnu",IF(AND(F48&lt;&gt;"",F48=A48),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z48" s="9" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>all-styles-dance</t>
+          <t>zumba</t>
         </is>
       </c>
       <c r="B49" s="9" t="n"/>
       <c r="C49" s="9" t="inlineStr">
         <is>
-          <t>All Styles Dance</t>
+          <t>Zumba</t>
         </is>
       </c>
       <c r="D49" s="9" t="inlineStr">
@@ -4309,69 +4612,79 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F49" s="9" t="inlineStr">
+      <c r="F49" s="9" t="inlineStr"/>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr">
         <is>
           <t>Danser</t>
         </is>
       </c>
-      <c r="G49" s="9" t="inlineStr"/>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="I49" s="9" t="inlineStr"/>
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>Modéré</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="K49" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J49" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="K49" s="9" t="inlineStr">
+      <c r="L49" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M49" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L49" s="10" t="n"/>
-      <c r="M49" s="10" t="inlineStr"/>
-      <c r="N49" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="O49" s="10" t="inlineStr"/>
-      <c r="P49" s="10" t="inlineStr"/>
-      <c r="Q49" s="10" t="inlineStr"/>
-      <c r="R49" s="10" t="inlineStr"/>
+      <c r="N49" s="10" t="n"/>
+      <c r="O49" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P49" s="10" t="n"/>
+      <c r="Q49" s="10" t="n"/>
+      <c r="R49" s="10" t="n"/>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
+          <t>x</t>
         </is>
       </c>
       <c r="T49" s="10" t="inlineStr">
         <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="U49" s="10" t="inlineStr"/>
-      <c r="V49" s="10" t="inlineStr"/>
-      <c r="W49" s="11">
-        <f>IF(C49="","",IF(E49="","Type à choisir",IF(F49="","Objectif principal à choisir",IF(H49="","Intensité à choisir",IF(I49="","Format à choisir",IF(COUNTIF(M49:V49,"Cours co")+COUNTIF(M49:V49,"SGT")=0,"Aucun club coché",IF(E49=IF(COUNTIF(M49:V49,"Cours co")&gt;0,IF(COUNTIF(M49:V49,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X49" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U49" s="10" t="n"/>
+      <c r="V49" s="10" t="n"/>
+      <c r="W49" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X49" s="10" t="n"/>
+      <c r="Y49" s="11">
+        <f>IF(C49="","",IF(E49="","Type à choisir",IF(H49="","Objectif principal à choisir",IF(J49="","Intensité à choisir",IF(K49="","Format à choisir",IF(COUNTA(O49:X49)=0,"Aucun club coché",IF(AND(F49&lt;&gt;"",COUNTIF($A$2:$A$81,F49)=0),"Même cours que : identifiant inconnu",IF(AND(F49&lt;&gt;"",F49=A49),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z49" s="9" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="inlineStr">
         <is>
-          <t>boxe</t>
+          <t>salsa</t>
         </is>
       </c>
       <c r="B50" s="9" t="n"/>
       <c r="C50" s="9" t="inlineStr">
         <is>
-          <t>Boxe</t>
+          <t>Salsa</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
@@ -4384,69 +4697,67 @@
           <t>Cours co</t>
         </is>
       </c>
-      <c r="F50" s="9" t="inlineStr">
-        <is>
-          <t>Se dépenser</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr"/>
+      <c r="F50" s="9" t="inlineStr"/>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H50" s="9" t="inlineStr">
         <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
+          <t>Danser</t>
+        </is>
+      </c>
+      <c r="I50" s="9" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+      <c r="K50" s="9" t="inlineStr">
         <is>
           <t>Salle</t>
         </is>
       </c>
-      <c r="J50" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="K50" s="9" t="inlineStr">
+      <c r="L50" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="M50" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L50" s="10" t="n"/>
-      <c r="M50" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="N50" s="10" t="inlineStr"/>
-      <c r="O50" s="10" t="inlineStr"/>
-      <c r="P50" s="10" t="inlineStr"/>
-      <c r="Q50" s="10" t="inlineStr"/>
-      <c r="R50" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr"/>
-      <c r="T50" s="10" t="inlineStr"/>
-      <c r="U50" s="10" t="inlineStr"/>
-      <c r="V50" s="10" t="inlineStr">
-        <is>
-          <t>Cours co</t>
-        </is>
-      </c>
-      <c r="W50" s="11">
-        <f>IF(C50="","",IF(E50="","Type à choisir",IF(F50="","Objectif principal à choisir",IF(H50="","Intensité à choisir",IF(I50="","Format à choisir",IF(COUNTIF(M50:V50,"Cours co")+COUNTIF(M50:V50,"SGT")=0,"Aucun club coché",IF(E50=IF(COUNTIF(M50:V50,"Cours co")&gt;0,IF(COUNTIF(M50:V50,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X50" s="9" t="n"/>
+      <c r="N50" s="10" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q50" s="10" t="n"/>
+      <c r="R50" s="10" t="n"/>
+      <c r="S50" s="10" t="n"/>
+      <c r="T50" s="10" t="n"/>
+      <c r="U50" s="10" t="n"/>
+      <c r="V50" s="10" t="n"/>
+      <c r="W50" s="10" t="n"/>
+      <c r="X50" s="10" t="n"/>
+      <c r="Y50" s="11">
+        <f>IF(C50="","",IF(E50="","Type à choisir",IF(H50="","Objectif principal à choisir",IF(J50="","Intensité à choisir",IF(K50="","Format à choisir",IF(COUNTA(O50:X50)=0,"Aucun club coché",IF(AND(F50&lt;&gt;"",COUNTIF($A$2:$A$81,F50)=0),"Même cours que : identifiant inconnu",IF(AND(F50&lt;&gt;"",F50=A50),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z50" s="9" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>hiit-boxing</t>
+          <t>all-styles-dance</t>
         </is>
       </c>
       <c r="B51" s="9" t="n"/>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>HIIT Boxing</t>
+          <t>All Styles Dance</t>
         </is>
       </c>
       <c r="D51" s="9" t="inlineStr">
@@ -4456,64 +4767,78 @@
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="inlineStr">
-        <is>
-          <t>Se dépenser</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr"/>
+          <t>Cours co</t>
+        </is>
+      </c>
+      <c r="F51" s="9" t="inlineStr"/>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H51" s="9" t="inlineStr">
         <is>
-          <t>Intense</t>
-        </is>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>Petit groupe</t>
-        </is>
-      </c>
-      <c r="J51" s="10" t="n">
-        <v>45</v>
+          <t>Danser</t>
+        </is>
+      </c>
+      <c r="I51" s="9" t="inlineStr"/>
+      <c r="J51" s="9" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
       </c>
       <c r="K51" s="9" t="inlineStr">
         <is>
+          <t>Salle</t>
+        </is>
+      </c>
+      <c r="L51" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="M51" s="9" t="inlineStr">
+        <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L51" s="10" t="n"/>
-      <c r="M51" s="10" t="inlineStr"/>
-      <c r="N51" s="10" t="inlineStr"/>
-      <c r="O51" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="P51" s="10" t="inlineStr"/>
-      <c r="Q51" s="10" t="inlineStr"/>
-      <c r="R51" s="10" t="inlineStr"/>
-      <c r="S51" s="10" t="inlineStr"/>
-      <c r="T51" s="10" t="inlineStr"/>
-      <c r="U51" s="10" t="inlineStr"/>
-      <c r="V51" s="10" t="inlineStr"/>
-      <c r="W51" s="11">
-        <f>IF(C51="","",IF(E51="","Type à choisir",IF(F51="","Objectif principal à choisir",IF(H51="","Intensité à choisir",IF(I51="","Format à choisir",IF(COUNTIF(M51:V51,"Cours co")+COUNTIF(M51:V51,"SGT")=0,"Aucun club coché",IF(E51=IF(COUNTIF(M51:V51,"Cours co")&gt;0,IF(COUNTIF(M51:V51,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X51" s="9" t="n"/>
+      <c r="N51" s="10" t="n"/>
+      <c r="O51" s="10" t="n"/>
+      <c r="P51" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q51" s="10" t="n"/>
+      <c r="R51" s="10" t="n"/>
+      <c r="S51" s="10" t="n"/>
+      <c r="T51" s="10" t="n"/>
+      <c r="U51" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V51" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W51" s="10" t="n"/>
+      <c r="X51" s="10" t="n"/>
+      <c r="Y51" s="11">
+        <f>IF(C51="","",IF(E51="","Type à choisir",IF(H51="","Objectif principal à choisir",IF(J51="","Intensité à choisir",IF(K51="","Format à choisir",IF(COUNTA(O51:X51)=0,"Aucun club coché",IF(AND(F51&lt;&gt;"",COUNTIF($A$2:$A$81,F51)=0),"Même cours que : identifiant inconnu",IF(AND(F51&lt;&gt;"",F51=A51),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z51" s="9" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="inlineStr">
         <is>
-          <t>flow</t>
+          <t>boxe</t>
         </is>
       </c>
       <c r="B52" s="9" t="n"/>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>Boxe</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
@@ -4523,68 +4848,78 @@
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="F52" s="9" t="inlineStr">
-        <is>
-          <t>Bouger mieux et soulager son dos</t>
-        </is>
-      </c>
+          <t>Cours co</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="inlineStr"/>
       <c r="G52" s="9" t="inlineStr">
         <is>
-          <t>Se détendre</t>
+          <t>Aucune</t>
         </is>
       </c>
       <c r="H52" s="9" t="inlineStr">
         <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>Petit groupe</t>
-        </is>
-      </c>
-      <c r="J52" s="10" t="n">
+          <t>Se dépenser</t>
+        </is>
+      </c>
+      <c r="I52" s="9" t="inlineStr"/>
+      <c r="J52" s="9" t="inlineStr">
+        <is>
+          <t>Intense</t>
+        </is>
+      </c>
+      <c r="K52" s="9" t="inlineStr">
+        <is>
+          <t>Salle</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K52" s="9" t="inlineStr">
+      <c r="M52" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L52" s="10" t="n"/>
-      <c r="M52" s="10" t="inlineStr"/>
-      <c r="N52" s="10" t="inlineStr"/>
+      <c r="N52" s="10" t="n"/>
       <c r="O52" s="10" t="inlineStr">
         <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="P52" s="10" t="inlineStr"/>
-      <c r="Q52" s="10" t="inlineStr"/>
-      <c r="R52" s="10" t="inlineStr"/>
-      <c r="S52" s="10" t="inlineStr"/>
-      <c r="T52" s="10" t="inlineStr"/>
-      <c r="U52" s="10" t="inlineStr"/>
-      <c r="V52" s="10" t="inlineStr"/>
-      <c r="W52" s="11">
-        <f>IF(C52="","",IF(E52="","Type à choisir",IF(F52="","Objectif principal à choisir",IF(H52="","Intensité à choisir",IF(I52="","Format à choisir",IF(COUNTIF(M52:V52,"Cours co")+COUNTIF(M52:V52,"SGT")=0,"Aucun club coché",IF(E52=IF(COUNTIF(M52:V52,"Cours co")&gt;0,IF(COUNTIF(M52:V52,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X52" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="10" t="n"/>
+      <c r="R52" s="10" t="n"/>
+      <c r="S52" s="10" t="n"/>
+      <c r="T52" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U52" s="10" t="n"/>
+      <c r="V52" s="10" t="n"/>
+      <c r="W52" s="10" t="n"/>
+      <c r="X52" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y52" s="11">
+        <f>IF(C52="","",IF(E52="","Type à choisir",IF(H52="","Objectif principal à choisir",IF(J52="","Intensité à choisir",IF(K52="","Format à choisir",IF(COUNTA(O52:X52)=0,"Aucun club coché",IF(AND(F52&lt;&gt;"",COUNTIF($A$2:$A$81,F52)=0),"Même cours que : identifiant inconnu",IF(AND(F52&lt;&gt;"",F52=A52),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z52" s="9" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="inlineStr">
         <is>
-          <t>lorem-ipsum</t>
+          <t>hiit-boxing</t>
         </is>
       </c>
       <c r="B53" s="9" t="n"/>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Lorem Ipsum</t>
+          <t>HIIT Boxing</t>
         </is>
       </c>
       <c r="D53" s="9" t="inlineStr">
@@ -4597,207 +4932,311 @@
           <t>SGT</t>
         </is>
       </c>
-      <c r="F53" s="9" t="inlineStr">
-        <is>
-          <t>Se renforcer et sculpter</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr"/>
+      <c r="F53" s="9" t="inlineStr"/>
+      <c r="G53" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
       <c r="H53" s="9" t="inlineStr">
         <is>
-          <t>Modéré</t>
-        </is>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
+          <t>Se dépenser</t>
+        </is>
+      </c>
+      <c r="I53" s="9" t="inlineStr"/>
+      <c r="J53" s="9" t="inlineStr">
+        <is>
+          <t>Intense</t>
+        </is>
+      </c>
+      <c r="K53" s="9" t="inlineStr">
         <is>
           <t>Petit groupe</t>
         </is>
       </c>
-      <c r="J53" s="10" t="n">
+      <c r="L53" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="K53" s="9" t="inlineStr">
+      <c r="M53" s="9" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
       </c>
-      <c r="L53" s="10" t="n"/>
-      <c r="M53" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="N53" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="O53" s="10" t="inlineStr"/>
-      <c r="P53" s="10" t="inlineStr"/>
+      <c r="N53" s="10" t="n"/>
+      <c r="O53" s="10" t="n"/>
+      <c r="P53" s="10" t="n"/>
       <c r="Q53" s="10" t="inlineStr">
         <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="R53" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="T53" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="U53" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="V53" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="W53" s="11">
-        <f>IF(C53="","",IF(E53="","Type à choisir",IF(F53="","Objectif principal à choisir",IF(H53="","Intensité à choisir",IF(I53="","Format à choisir",IF(COUNTIF(M53:V53,"Cours co")+COUNTIF(M53:V53,"SGT")=0,"Aucun club coché",IF(E53=IF(COUNTIF(M53:V53,"Cours co")&gt;0,IF(COUNTIF(M53:V53,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X53" s="9" t="n"/>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="n"/>
+      <c r="S53" s="10" t="n"/>
+      <c r="T53" s="10" t="n"/>
+      <c r="U53" s="10" t="n"/>
+      <c r="V53" s="10" t="n"/>
+      <c r="W53" s="10" t="n"/>
+      <c r="X53" s="10" t="n"/>
+      <c r="Y53" s="11">
+        <f>IF(C53="","",IF(E53="","Type à choisir",IF(H53="","Objectif principal à choisir",IF(J53="","Intensité à choisir",IF(K53="","Format à choisir",IF(COUNTA(O53:X53)=0,"Aucun club coché",IF(AND(F53&lt;&gt;"",COUNTIF($A$2:$A$81,F53)=0),"Même cours que : identifiant inconnu",IF(AND(F53&lt;&gt;"",F53=A53),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z53" s="9" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="inlineStr">
         <is>
-          <t>ceremony-hyrox-max</t>
+          <t>flow</t>
         </is>
       </c>
       <c r="B54" s="9" t="n"/>
       <c r="C54" s="9" t="inlineStr">
         <is>
+          <t>Flow</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="E54" s="9" t="inlineStr">
+        <is>
+          <t>SGT</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="inlineStr"/>
+      <c r="G54" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr">
+        <is>
+          <t>Bouger mieux et soulager son dos</t>
+        </is>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>Se détendre</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+      <c r="K54" s="9" t="inlineStr">
+        <is>
+          <t>Petit groupe</t>
+        </is>
+      </c>
+      <c r="L54" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="M54" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="N54" s="10" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R54" s="10" t="n"/>
+      <c r="S54" s="10" t="n"/>
+      <c r="T54" s="10" t="n"/>
+      <c r="U54" s="10" t="n"/>
+      <c r="V54" s="10" t="n"/>
+      <c r="W54" s="10" t="n"/>
+      <c r="X54" s="10" t="n"/>
+      <c r="Y54" s="11">
+        <f>IF(C54="","",IF(E54="","Type à choisir",IF(H54="","Objectif principal à choisir",IF(J54="","Intensité à choisir",IF(K54="","Format à choisir",IF(COUNTA(O54:X54)=0,"Aucun club coché",IF(AND(F54&lt;&gt;"",COUNTIF($A$2:$A$81,F54)=0),"Même cours que : identifiant inconnu",IF(AND(F54&lt;&gt;"",F54=A54),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>lorem-ipsum</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="n"/>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>Lorem Ipsum</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="inlineStr">
+        <is>
+          <t>Actif</t>
+        </is>
+      </c>
+      <c r="E55" s="9" t="inlineStr">
+        <is>
+          <t>SGT</t>
+        </is>
+      </c>
+      <c r="F55" s="9" t="inlineStr"/>
+      <c r="G55" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H55" s="9" t="inlineStr">
+        <is>
+          <t>Se renforcer et sculpter</t>
+        </is>
+      </c>
+      <c r="I55" s="9" t="inlineStr"/>
+      <c r="J55" s="9" t="inlineStr">
+        <is>
+          <t>Modéré</t>
+        </is>
+      </c>
+      <c r="K55" s="9" t="inlineStr">
+        <is>
+          <t>Petit groupe</t>
+        </is>
+      </c>
+      <c r="L55" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="M55" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="N55" s="10" t="n"/>
+      <c r="O55" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="P55" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Q55" s="10" t="n"/>
+      <c r="R55" s="10" t="n"/>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T55" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="U55" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="V55" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="W55" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="X55" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="Y55" s="11">
+        <f>IF(C55="","",IF(E55="","Type à choisir",IF(H55="","Objectif principal à choisir",IF(J55="","Intensité à choisir",IF(K55="","Format à choisir",IF(COUNTA(O55:X55)=0,"Aucun club coché",IF(AND(F55&lt;&gt;"",COUNTIF($A$2:$A$81,F55)=0),"Même cours que : identifiant inconnu",IF(AND(F55&lt;&gt;"",F55=A55),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>ceremony-hyrox-max</t>
+        </is>
+      </c>
+      <c r="B56" s="9" t="n"/>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
           <t>Ceremony Hyrox Max</t>
         </is>
       </c>
-      <c r="D54" s="9" t="inlineStr">
+      <c r="D56" s="9" t="inlineStr">
         <is>
           <t>Actif</t>
         </is>
       </c>
-      <c r="E54" s="9" t="inlineStr">
+      <c r="E56" s="9" t="inlineStr">
         <is>
           <t>SGT</t>
         </is>
       </c>
-      <c r="F54" s="9" t="inlineStr">
+      <c r="F56" s="9" t="inlineStr"/>
+      <c r="G56" s="9" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H56" s="9" t="inlineStr">
         <is>
           <t>Se dépasser</t>
         </is>
       </c>
-      <c r="G54" s="9" t="inlineStr"/>
-      <c r="H54" s="9" t="inlineStr">
+      <c r="I56" s="9" t="inlineStr"/>
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>Intense</t>
         </is>
       </c>
-      <c r="I54" s="9" t="inlineStr">
+      <c r="K56" s="9" t="inlineStr">
         <is>
           <t>Petit groupe</t>
         </is>
       </c>
-      <c r="J54" s="10" t="n">
+      <c r="L56" s="10" t="n">
         <v>60</v>
       </c>
-      <c r="K54" s="9" t="inlineStr">
+      <c r="M56" s="9" t="inlineStr">
         <is>
           <t>Hyrox</t>
         </is>
       </c>
-      <c r="L54" s="10" t="n"/>
-      <c r="M54" s="10" t="inlineStr"/>
-      <c r="N54" s="10" t="inlineStr"/>
-      <c r="O54" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="P54" s="10" t="inlineStr"/>
-      <c r="Q54" s="10" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
-      <c r="R54" s="10" t="inlineStr"/>
-      <c r="S54" s="10" t="inlineStr"/>
-      <c r="T54" s="10" t="inlineStr"/>
-      <c r="U54" s="10" t="inlineStr"/>
-      <c r="V54" s="10" t="inlineStr"/>
-      <c r="W54" s="11">
-        <f>IF(C54="","",IF(E54="","Type à choisir",IF(F54="","Objectif principal à choisir",IF(H54="","Intensité à choisir",IF(I54="","Format à choisir",IF(COUNTIF(M54:V54,"Cours co")+COUNTIF(M54:V54,"SGT")=0,"Aucun club coché",IF(E54=IF(COUNTIF(M54:V54,"Cours co")&gt;0,IF(COUNTIF(M54:V54,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X54" s="9" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="n"/>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="12" t="n"/>
-      <c r="H55" s="12" t="n"/>
-      <c r="I55" s="12" t="n"/>
-      <c r="J55" s="13" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="13" t="n"/>
-      <c r="M55" s="13" t="n"/>
-      <c r="N55" s="13" t="n"/>
-      <c r="O55" s="13" t="n"/>
-      <c r="P55" s="13" t="n"/>
-      <c r="Q55" s="13" t="n"/>
-      <c r="R55" s="13" t="n"/>
-      <c r="S55" s="13" t="n"/>
-      <c r="T55" s="13" t="n"/>
-      <c r="U55" s="13" t="n"/>
-      <c r="V55" s="13" t="n"/>
-      <c r="W55" s="11">
-        <f>IF(C55="","",IF(E55="","Type à choisir",IF(F55="","Objectif principal à choisir",IF(H55="","Intensité à choisir",IF(I55="","Format à choisir",IF(COUNTIF(M55:V55,"Cours co")+COUNTIF(M55:V55,"SGT")=0,"Aucun club coché",IF(E55=IF(COUNTIF(M55:V55,"Cours co")&gt;0,IF(COUNTIF(M55:V55,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X55" s="12" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="n"/>
-      <c r="B56" s="12" t="n"/>
-      <c r="C56" s="12" t="n"/>
-      <c r="D56" s="12" t="n"/>
-      <c r="E56" s="12" t="n"/>
-      <c r="F56" s="12" t="n"/>
-      <c r="G56" s="12" t="n"/>
-      <c r="H56" s="12" t="n"/>
-      <c r="I56" s="12" t="n"/>
-      <c r="J56" s="13" t="n"/>
-      <c r="K56" s="12" t="n"/>
-      <c r="L56" s="13" t="n"/>
-      <c r="M56" s="13" t="n"/>
-      <c r="N56" s="13" t="n"/>
-      <c r="O56" s="13" t="n"/>
-      <c r="P56" s="13" t="n"/>
-      <c r="Q56" s="13" t="n"/>
-      <c r="R56" s="13" t="n"/>
-      <c r="S56" s="13" t="n"/>
-      <c r="T56" s="13" t="n"/>
-      <c r="U56" s="13" t="n"/>
-      <c r="V56" s="13" t="n"/>
-      <c r="W56" s="11">
-        <f>IF(C56="","",IF(E56="","Type à choisir",IF(F56="","Objectif principal à choisir",IF(H56="","Intensité à choisir",IF(I56="","Format à choisir",IF(COUNTIF(M56:V56,"Cours co")+COUNTIF(M56:V56,"SGT")=0,"Aucun club coché",IF(E56=IF(COUNTIF(M56:V56,"Cours co")&gt;0,IF(COUNTIF(M56:V56,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X56" s="12" t="n"/>
+      <c r="N56" s="10" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="R56" s="10" t="n"/>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="T56" s="10" t="n"/>
+      <c r="U56" s="10" t="n"/>
+      <c r="V56" s="10" t="n"/>
+      <c r="W56" s="10" t="n"/>
+      <c r="X56" s="10" t="n"/>
+      <c r="Y56" s="11">
+        <f>IF(C56="","",IF(E56="","Type à choisir",IF(H56="","Objectif principal à choisir",IF(J56="","Intensité à choisir",IF(K56="","Format à choisir",IF(COUNTA(O56:X56)=0,"Aucun club coché",IF(AND(F56&lt;&gt;"",COUNTIF($A$2:$A$81,F56)=0),"Même cours que : identifiant inconnu",IF(AND(F56&lt;&gt;"",F56=A56),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z56" s="9" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="n"/>
@@ -4809,10 +5248,10 @@
       <c r="G57" s="12" t="n"/>
       <c r="H57" s="12" t="n"/>
       <c r="I57" s="12" t="n"/>
-      <c r="J57" s="13" t="n"/>
+      <c r="J57" s="12" t="n"/>
       <c r="K57" s="12" t="n"/>
       <c r="L57" s="13" t="n"/>
-      <c r="M57" s="13" t="n"/>
+      <c r="M57" s="12" t="n"/>
       <c r="N57" s="13" t="n"/>
       <c r="O57" s="13" t="n"/>
       <c r="P57" s="13" t="n"/>
@@ -4822,11 +5261,13 @@
       <c r="T57" s="13" t="n"/>
       <c r="U57" s="13" t="n"/>
       <c r="V57" s="13" t="n"/>
-      <c r="W57" s="11">
-        <f>IF(C57="","",IF(E57="","Type à choisir",IF(F57="","Objectif principal à choisir",IF(H57="","Intensité à choisir",IF(I57="","Format à choisir",IF(COUNTIF(M57:V57,"Cours co")+COUNTIF(M57:V57,"SGT")=0,"Aucun club coché",IF(E57=IF(COUNTIF(M57:V57,"Cours co")&gt;0,IF(COUNTIF(M57:V57,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X57" s="12" t="n"/>
+      <c r="W57" s="13" t="n"/>
+      <c r="X57" s="13" t="n"/>
+      <c r="Y57" s="11">
+        <f>IF(C57="","",IF(E57="","Type à choisir",IF(H57="","Objectif principal à choisir",IF(J57="","Intensité à choisir",IF(K57="","Format à choisir",IF(COUNTA(O57:X57)=0,"Aucun club coché",IF(AND(F57&lt;&gt;"",COUNTIF($A$2:$A$81,F57)=0),"Même cours que : identifiant inconnu",IF(AND(F57&lt;&gt;"",F57=A57),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z57" s="12" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="n"/>
@@ -4838,10 +5279,10 @@
       <c r="G58" s="12" t="n"/>
       <c r="H58" s="12" t="n"/>
       <c r="I58" s="12" t="n"/>
-      <c r="J58" s="13" t="n"/>
+      <c r="J58" s="12" t="n"/>
       <c r="K58" s="12" t="n"/>
       <c r="L58" s="13" t="n"/>
-      <c r="M58" s="13" t="n"/>
+      <c r="M58" s="12" t="n"/>
       <c r="N58" s="13" t="n"/>
       <c r="O58" s="13" t="n"/>
       <c r="P58" s="13" t="n"/>
@@ -4851,11 +5292,13 @@
       <c r="T58" s="13" t="n"/>
       <c r="U58" s="13" t="n"/>
       <c r="V58" s="13" t="n"/>
-      <c r="W58" s="11">
-        <f>IF(C58="","",IF(E58="","Type à choisir",IF(F58="","Objectif principal à choisir",IF(H58="","Intensité à choisir",IF(I58="","Format à choisir",IF(COUNTIF(M58:V58,"Cours co")+COUNTIF(M58:V58,"SGT")=0,"Aucun club coché",IF(E58=IF(COUNTIF(M58:V58,"Cours co")&gt;0,IF(COUNTIF(M58:V58,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X58" s="12" t="n"/>
+      <c r="W58" s="13" t="n"/>
+      <c r="X58" s="13" t="n"/>
+      <c r="Y58" s="11">
+        <f>IF(C58="","",IF(E58="","Type à choisir",IF(H58="","Objectif principal à choisir",IF(J58="","Intensité à choisir",IF(K58="","Format à choisir",IF(COUNTA(O58:X58)=0,"Aucun club coché",IF(AND(F58&lt;&gt;"",COUNTIF($A$2:$A$81,F58)=0),"Même cours que : identifiant inconnu",IF(AND(F58&lt;&gt;"",F58=A58),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z58" s="12" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="n"/>
@@ -4867,10 +5310,10 @@
       <c r="G59" s="12" t="n"/>
       <c r="H59" s="12" t="n"/>
       <c r="I59" s="12" t="n"/>
-      <c r="J59" s="13" t="n"/>
+      <c r="J59" s="12" t="n"/>
       <c r="K59" s="12" t="n"/>
       <c r="L59" s="13" t="n"/>
-      <c r="M59" s="13" t="n"/>
+      <c r="M59" s="12" t="n"/>
       <c r="N59" s="13" t="n"/>
       <c r="O59" s="13" t="n"/>
       <c r="P59" s="13" t="n"/>
@@ -4880,11 +5323,13 @@
       <c r="T59" s="13" t="n"/>
       <c r="U59" s="13" t="n"/>
       <c r="V59" s="13" t="n"/>
-      <c r="W59" s="11">
-        <f>IF(C59="","",IF(E59="","Type à choisir",IF(F59="","Objectif principal à choisir",IF(H59="","Intensité à choisir",IF(I59="","Format à choisir",IF(COUNTIF(M59:V59,"Cours co")+COUNTIF(M59:V59,"SGT")=0,"Aucun club coché",IF(E59=IF(COUNTIF(M59:V59,"Cours co")&gt;0,IF(COUNTIF(M59:V59,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X59" s="12" t="n"/>
+      <c r="W59" s="13" t="n"/>
+      <c r="X59" s="13" t="n"/>
+      <c r="Y59" s="11">
+        <f>IF(C59="","",IF(E59="","Type à choisir",IF(H59="","Objectif principal à choisir",IF(J59="","Intensité à choisir",IF(K59="","Format à choisir",IF(COUNTA(O59:X59)=0,"Aucun club coché",IF(AND(F59&lt;&gt;"",COUNTIF($A$2:$A$81,F59)=0),"Même cours que : identifiant inconnu",IF(AND(F59&lt;&gt;"",F59=A59),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z59" s="12" t="n"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="n"/>
@@ -4896,10 +5341,10 @@
       <c r="G60" s="12" t="n"/>
       <c r="H60" s="12" t="n"/>
       <c r="I60" s="12" t="n"/>
-      <c r="J60" s="13" t="n"/>
+      <c r="J60" s="12" t="n"/>
       <c r="K60" s="12" t="n"/>
       <c r="L60" s="13" t="n"/>
-      <c r="M60" s="13" t="n"/>
+      <c r="M60" s="12" t="n"/>
       <c r="N60" s="13" t="n"/>
       <c r="O60" s="13" t="n"/>
       <c r="P60" s="13" t="n"/>
@@ -4909,11 +5354,13 @@
       <c r="T60" s="13" t="n"/>
       <c r="U60" s="13" t="n"/>
       <c r="V60" s="13" t="n"/>
-      <c r="W60" s="11">
-        <f>IF(C60="","",IF(E60="","Type à choisir",IF(F60="","Objectif principal à choisir",IF(H60="","Intensité à choisir",IF(I60="","Format à choisir",IF(COUNTIF(M60:V60,"Cours co")+COUNTIF(M60:V60,"SGT")=0,"Aucun club coché",IF(E60=IF(COUNTIF(M60:V60,"Cours co")&gt;0,IF(COUNTIF(M60:V60,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X60" s="12" t="n"/>
+      <c r="W60" s="13" t="n"/>
+      <c r="X60" s="13" t="n"/>
+      <c r="Y60" s="11">
+        <f>IF(C60="","",IF(E60="","Type à choisir",IF(H60="","Objectif principal à choisir",IF(J60="","Intensité à choisir",IF(K60="","Format à choisir",IF(COUNTA(O60:X60)=0,"Aucun club coché",IF(AND(F60&lt;&gt;"",COUNTIF($A$2:$A$81,F60)=0),"Même cours que : identifiant inconnu",IF(AND(F60&lt;&gt;"",F60=A60),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z60" s="12" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="n"/>
@@ -4925,10 +5372,10 @@
       <c r="G61" s="12" t="n"/>
       <c r="H61" s="12" t="n"/>
       <c r="I61" s="12" t="n"/>
-      <c r="J61" s="13" t="n"/>
+      <c r="J61" s="12" t="n"/>
       <c r="K61" s="12" t="n"/>
       <c r="L61" s="13" t="n"/>
-      <c r="M61" s="13" t="n"/>
+      <c r="M61" s="12" t="n"/>
       <c r="N61" s="13" t="n"/>
       <c r="O61" s="13" t="n"/>
       <c r="P61" s="13" t="n"/>
@@ -4938,11 +5385,13 @@
       <c r="T61" s="13" t="n"/>
       <c r="U61" s="13" t="n"/>
       <c r="V61" s="13" t="n"/>
-      <c r="W61" s="11">
-        <f>IF(C61="","",IF(E61="","Type à choisir",IF(F61="","Objectif principal à choisir",IF(H61="","Intensité à choisir",IF(I61="","Format à choisir",IF(COUNTIF(M61:V61,"Cours co")+COUNTIF(M61:V61,"SGT")=0,"Aucun club coché",IF(E61=IF(COUNTIF(M61:V61,"Cours co")&gt;0,IF(COUNTIF(M61:V61,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X61" s="12" t="n"/>
+      <c r="W61" s="13" t="n"/>
+      <c r="X61" s="13" t="n"/>
+      <c r="Y61" s="11">
+        <f>IF(C61="","",IF(E61="","Type à choisir",IF(H61="","Objectif principal à choisir",IF(J61="","Intensité à choisir",IF(K61="","Format à choisir",IF(COUNTA(O61:X61)=0,"Aucun club coché",IF(AND(F61&lt;&gt;"",COUNTIF($A$2:$A$81,F61)=0),"Même cours que : identifiant inconnu",IF(AND(F61&lt;&gt;"",F61=A61),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z61" s="12" t="n"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="n"/>
@@ -4954,10 +5403,10 @@
       <c r="G62" s="12" t="n"/>
       <c r="H62" s="12" t="n"/>
       <c r="I62" s="12" t="n"/>
-      <c r="J62" s="13" t="n"/>
+      <c r="J62" s="12" t="n"/>
       <c r="K62" s="12" t="n"/>
       <c r="L62" s="13" t="n"/>
-      <c r="M62" s="13" t="n"/>
+      <c r="M62" s="12" t="n"/>
       <c r="N62" s="13" t="n"/>
       <c r="O62" s="13" t="n"/>
       <c r="P62" s="13" t="n"/>
@@ -4967,11 +5416,13 @@
       <c r="T62" s="13" t="n"/>
       <c r="U62" s="13" t="n"/>
       <c r="V62" s="13" t="n"/>
-      <c r="W62" s="11">
-        <f>IF(C62="","",IF(E62="","Type à choisir",IF(F62="","Objectif principal à choisir",IF(H62="","Intensité à choisir",IF(I62="","Format à choisir",IF(COUNTIF(M62:V62,"Cours co")+COUNTIF(M62:V62,"SGT")=0,"Aucun club coché",IF(E62=IF(COUNTIF(M62:V62,"Cours co")&gt;0,IF(COUNTIF(M62:V62,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X62" s="12" t="n"/>
+      <c r="W62" s="13" t="n"/>
+      <c r="X62" s="13" t="n"/>
+      <c r="Y62" s="11">
+        <f>IF(C62="","",IF(E62="","Type à choisir",IF(H62="","Objectif principal à choisir",IF(J62="","Intensité à choisir",IF(K62="","Format à choisir",IF(COUNTA(O62:X62)=0,"Aucun club coché",IF(AND(F62&lt;&gt;"",COUNTIF($A$2:$A$81,F62)=0),"Même cours que : identifiant inconnu",IF(AND(F62&lt;&gt;"",F62=A62),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z62" s="12" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="n"/>
@@ -4983,10 +5434,10 @@
       <c r="G63" s="12" t="n"/>
       <c r="H63" s="12" t="n"/>
       <c r="I63" s="12" t="n"/>
-      <c r="J63" s="13" t="n"/>
+      <c r="J63" s="12" t="n"/>
       <c r="K63" s="12" t="n"/>
       <c r="L63" s="13" t="n"/>
-      <c r="M63" s="13" t="n"/>
+      <c r="M63" s="12" t="n"/>
       <c r="N63" s="13" t="n"/>
       <c r="O63" s="13" t="n"/>
       <c r="P63" s="13" t="n"/>
@@ -4996,11 +5447,13 @@
       <c r="T63" s="13" t="n"/>
       <c r="U63" s="13" t="n"/>
       <c r="V63" s="13" t="n"/>
-      <c r="W63" s="11">
-        <f>IF(C63="","",IF(E63="","Type à choisir",IF(F63="","Objectif principal à choisir",IF(H63="","Intensité à choisir",IF(I63="","Format à choisir",IF(COUNTIF(M63:V63,"Cours co")+COUNTIF(M63:V63,"SGT")=0,"Aucun club coché",IF(E63=IF(COUNTIF(M63:V63,"Cours co")&gt;0,IF(COUNTIF(M63:V63,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X63" s="12" t="n"/>
+      <c r="W63" s="13" t="n"/>
+      <c r="X63" s="13" t="n"/>
+      <c r="Y63" s="11">
+        <f>IF(C63="","",IF(E63="","Type à choisir",IF(H63="","Objectif principal à choisir",IF(J63="","Intensité à choisir",IF(K63="","Format à choisir",IF(COUNTA(O63:X63)=0,"Aucun club coché",IF(AND(F63&lt;&gt;"",COUNTIF($A$2:$A$81,F63)=0),"Même cours que : identifiant inconnu",IF(AND(F63&lt;&gt;"",F63=A63),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z63" s="12" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="n"/>
@@ -5012,10 +5465,10 @@
       <c r="G64" s="12" t="n"/>
       <c r="H64" s="12" t="n"/>
       <c r="I64" s="12" t="n"/>
-      <c r="J64" s="13" t="n"/>
+      <c r="J64" s="12" t="n"/>
       <c r="K64" s="12" t="n"/>
       <c r="L64" s="13" t="n"/>
-      <c r="M64" s="13" t="n"/>
+      <c r="M64" s="12" t="n"/>
       <c r="N64" s="13" t="n"/>
       <c r="O64" s="13" t="n"/>
       <c r="P64" s="13" t="n"/>
@@ -5025,11 +5478,13 @@
       <c r="T64" s="13" t="n"/>
       <c r="U64" s="13" t="n"/>
       <c r="V64" s="13" t="n"/>
-      <c r="W64" s="11">
-        <f>IF(C64="","",IF(E64="","Type à choisir",IF(F64="","Objectif principal à choisir",IF(H64="","Intensité à choisir",IF(I64="","Format à choisir",IF(COUNTIF(M64:V64,"Cours co")+COUNTIF(M64:V64,"SGT")=0,"Aucun club coché",IF(E64=IF(COUNTIF(M64:V64,"Cours co")&gt;0,IF(COUNTIF(M64:V64,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X64" s="12" t="n"/>
+      <c r="W64" s="13" t="n"/>
+      <c r="X64" s="13" t="n"/>
+      <c r="Y64" s="11">
+        <f>IF(C64="","",IF(E64="","Type à choisir",IF(H64="","Objectif principal à choisir",IF(J64="","Intensité à choisir",IF(K64="","Format à choisir",IF(COUNTA(O64:X64)=0,"Aucun club coché",IF(AND(F64&lt;&gt;"",COUNTIF($A$2:$A$81,F64)=0),"Même cours que : identifiant inconnu",IF(AND(F64&lt;&gt;"",F64=A64),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z64" s="12" t="n"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="n"/>
@@ -5041,10 +5496,10 @@
       <c r="G65" s="12" t="n"/>
       <c r="H65" s="12" t="n"/>
       <c r="I65" s="12" t="n"/>
-      <c r="J65" s="13" t="n"/>
+      <c r="J65" s="12" t="n"/>
       <c r="K65" s="12" t="n"/>
       <c r="L65" s="13" t="n"/>
-      <c r="M65" s="13" t="n"/>
+      <c r="M65" s="12" t="n"/>
       <c r="N65" s="13" t="n"/>
       <c r="O65" s="13" t="n"/>
       <c r="P65" s="13" t="n"/>
@@ -5054,11 +5509,13 @@
       <c r="T65" s="13" t="n"/>
       <c r="U65" s="13" t="n"/>
       <c r="V65" s="13" t="n"/>
-      <c r="W65" s="11">
-        <f>IF(C65="","",IF(E65="","Type à choisir",IF(F65="","Objectif principal à choisir",IF(H65="","Intensité à choisir",IF(I65="","Format à choisir",IF(COUNTIF(M65:V65,"Cours co")+COUNTIF(M65:V65,"SGT")=0,"Aucun club coché",IF(E65=IF(COUNTIF(M65:V65,"Cours co")&gt;0,IF(COUNTIF(M65:V65,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X65" s="12" t="n"/>
+      <c r="W65" s="13" t="n"/>
+      <c r="X65" s="13" t="n"/>
+      <c r="Y65" s="11">
+        <f>IF(C65="","",IF(E65="","Type à choisir",IF(H65="","Objectif principal à choisir",IF(J65="","Intensité à choisir",IF(K65="","Format à choisir",IF(COUNTA(O65:X65)=0,"Aucun club coché",IF(AND(F65&lt;&gt;"",COUNTIF($A$2:$A$81,F65)=0),"Même cours que : identifiant inconnu",IF(AND(F65&lt;&gt;"",F65=A65),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z65" s="12" t="n"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="n"/>
@@ -5070,10 +5527,10 @@
       <c r="G66" s="12" t="n"/>
       <c r="H66" s="12" t="n"/>
       <c r="I66" s="12" t="n"/>
-      <c r="J66" s="13" t="n"/>
+      <c r="J66" s="12" t="n"/>
       <c r="K66" s="12" t="n"/>
       <c r="L66" s="13" t="n"/>
-      <c r="M66" s="13" t="n"/>
+      <c r="M66" s="12" t="n"/>
       <c r="N66" s="13" t="n"/>
       <c r="O66" s="13" t="n"/>
       <c r="P66" s="13" t="n"/>
@@ -5083,11 +5540,13 @@
       <c r="T66" s="13" t="n"/>
       <c r="U66" s="13" t="n"/>
       <c r="V66" s="13" t="n"/>
-      <c r="W66" s="11">
-        <f>IF(C66="","",IF(E66="","Type à choisir",IF(F66="","Objectif principal à choisir",IF(H66="","Intensité à choisir",IF(I66="","Format à choisir",IF(COUNTIF(M66:V66,"Cours co")+COUNTIF(M66:V66,"SGT")=0,"Aucun club coché",IF(E66=IF(COUNTIF(M66:V66,"Cours co")&gt;0,IF(COUNTIF(M66:V66,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X66" s="12" t="n"/>
+      <c r="W66" s="13" t="n"/>
+      <c r="X66" s="13" t="n"/>
+      <c r="Y66" s="11">
+        <f>IF(C66="","",IF(E66="","Type à choisir",IF(H66="","Objectif principal à choisir",IF(J66="","Intensité à choisir",IF(K66="","Format à choisir",IF(COUNTA(O66:X66)=0,"Aucun club coché",IF(AND(F66&lt;&gt;"",COUNTIF($A$2:$A$81,F66)=0),"Même cours que : identifiant inconnu",IF(AND(F66&lt;&gt;"",F66=A66),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z66" s="12" t="n"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="n"/>
@@ -5099,10 +5558,10 @@
       <c r="G67" s="12" t="n"/>
       <c r="H67" s="12" t="n"/>
       <c r="I67" s="12" t="n"/>
-      <c r="J67" s="13" t="n"/>
+      <c r="J67" s="12" t="n"/>
       <c r="K67" s="12" t="n"/>
       <c r="L67" s="13" t="n"/>
-      <c r="M67" s="13" t="n"/>
+      <c r="M67" s="12" t="n"/>
       <c r="N67" s="13" t="n"/>
       <c r="O67" s="13" t="n"/>
       <c r="P67" s="13" t="n"/>
@@ -5112,11 +5571,13 @@
       <c r="T67" s="13" t="n"/>
       <c r="U67" s="13" t="n"/>
       <c r="V67" s="13" t="n"/>
-      <c r="W67" s="11">
-        <f>IF(C67="","",IF(E67="","Type à choisir",IF(F67="","Objectif principal à choisir",IF(H67="","Intensité à choisir",IF(I67="","Format à choisir",IF(COUNTIF(M67:V67,"Cours co")+COUNTIF(M67:V67,"SGT")=0,"Aucun club coché",IF(E67=IF(COUNTIF(M67:V67,"Cours co")&gt;0,IF(COUNTIF(M67:V67,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X67" s="12" t="n"/>
+      <c r="W67" s="13" t="n"/>
+      <c r="X67" s="13" t="n"/>
+      <c r="Y67" s="11">
+        <f>IF(C67="","",IF(E67="","Type à choisir",IF(H67="","Objectif principal à choisir",IF(J67="","Intensité à choisir",IF(K67="","Format à choisir",IF(COUNTA(O67:X67)=0,"Aucun club coché",IF(AND(F67&lt;&gt;"",COUNTIF($A$2:$A$81,F67)=0),"Même cours que : identifiant inconnu",IF(AND(F67&lt;&gt;"",F67=A67),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z67" s="12" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="n"/>
@@ -5128,10 +5589,10 @@
       <c r="G68" s="12" t="n"/>
       <c r="H68" s="12" t="n"/>
       <c r="I68" s="12" t="n"/>
-      <c r="J68" s="13" t="n"/>
+      <c r="J68" s="12" t="n"/>
       <c r="K68" s="12" t="n"/>
       <c r="L68" s="13" t="n"/>
-      <c r="M68" s="13" t="n"/>
+      <c r="M68" s="12" t="n"/>
       <c r="N68" s="13" t="n"/>
       <c r="O68" s="13" t="n"/>
       <c r="P68" s="13" t="n"/>
@@ -5141,11 +5602,13 @@
       <c r="T68" s="13" t="n"/>
       <c r="U68" s="13" t="n"/>
       <c r="V68" s="13" t="n"/>
-      <c r="W68" s="11">
-        <f>IF(C68="","",IF(E68="","Type à choisir",IF(F68="","Objectif principal à choisir",IF(H68="","Intensité à choisir",IF(I68="","Format à choisir",IF(COUNTIF(M68:V68,"Cours co")+COUNTIF(M68:V68,"SGT")=0,"Aucun club coché",IF(E68=IF(COUNTIF(M68:V68,"Cours co")&gt;0,IF(COUNTIF(M68:V68,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X68" s="12" t="n"/>
+      <c r="W68" s="13" t="n"/>
+      <c r="X68" s="13" t="n"/>
+      <c r="Y68" s="11">
+        <f>IF(C68="","",IF(E68="","Type à choisir",IF(H68="","Objectif principal à choisir",IF(J68="","Intensité à choisir",IF(K68="","Format à choisir",IF(COUNTA(O68:X68)=0,"Aucun club coché",IF(AND(F68&lt;&gt;"",COUNTIF($A$2:$A$81,F68)=0),"Même cours que : identifiant inconnu",IF(AND(F68&lt;&gt;"",F68=A68),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z68" s="12" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="n"/>
@@ -5157,10 +5620,10 @@
       <c r="G69" s="12" t="n"/>
       <c r="H69" s="12" t="n"/>
       <c r="I69" s="12" t="n"/>
-      <c r="J69" s="13" t="n"/>
+      <c r="J69" s="12" t="n"/>
       <c r="K69" s="12" t="n"/>
       <c r="L69" s="13" t="n"/>
-      <c r="M69" s="13" t="n"/>
+      <c r="M69" s="12" t="n"/>
       <c r="N69" s="13" t="n"/>
       <c r="O69" s="13" t="n"/>
       <c r="P69" s="13" t="n"/>
@@ -5170,11 +5633,13 @@
       <c r="T69" s="13" t="n"/>
       <c r="U69" s="13" t="n"/>
       <c r="V69" s="13" t="n"/>
-      <c r="W69" s="11">
-        <f>IF(C69="","",IF(E69="","Type à choisir",IF(F69="","Objectif principal à choisir",IF(H69="","Intensité à choisir",IF(I69="","Format à choisir",IF(COUNTIF(M69:V69,"Cours co")+COUNTIF(M69:V69,"SGT")=0,"Aucun club coché",IF(E69=IF(COUNTIF(M69:V69,"Cours co")&gt;0,IF(COUNTIF(M69:V69,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X69" s="12" t="n"/>
+      <c r="W69" s="13" t="n"/>
+      <c r="X69" s="13" t="n"/>
+      <c r="Y69" s="11">
+        <f>IF(C69="","",IF(E69="","Type à choisir",IF(H69="","Objectif principal à choisir",IF(J69="","Intensité à choisir",IF(K69="","Format à choisir",IF(COUNTA(O69:X69)=0,"Aucun club coché",IF(AND(F69&lt;&gt;"",COUNTIF($A$2:$A$81,F69)=0),"Même cours que : identifiant inconnu",IF(AND(F69&lt;&gt;"",F69=A69),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z69" s="12" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="n"/>
@@ -5186,10 +5651,10 @@
       <c r="G70" s="12" t="n"/>
       <c r="H70" s="12" t="n"/>
       <c r="I70" s="12" t="n"/>
-      <c r="J70" s="13" t="n"/>
+      <c r="J70" s="12" t="n"/>
       <c r="K70" s="12" t="n"/>
       <c r="L70" s="13" t="n"/>
-      <c r="M70" s="13" t="n"/>
+      <c r="M70" s="12" t="n"/>
       <c r="N70" s="13" t="n"/>
       <c r="O70" s="13" t="n"/>
       <c r="P70" s="13" t="n"/>
@@ -5199,11 +5664,13 @@
       <c r="T70" s="13" t="n"/>
       <c r="U70" s="13" t="n"/>
       <c r="V70" s="13" t="n"/>
-      <c r="W70" s="11">
-        <f>IF(C70="","",IF(E70="","Type à choisir",IF(F70="","Objectif principal à choisir",IF(H70="","Intensité à choisir",IF(I70="","Format à choisir",IF(COUNTIF(M70:V70,"Cours co")+COUNTIF(M70:V70,"SGT")=0,"Aucun club coché",IF(E70=IF(COUNTIF(M70:V70,"Cours co")&gt;0,IF(COUNTIF(M70:V70,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X70" s="12" t="n"/>
+      <c r="W70" s="13" t="n"/>
+      <c r="X70" s="13" t="n"/>
+      <c r="Y70" s="11">
+        <f>IF(C70="","",IF(E70="","Type à choisir",IF(H70="","Objectif principal à choisir",IF(J70="","Intensité à choisir",IF(K70="","Format à choisir",IF(COUNTA(O70:X70)=0,"Aucun club coché",IF(AND(F70&lt;&gt;"",COUNTIF($A$2:$A$81,F70)=0),"Même cours que : identifiant inconnu",IF(AND(F70&lt;&gt;"",F70=A70),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z70" s="12" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="n"/>
@@ -5215,10 +5682,10 @@
       <c r="G71" s="12" t="n"/>
       <c r="H71" s="12" t="n"/>
       <c r="I71" s="12" t="n"/>
-      <c r="J71" s="13" t="n"/>
+      <c r="J71" s="12" t="n"/>
       <c r="K71" s="12" t="n"/>
       <c r="L71" s="13" t="n"/>
-      <c r="M71" s="13" t="n"/>
+      <c r="M71" s="12" t="n"/>
       <c r="N71" s="13" t="n"/>
       <c r="O71" s="13" t="n"/>
       <c r="P71" s="13" t="n"/>
@@ -5228,11 +5695,13 @@
       <c r="T71" s="13" t="n"/>
       <c r="U71" s="13" t="n"/>
       <c r="V71" s="13" t="n"/>
-      <c r="W71" s="11">
-        <f>IF(C71="","",IF(E71="","Type à choisir",IF(F71="","Objectif principal à choisir",IF(H71="","Intensité à choisir",IF(I71="","Format à choisir",IF(COUNTIF(M71:V71,"Cours co")+COUNTIF(M71:V71,"SGT")=0,"Aucun club coché",IF(E71=IF(COUNTIF(M71:V71,"Cours co")&gt;0,IF(COUNTIF(M71:V71,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X71" s="12" t="n"/>
+      <c r="W71" s="13" t="n"/>
+      <c r="X71" s="13" t="n"/>
+      <c r="Y71" s="11">
+        <f>IF(C71="","",IF(E71="","Type à choisir",IF(H71="","Objectif principal à choisir",IF(J71="","Intensité à choisir",IF(K71="","Format à choisir",IF(COUNTA(O71:X71)=0,"Aucun club coché",IF(AND(F71&lt;&gt;"",COUNTIF($A$2:$A$81,F71)=0),"Même cours que : identifiant inconnu",IF(AND(F71&lt;&gt;"",F71=A71),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z71" s="12" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="n"/>
@@ -5244,10 +5713,10 @@
       <c r="G72" s="12" t="n"/>
       <c r="H72" s="12" t="n"/>
       <c r="I72" s="12" t="n"/>
-      <c r="J72" s="13" t="n"/>
+      <c r="J72" s="12" t="n"/>
       <c r="K72" s="12" t="n"/>
       <c r="L72" s="13" t="n"/>
-      <c r="M72" s="13" t="n"/>
+      <c r="M72" s="12" t="n"/>
       <c r="N72" s="13" t="n"/>
       <c r="O72" s="13" t="n"/>
       <c r="P72" s="13" t="n"/>
@@ -5257,11 +5726,13 @@
       <c r="T72" s="13" t="n"/>
       <c r="U72" s="13" t="n"/>
       <c r="V72" s="13" t="n"/>
-      <c r="W72" s="11">
-        <f>IF(C72="","",IF(E72="","Type à choisir",IF(F72="","Objectif principal à choisir",IF(H72="","Intensité à choisir",IF(I72="","Format à choisir",IF(COUNTIF(M72:V72,"Cours co")+COUNTIF(M72:V72,"SGT")=0,"Aucun club coché",IF(E72=IF(COUNTIF(M72:V72,"Cours co")&gt;0,IF(COUNTIF(M72:V72,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X72" s="12" t="n"/>
+      <c r="W72" s="13" t="n"/>
+      <c r="X72" s="13" t="n"/>
+      <c r="Y72" s="11">
+        <f>IF(C72="","",IF(E72="","Type à choisir",IF(H72="","Objectif principal à choisir",IF(J72="","Intensité à choisir",IF(K72="","Format à choisir",IF(COUNTA(O72:X72)=0,"Aucun club coché",IF(AND(F72&lt;&gt;"",COUNTIF($A$2:$A$81,F72)=0),"Même cours que : identifiant inconnu",IF(AND(F72&lt;&gt;"",F72=A72),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z72" s="12" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="8" t="n"/>
@@ -5273,10 +5744,10 @@
       <c r="G73" s="12" t="n"/>
       <c r="H73" s="12" t="n"/>
       <c r="I73" s="12" t="n"/>
-      <c r="J73" s="13" t="n"/>
+      <c r="J73" s="12" t="n"/>
       <c r="K73" s="12" t="n"/>
       <c r="L73" s="13" t="n"/>
-      <c r="M73" s="13" t="n"/>
+      <c r="M73" s="12" t="n"/>
       <c r="N73" s="13" t="n"/>
       <c r="O73" s="13" t="n"/>
       <c r="P73" s="13" t="n"/>
@@ -5286,11 +5757,13 @@
       <c r="T73" s="13" t="n"/>
       <c r="U73" s="13" t="n"/>
       <c r="V73" s="13" t="n"/>
-      <c r="W73" s="11">
-        <f>IF(C73="","",IF(E73="","Type à choisir",IF(F73="","Objectif principal à choisir",IF(H73="","Intensité à choisir",IF(I73="","Format à choisir",IF(COUNTIF(M73:V73,"Cours co")+COUNTIF(M73:V73,"SGT")=0,"Aucun club coché",IF(E73=IF(COUNTIF(M73:V73,"Cours co")&gt;0,IF(COUNTIF(M73:V73,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X73" s="12" t="n"/>
+      <c r="W73" s="13" t="n"/>
+      <c r="X73" s="13" t="n"/>
+      <c r="Y73" s="11">
+        <f>IF(C73="","",IF(E73="","Type à choisir",IF(H73="","Objectif principal à choisir",IF(J73="","Intensité à choisir",IF(K73="","Format à choisir",IF(COUNTA(O73:X73)=0,"Aucun club coché",IF(AND(F73&lt;&gt;"",COUNTIF($A$2:$A$81,F73)=0),"Même cours que : identifiant inconnu",IF(AND(F73&lt;&gt;"",F73=A73),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z73" s="12" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="8" t="n"/>
@@ -5302,10 +5775,10 @@
       <c r="G74" s="12" t="n"/>
       <c r="H74" s="12" t="n"/>
       <c r="I74" s="12" t="n"/>
-      <c r="J74" s="13" t="n"/>
+      <c r="J74" s="12" t="n"/>
       <c r="K74" s="12" t="n"/>
       <c r="L74" s="13" t="n"/>
-      <c r="M74" s="13" t="n"/>
+      <c r="M74" s="12" t="n"/>
       <c r="N74" s="13" t="n"/>
       <c r="O74" s="13" t="n"/>
       <c r="P74" s="13" t="n"/>
@@ -5315,11 +5788,13 @@
       <c r="T74" s="13" t="n"/>
       <c r="U74" s="13" t="n"/>
       <c r="V74" s="13" t="n"/>
-      <c r="W74" s="11">
-        <f>IF(C74="","",IF(E74="","Type à choisir",IF(F74="","Objectif principal à choisir",IF(H74="","Intensité à choisir",IF(I74="","Format à choisir",IF(COUNTIF(M74:V74,"Cours co")+COUNTIF(M74:V74,"SGT")=0,"Aucun club coché",IF(E74=IF(COUNTIF(M74:V74,"Cours co")&gt;0,IF(COUNTIF(M74:V74,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X74" s="12" t="n"/>
+      <c r="W74" s="13" t="n"/>
+      <c r="X74" s="13" t="n"/>
+      <c r="Y74" s="11">
+        <f>IF(C74="","",IF(E74="","Type à choisir",IF(H74="","Objectif principal à choisir",IF(J74="","Intensité à choisir",IF(K74="","Format à choisir",IF(COUNTA(O74:X74)=0,"Aucun club coché",IF(AND(F74&lt;&gt;"",COUNTIF($A$2:$A$81,F74)=0),"Même cours que : identifiant inconnu",IF(AND(F74&lt;&gt;"",F74=A74),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z74" s="12" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="8" t="n"/>
@@ -5331,10 +5806,10 @@
       <c r="G75" s="12" t="n"/>
       <c r="H75" s="12" t="n"/>
       <c r="I75" s="12" t="n"/>
-      <c r="J75" s="13" t="n"/>
+      <c r="J75" s="12" t="n"/>
       <c r="K75" s="12" t="n"/>
       <c r="L75" s="13" t="n"/>
-      <c r="M75" s="13" t="n"/>
+      <c r="M75" s="12" t="n"/>
       <c r="N75" s="13" t="n"/>
       <c r="O75" s="13" t="n"/>
       <c r="P75" s="13" t="n"/>
@@ -5344,11 +5819,13 @@
       <c r="T75" s="13" t="n"/>
       <c r="U75" s="13" t="n"/>
       <c r="V75" s="13" t="n"/>
-      <c r="W75" s="11">
-        <f>IF(C75="","",IF(E75="","Type à choisir",IF(F75="","Objectif principal à choisir",IF(H75="","Intensité à choisir",IF(I75="","Format à choisir",IF(COUNTIF(M75:V75,"Cours co")+COUNTIF(M75:V75,"SGT")=0,"Aucun club coché",IF(E75=IF(COUNTIF(M75:V75,"Cours co")&gt;0,IF(COUNTIF(M75:V75,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X75" s="12" t="n"/>
+      <c r="W75" s="13" t="n"/>
+      <c r="X75" s="13" t="n"/>
+      <c r="Y75" s="11">
+        <f>IF(C75="","",IF(E75="","Type à choisir",IF(H75="","Objectif principal à choisir",IF(J75="","Intensité à choisir",IF(K75="","Format à choisir",IF(COUNTA(O75:X75)=0,"Aucun club coché",IF(AND(F75&lt;&gt;"",COUNTIF($A$2:$A$81,F75)=0),"Même cours que : identifiant inconnu",IF(AND(F75&lt;&gt;"",F75=A75),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z75" s="12" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="8" t="n"/>
@@ -5360,10 +5837,10 @@
       <c r="G76" s="12" t="n"/>
       <c r="H76" s="12" t="n"/>
       <c r="I76" s="12" t="n"/>
-      <c r="J76" s="13" t="n"/>
+      <c r="J76" s="12" t="n"/>
       <c r="K76" s="12" t="n"/>
       <c r="L76" s="13" t="n"/>
-      <c r="M76" s="13" t="n"/>
+      <c r="M76" s="12" t="n"/>
       <c r="N76" s="13" t="n"/>
       <c r="O76" s="13" t="n"/>
       <c r="P76" s="13" t="n"/>
@@ -5373,11 +5850,13 @@
       <c r="T76" s="13" t="n"/>
       <c r="U76" s="13" t="n"/>
       <c r="V76" s="13" t="n"/>
-      <c r="W76" s="11">
-        <f>IF(C76="","",IF(E76="","Type à choisir",IF(F76="","Objectif principal à choisir",IF(H76="","Intensité à choisir",IF(I76="","Format à choisir",IF(COUNTIF(M76:V76,"Cours co")+COUNTIF(M76:V76,"SGT")=0,"Aucun club coché",IF(E76=IF(COUNTIF(M76:V76,"Cours co")&gt;0,IF(COUNTIF(M76:V76,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X76" s="12" t="n"/>
+      <c r="W76" s="13" t="n"/>
+      <c r="X76" s="13" t="n"/>
+      <c r="Y76" s="11">
+        <f>IF(C76="","",IF(E76="","Type à choisir",IF(H76="","Objectif principal à choisir",IF(J76="","Intensité à choisir",IF(K76="","Format à choisir",IF(COUNTA(O76:X76)=0,"Aucun club coché",IF(AND(F76&lt;&gt;"",COUNTIF($A$2:$A$81,F76)=0),"Même cours que : identifiant inconnu",IF(AND(F76&lt;&gt;"",F76=A76),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z76" s="12" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="8" t="n"/>
@@ -5389,10 +5868,10 @@
       <c r="G77" s="12" t="n"/>
       <c r="H77" s="12" t="n"/>
       <c r="I77" s="12" t="n"/>
-      <c r="J77" s="13" t="n"/>
+      <c r="J77" s="12" t="n"/>
       <c r="K77" s="12" t="n"/>
       <c r="L77" s="13" t="n"/>
-      <c r="M77" s="13" t="n"/>
+      <c r="M77" s="12" t="n"/>
       <c r="N77" s="13" t="n"/>
       <c r="O77" s="13" t="n"/>
       <c r="P77" s="13" t="n"/>
@@ -5402,11 +5881,13 @@
       <c r="T77" s="13" t="n"/>
       <c r="U77" s="13" t="n"/>
       <c r="V77" s="13" t="n"/>
-      <c r="W77" s="11">
-        <f>IF(C77="","",IF(E77="","Type à choisir",IF(F77="","Objectif principal à choisir",IF(H77="","Intensité à choisir",IF(I77="","Format à choisir",IF(COUNTIF(M77:V77,"Cours co")+COUNTIF(M77:V77,"SGT")=0,"Aucun club coché",IF(E77=IF(COUNTIF(M77:V77,"Cours co")&gt;0,IF(COUNTIF(M77:V77,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X77" s="12" t="n"/>
+      <c r="W77" s="13" t="n"/>
+      <c r="X77" s="13" t="n"/>
+      <c r="Y77" s="11">
+        <f>IF(C77="","",IF(E77="","Type à choisir",IF(H77="","Objectif principal à choisir",IF(J77="","Intensité à choisir",IF(K77="","Format à choisir",IF(COUNTA(O77:X77)=0,"Aucun club coché",IF(AND(F77&lt;&gt;"",COUNTIF($A$2:$A$81,F77)=0),"Même cours que : identifiant inconnu",IF(AND(F77&lt;&gt;"",F77=A77),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z77" s="12" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="8" t="n"/>
@@ -5418,10 +5899,10 @@
       <c r="G78" s="12" t="n"/>
       <c r="H78" s="12" t="n"/>
       <c r="I78" s="12" t="n"/>
-      <c r="J78" s="13" t="n"/>
+      <c r="J78" s="12" t="n"/>
       <c r="K78" s="12" t="n"/>
       <c r="L78" s="13" t="n"/>
-      <c r="M78" s="13" t="n"/>
+      <c r="M78" s="12" t="n"/>
       <c r="N78" s="13" t="n"/>
       <c r="O78" s="13" t="n"/>
       <c r="P78" s="13" t="n"/>
@@ -5431,11 +5912,13 @@
       <c r="T78" s="13" t="n"/>
       <c r="U78" s="13" t="n"/>
       <c r="V78" s="13" t="n"/>
-      <c r="W78" s="11">
-        <f>IF(C78="","",IF(E78="","Type à choisir",IF(F78="","Objectif principal à choisir",IF(H78="","Intensité à choisir",IF(I78="","Format à choisir",IF(COUNTIF(M78:V78,"Cours co")+COUNTIF(M78:V78,"SGT")=0,"Aucun club coché",IF(E78=IF(COUNTIF(M78:V78,"Cours co")&gt;0,IF(COUNTIF(M78:V78,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X78" s="12" t="n"/>
+      <c r="W78" s="13" t="n"/>
+      <c r="X78" s="13" t="n"/>
+      <c r="Y78" s="11">
+        <f>IF(C78="","",IF(E78="","Type à choisir",IF(H78="","Objectif principal à choisir",IF(J78="","Intensité à choisir",IF(K78="","Format à choisir",IF(COUNTA(O78:X78)=0,"Aucun club coché",IF(AND(F78&lt;&gt;"",COUNTIF($A$2:$A$81,F78)=0),"Même cours que : identifiant inconnu",IF(AND(F78&lt;&gt;"",F78=A78),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z78" s="12" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="8" t="n"/>
@@ -5447,10 +5930,10 @@
       <c r="G79" s="12" t="n"/>
       <c r="H79" s="12" t="n"/>
       <c r="I79" s="12" t="n"/>
-      <c r="J79" s="13" t="n"/>
+      <c r="J79" s="12" t="n"/>
       <c r="K79" s="12" t="n"/>
       <c r="L79" s="13" t="n"/>
-      <c r="M79" s="13" t="n"/>
+      <c r="M79" s="12" t="n"/>
       <c r="N79" s="13" t="n"/>
       <c r="O79" s="13" t="n"/>
       <c r="P79" s="13" t="n"/>
@@ -5460,120 +5943,187 @@
       <c r="T79" s="13" t="n"/>
       <c r="U79" s="13" t="n"/>
       <c r="V79" s="13" t="n"/>
-      <c r="W79" s="11">
-        <f>IF(C79="","",IF(E79="","Type à choisir",IF(F79="","Objectif principal à choisir",IF(H79="","Intensité à choisir",IF(I79="","Format à choisir",IF(COUNTIF(M79:V79,"Cours co")+COUNTIF(M79:V79,"SGT")=0,"Aucun club coché",IF(E79=IF(COUNTIF(M79:V79,"Cours co")&gt;0,IF(COUNTIF(M79:V79,"SGT")&gt;0,"Les deux selon le club","Cours co"),"SGT"),"OK","Type et clubs se contredisent")))))))</f>
-        <v/>
-      </c>
-      <c r="X79" s="12" t="n"/>
+      <c r="W79" s="13" t="n"/>
+      <c r="X79" s="13" t="n"/>
+      <c r="Y79" s="11">
+        <f>IF(C79="","",IF(E79="","Type à choisir",IF(H79="","Objectif principal à choisir",IF(J79="","Intensité à choisir",IF(K79="","Format à choisir",IF(COUNTA(O79:X79)=0,"Aucun club coché",IF(AND(F79&lt;&gt;"",COUNTIF($A$2:$A$81,F79)=0),"Même cours que : identifiant inconnu",IF(AND(F79&lt;&gt;"",F79=A79),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z79" s="12" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="8" t="n"/>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="12" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="12" t="n"/>
+      <c r="G80" s="12" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="13" t="n"/>
+      <c r="M80" s="12" t="n"/>
+      <c r="N80" s="13" t="n"/>
+      <c r="O80" s="13" t="n"/>
+      <c r="P80" s="13" t="n"/>
+      <c r="Q80" s="13" t="n"/>
+      <c r="R80" s="13" t="n"/>
+      <c r="S80" s="13" t="n"/>
+      <c r="T80" s="13" t="n"/>
+      <c r="U80" s="13" t="n"/>
+      <c r="V80" s="13" t="n"/>
+      <c r="W80" s="13" t="n"/>
+      <c r="X80" s="13" t="n"/>
+      <c r="Y80" s="11">
+        <f>IF(C80="","",IF(E80="","Type à choisir",IF(H80="","Objectif principal à choisir",IF(J80="","Intensité à choisir",IF(K80="","Format à choisir",IF(COUNTA(O80:X80)=0,"Aucun club coché",IF(AND(F80&lt;&gt;"",COUNTIF($A$2:$A$81,F80)=0),"Même cours que : identifiant inconnu",IF(AND(F80&lt;&gt;"",F80=A80),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z80" s="12" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="8" t="n"/>
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="12" t="n"/>
+      <c r="G81" s="12" t="n"/>
+      <c r="H81" s="12" t="n"/>
+      <c r="I81" s="12" t="n"/>
+      <c r="J81" s="12" t="n"/>
+      <c r="K81" s="12" t="n"/>
+      <c r="L81" s="13" t="n"/>
+      <c r="M81" s="12" t="n"/>
+      <c r="N81" s="13" t="n"/>
+      <c r="O81" s="13" t="n"/>
+      <c r="P81" s="13" t="n"/>
+      <c r="Q81" s="13" t="n"/>
+      <c r="R81" s="13" t="n"/>
+      <c r="S81" s="13" t="n"/>
+      <c r="T81" s="13" t="n"/>
+      <c r="U81" s="13" t="n"/>
+      <c r="V81" s="13" t="n"/>
+      <c r="W81" s="13" t="n"/>
+      <c r="X81" s="13" t="n"/>
+      <c r="Y81" s="11">
+        <f>IF(C81="","",IF(E81="","Type à choisir",IF(H81="","Objectif principal à choisir",IF(J81="","Intensité à choisir",IF(K81="","Format à choisir",IF(COUNTA(O81:X81)=0,"Aucun club coché",IF(AND(F81&lt;&gt;"",COUNTIF($A$2:$A$81,F81)=0),"Même cours que : identifiant inconnu",IF(AND(F81&lt;&gt;"",F81=A81),"Même cours que : la ligne se cite elle-même","OK"))))))))</f>
+        <v/>
+      </c>
+      <c r="Z81" s="12" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:X79"/>
-  <conditionalFormatting sqref="W2:W79">
+  <autoFilter ref="A1:Z81"/>
+  <conditionalFormatting sqref="Y2:Y81">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>AND($W2&lt;&gt;"",$W2&lt;&gt;"OK")</formula>
+      <formula>AND($Y2&lt;&gt;"",$Y2&lt;&gt;"OK")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M79">
+  <conditionalFormatting sqref="O2:O81">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$M2="SGT"</formula>
+      <formula>AND(O2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="3" dxfId="2">
-      <formula>$M2="Cours co"</formula>
+      <formula>AND(O2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N79">
+  <conditionalFormatting sqref="P2:P81">
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>$N2="SGT"</formula>
+      <formula>AND(P2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="5" dxfId="2">
-      <formula>$N2="Cours co"</formula>
+      <formula>AND(P2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O79">
+  <conditionalFormatting sqref="Q2:Q81">
     <cfRule type="expression" priority="6" dxfId="1">
-      <formula>$O2="SGT"</formula>
+      <formula>AND(Q2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="7" dxfId="2">
-      <formula>$O2="Cours co"</formula>
+      <formula>AND(Q2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P79">
+  <conditionalFormatting sqref="R2:R81">
     <cfRule type="expression" priority="8" dxfId="1">
-      <formula>$P2="SGT"</formula>
+      <formula>AND(R2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="9" dxfId="2">
-      <formula>$P2="Cours co"</formula>
+      <formula>AND(R2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q79">
+  <conditionalFormatting sqref="S2:S81">
     <cfRule type="expression" priority="10" dxfId="1">
-      <formula>$Q2="SGT"</formula>
+      <formula>AND(S2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="11" dxfId="2">
-      <formula>$Q2="Cours co"</formula>
+      <formula>AND(S2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R79">
+  <conditionalFormatting sqref="T2:T81">
     <cfRule type="expression" priority="12" dxfId="1">
-      <formula>$R2="SGT"</formula>
+      <formula>AND(T2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="13" dxfId="2">
-      <formula>$R2="Cours co"</formula>
+      <formula>AND(T2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S79">
+  <conditionalFormatting sqref="U2:U81">
     <cfRule type="expression" priority="14" dxfId="1">
-      <formula>$S2="SGT"</formula>
+      <formula>AND(U2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="15" dxfId="2">
-      <formula>$S2="Cours co"</formula>
+      <formula>AND(U2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T79">
+  <conditionalFormatting sqref="V2:V81">
     <cfRule type="expression" priority="16" dxfId="1">
-      <formula>$T2="SGT"</formula>
+      <formula>AND(V2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="17" dxfId="2">
-      <formula>$T2="Cours co"</formula>
+      <formula>AND(V2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U79">
+  <conditionalFormatting sqref="W2:W81">
     <cfRule type="expression" priority="18" dxfId="1">
-      <formula>$U2="SGT"</formula>
+      <formula>AND(W2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="19" dxfId="2">
-      <formula>$U2="Cours co"</formula>
+      <formula>AND(W2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V79">
+  <conditionalFormatting sqref="X2:X81">
     <cfRule type="expression" priority="20" dxfId="1">
-      <formula>$V2="SGT"</formula>
+      <formula>AND(X2&lt;&gt;"",$E2="SGT")</formula>
     </cfRule>
     <cfRule type="expression" priority="21" dxfId="2">
-      <formula>$V2="Cours co"</formula>
+      <formula>AND(X2&lt;&gt;"",$E2="Cours co")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="7">
-    <dataValidation sqref="D2:D79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
+  <dataValidations count="8">
+    <dataValidation sqref="D2:D81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
       <formula1>Listes!$F$2:$F$4</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
-      <formula1>Listes!$D$2:$D$4</formula1>
+    <dataValidation sqref="E2:E81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
+      <formula1>Listes!$D$2:$D$3</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:G79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
+    <dataValidation sqref="G2:G81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
+      <formula1>Listes!$H$2:$H$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="H2:I81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
       <formula1>Listes!$A$2:$A$7</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
+    <dataValidation sqref="J2:J81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
       <formula1>Listes!$B$2:$B$4</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
+    <dataValidation sqref="K2:K81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
       <formula1>Listes!$C$2:$C$4</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
+    <dataValidation sqref="M2:M81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
       <formula1>Listes!$G$2:$G$6</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:V79" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
-      <formula1>Listes!$E$2:$E$3</formula1>
+    <dataValidation sqref="O2:X81" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valeur hors liste" error="Choisissez une valeur dans la liste." type="list">
+      <formula1>Listes!$E$2:$E$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5596,6 +6146,7 @@
     <col width="24" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5621,7 +6172,7 @@
       </c>
       <c r="E1" s="14" t="inlineStr">
         <is>
-          <t>Formes</t>
+          <t>Coche</t>
         </is>
       </c>
       <c r="F1" s="14" t="inlineStr">
@@ -5632,6 +6183,11 @@
       <c r="G1" s="14" t="inlineStr">
         <is>
           <t>Licences</t>
+        </is>
+      </c>
+      <c r="H1" s="14" t="inlineStr">
+        <is>
+          <t>Familles</t>
         </is>
       </c>
       <c r="I1" s="15" t="inlineStr">
@@ -5663,7 +6219,7 @@
       </c>
       <c r="E2" s="16" t="inlineStr">
         <is>
-          <t>Cours co</t>
+          <t>x</t>
         </is>
       </c>
       <c r="F2" s="16" t="inlineStr">
@@ -5672,6 +6228,11 @@
         </is>
       </c>
       <c r="G2" s="16" t="inlineStr">
+        <is>
+          <t>Aucune</t>
+        </is>
+      </c>
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>Aucune</t>
         </is>
@@ -5703,11 +6264,6 @@
           <t>SGT</t>
         </is>
       </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>SGT</t>
-        </is>
-      </c>
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>Nouveau</t>
@@ -5716,6 +6272,11 @@
       <c r="G3" s="16" t="inlineStr">
         <is>
           <t>Les Mills</t>
+        </is>
+      </c>
+      <c r="H3" s="16" t="inlineStr">
+        <is>
+          <t>Pilates</t>
         </is>
       </c>
     </row>
@@ -5735,11 +6296,6 @@
           <t>Petit groupe</t>
         </is>
       </c>
-      <c r="D4" s="16" t="inlineStr">
-        <is>
-          <t>Les deux selon le club</t>
-        </is>
-      </c>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>À retirer</t>
@@ -5748,6 +6304,11 @@
       <c r="G4" s="16" t="inlineStr">
         <is>
           <t>Hyrox</t>
+        </is>
+      </c>
+      <c r="H4" s="16" t="inlineStr">
+        <is>
+          <t>Yoga</t>
         </is>
       </c>
     </row>
@@ -5762,6 +6323,11 @@
           <t>Les Mills + Hyrox</t>
         </is>
       </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>Les Mills</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="16" t="inlineStr">
@@ -5772,6 +6338,11 @@
       <c r="G6" s="16" t="inlineStr">
         <is>
           <t>Autre</t>
+        </is>
+      </c>
+      <c r="H6" s="16" t="inlineStr">
+        <is>
+          <t>Aqua</t>
         </is>
       </c>
     </row>
@@ -5793,7 +6364,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H54"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6356,12 +6927,12 @@
     <row r="34">
       <c r="A34" s="15" t="inlineStr">
         <is>
-          <t>circuit-training</t>
+          <t>hiit-sgt</t>
         </is>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Circuit Training</t>
+          <t>HIIT</t>
         </is>
       </c>
       <c r="C34" s="17" t="n"/>
@@ -6372,12 +6943,12 @@
     <row r="35">
       <c r="A35" s="15" t="inlineStr">
         <is>
-          <t>cross-training</t>
+          <t>circuit-training</t>
         </is>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Cross Training</t>
+          <t>Circuit Training</t>
         </is>
       </c>
       <c r="C35" s="17" t="n"/>
@@ -6388,12 +6959,12 @@
     <row r="36">
       <c r="A36" s="15" t="inlineStr">
         <is>
-          <t>indoor-cycling</t>
+          <t>cross-training</t>
         </is>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>Indoor Cycling</t>
+          <t>Cross Training</t>
         </is>
       </c>
       <c r="C36" s="17" t="n"/>
@@ -6404,12 +6975,12 @@
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
         <is>
-          <t>step</t>
+          <t>cross-training-sgt</t>
         </is>
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>Step</t>
+          <t>Cross Training</t>
         </is>
       </c>
       <c r="C37" s="17" t="n"/>
@@ -6420,12 +6991,12 @@
     <row r="38">
       <c r="A38" s="15" t="inlineStr">
         <is>
-          <t>core-bike</t>
+          <t>indoor-cycling</t>
         </is>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>Core Bike</t>
+          <t>Indoor Cycling</t>
         </is>
       </c>
       <c r="C38" s="17" t="n"/>
@@ -6436,12 +7007,12 @@
     <row r="39">
       <c r="A39" s="15" t="inlineStr">
         <is>
-          <t>hybrid-training</t>
+          <t>step</t>
         </is>
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>Hybrid Training by Harmony</t>
+          <t>Step</t>
         </is>
       </c>
       <c r="C39" s="17" t="n"/>
@@ -6452,12 +7023,12 @@
     <row r="40">
       <c r="A40" s="15" t="inlineStr">
         <is>
-          <t>stretching</t>
+          <t>core-bike</t>
         </is>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>Stretching</t>
+          <t>Core Bike</t>
         </is>
       </c>
       <c r="C40" s="17" t="n"/>
@@ -6468,12 +7039,12 @@
     <row r="41">
       <c r="A41" s="15" t="inlineStr">
         <is>
-          <t>mobilite-stretching</t>
+          <t>hybrid-training</t>
         </is>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Mobilité Stretching</t>
+          <t>Hybrid Training by Harmony</t>
         </is>
       </c>
       <c r="C41" s="17" t="n"/>
@@ -6484,12 +7055,12 @@
     <row r="42">
       <c r="A42" s="15" t="inlineStr">
         <is>
-          <t>gym-douce</t>
+          <t>stretching</t>
         </is>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>Gym Douce</t>
+          <t>Stretching</t>
         </is>
       </c>
       <c r="C42" s="17" t="n"/>
@@ -6500,12 +7071,12 @@
     <row r="43">
       <c r="A43" s="15" t="inlineStr">
         <is>
-          <t>gym-douce-dos</t>
+          <t>mobilite-stretching</t>
         </is>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>Gym Douce Dos</t>
+          <t>Mobilité Stretching</t>
         </is>
       </c>
       <c r="C43" s="17" t="n"/>
@@ -6516,12 +7087,12 @@
     <row r="44">
       <c r="A44" s="15" t="inlineStr">
         <is>
-          <t>move-and-mind</t>
+          <t>gym-douce</t>
         </is>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>Move &amp; Mind</t>
+          <t>Gym Douce</t>
         </is>
       </c>
       <c r="C44" s="17" t="n"/>
@@ -6532,12 +7103,12 @@
     <row r="45">
       <c r="A45" s="15" t="inlineStr">
         <is>
-          <t>cours-zen</t>
+          <t>gym-douce-dos</t>
         </is>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>Cours Zen</t>
+          <t>Gym Douce Dos</t>
         </is>
       </c>
       <c r="C45" s="17" t="n"/>
@@ -6548,12 +7119,12 @@
     <row r="46">
       <c r="A46" s="15" t="inlineStr">
         <is>
-          <t>sophrologie-stretching</t>
+          <t>move-and-mind</t>
         </is>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>Sophrologie Stretching</t>
+          <t>Move &amp; Mind</t>
         </is>
       </c>
       <c r="C46" s="17" t="n"/>
@@ -6564,12 +7135,12 @@
     <row r="47">
       <c r="A47" s="15" t="inlineStr">
         <is>
-          <t>zumba</t>
+          <t>cours-zen</t>
         </is>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>Zumba</t>
+          <t>Cours Zen</t>
         </is>
       </c>
       <c r="C47" s="17" t="n"/>
@@ -6580,12 +7151,12 @@
     <row r="48">
       <c r="A48" s="15" t="inlineStr">
         <is>
-          <t>salsa</t>
+          <t>sophrologie-stretching</t>
         </is>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>Salsa</t>
+          <t>Sophrologie Stretching</t>
         </is>
       </c>
       <c r="C48" s="17" t="n"/>
@@ -6596,12 +7167,12 @@
     <row r="49">
       <c r="A49" s="15" t="inlineStr">
         <is>
-          <t>all-styles-dance</t>
+          <t>zumba</t>
         </is>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>All Styles Dance</t>
+          <t>Zumba</t>
         </is>
       </c>
       <c r="C49" s="17" t="n"/>
@@ -6612,12 +7183,12 @@
     <row r="50">
       <c r="A50" s="15" t="inlineStr">
         <is>
-          <t>boxe</t>
+          <t>salsa</t>
         </is>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>Boxe</t>
+          <t>Salsa</t>
         </is>
       </c>
       <c r="C50" s="17" t="n"/>
@@ -6628,12 +7199,12 @@
     <row r="51">
       <c r="A51" s="15" t="inlineStr">
         <is>
-          <t>hiit-boxing</t>
+          <t>all-styles-dance</t>
         </is>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>HIIT Boxing</t>
+          <t>All Styles Dance</t>
         </is>
       </c>
       <c r="C51" s="17" t="n"/>
@@ -6644,12 +7215,12 @@
     <row r="52">
       <c r="A52" s="15" t="inlineStr">
         <is>
-          <t>flow</t>
+          <t>boxe</t>
         </is>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>Flow</t>
+          <t>Boxe</t>
         </is>
       </c>
       <c r="C52" s="17" t="n"/>
@@ -6660,12 +7231,12 @@
     <row r="53">
       <c r="A53" s="15" t="inlineStr">
         <is>
-          <t>lorem-ipsum</t>
+          <t>hiit-boxing</t>
         </is>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>Lorem Ipsum</t>
+          <t>HIIT Boxing</t>
         </is>
       </c>
       <c r="C53" s="17" t="n"/>
@@ -6676,18 +7247,50 @@
     <row r="54">
       <c r="A54" s="15" t="inlineStr">
         <is>
-          <t>ceremony-hyrox-max</t>
+          <t>flow</t>
         </is>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>Ceremony Hyrox Max</t>
+          <t>Flow</t>
         </is>
       </c>
       <c r="C54" s="17" t="n"/>
       <c r="D54" s="17" t="n"/>
       <c r="E54" s="17" t="n"/>
       <c r="F54" s="17" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="15" t="inlineStr">
+        <is>
+          <t>lorem-ipsum</t>
+        </is>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>Lorem Ipsum</t>
+        </is>
+      </c>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="n"/>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="17" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="15" t="inlineStr">
+        <is>
+          <t>ceremony-hyrox-max</t>
+        </is>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Ceremony Hyrox Max</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="n"/>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
